--- a/output/oem_master.xlsx
+++ b/output/oem_master.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -469,8 +469,9 @@
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -501,15 +502,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>source_sheet</t>
         </is>
@@ -526,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H356"/>
+  <dimension ref="A1:I356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -535,8 +541,9 @@
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -567,15 +574,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>source_sheet</t>
         </is>
@@ -607,13 +619,18 @@
           <t>TALUSIA HR 140 BN140</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -641,13 +658,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -675,13 +697,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -709,13 +736,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -743,13 +775,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -777,13 +814,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -811,13 +853,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -845,13 +892,18 @@
           <t>TALUSIA HD 40 BN40 [GP.II BASE OIL]</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -879,13 +931,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -913,13 +970,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -947,13 +1009,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -981,13 +1048,18 @@
           <t>ATLANTA MARINE D 3005 BN5</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1015,13 +1087,18 @@
           <t>TALUSIA HR 140 BN140</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1049,13 +1126,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1083,13 +1165,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1117,13 +1204,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1151,13 +1243,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1185,13 +1282,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1219,13 +1321,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1253,13 +1360,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1287,13 +1399,18 @@
           <t>TALUSIA HD 40 BN40 [GP.II BASE OIL]</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1321,13 +1438,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1355,13 +1477,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -1389,13 +1516,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1423,13 +1555,18 @@
           <t>ATLANTA MARINE D 3005 BN5</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1457,13 +1594,18 @@
           <t>TALUSIA HR 140 BN140</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1491,13 +1633,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1525,13 +1672,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1559,13 +1711,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1593,13 +1750,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1627,13 +1789,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -1661,13 +1828,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1695,13 +1867,18 @@
           <t>TALUSIA HD 40 BN40 [GP.II BASE OIL]</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -1729,13 +1906,18 @@
           <t>TALUSIA HD 40 BN40 [GP.II BASE OIL]</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1763,13 +1945,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -1797,13 +1984,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1831,13 +2023,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -1865,13 +2062,18 @@
           <t>ATLANTA MARINE D 3005 BN5</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1899,13 +2101,18 @@
           <t>TALUSIA HR 140 BN140</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -1933,13 +2140,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1967,13 +2179,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -2001,13 +2218,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2035,13 +2257,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -2069,13 +2296,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2103,13 +2335,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -2137,13 +2374,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2171,13 +2413,18 @@
           <t>TALUSIA HD 40 BN40 [GP.II BASE OIL]</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -2205,13 +2452,18 @@
           <t>TALUSIA HD 40 BN40 [GP.II BASE OIL]</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H49" s="4" t="inlineStr"/>
+      <c r="I49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2239,13 +2491,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -2273,13 +2530,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2307,13 +2569,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -2341,13 +2608,18 @@
           <t>ATLANTA MARINE D 3005 BN5</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2375,13 +2647,18 @@
           <t>TALUSIA HR 140 BN140</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -2409,13 +2686,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2443,13 +2725,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -2477,13 +2764,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2511,13 +2803,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -2545,13 +2842,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H59" s="4" t="inlineStr"/>
+      <c r="I59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2579,13 +2881,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -2613,13 +2920,18 @@
           <t>TALUSIA HD 40 BN40 [GP.II BASE OIL]</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H61" s="4" t="inlineStr"/>
+      <c r="I61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2647,13 +2959,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -2681,13 +2998,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H63" s="4" t="inlineStr"/>
+      <c r="I63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2715,13 +3037,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -2749,13 +3076,18 @@
           <t>ATLANTA MARINE D 3005 BN5</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H65" s="4" t="inlineStr"/>
+      <c r="I65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2783,13 +3115,18 @@
           <t>TALUSIA HR 140 BN140</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -2817,13 +3154,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100</t>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H67" s="4" t="inlineStr"/>
+      <c r="I67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2851,13 +3193,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -2885,13 +3232,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H69" s="4" t="inlineStr"/>
+      <c r="I69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2919,13 +3271,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -2953,13 +3310,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H71" s="4" t="inlineStr"/>
+      <c r="I71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2987,13 +3349,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -3021,13 +3388,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H73" s="4" t="inlineStr"/>
+      <c r="I73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3055,13 +3427,18 @@
           <t>TALUSIA HD 40 BN40 [GP.II BASE OIL]</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -3089,13 +3466,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H75" s="4" t="inlineStr"/>
+      <c r="I75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3123,13 +3505,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -3157,13 +3544,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H77" s="4" t="inlineStr"/>
+      <c r="I77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3191,13 +3583,18 @@
           <t>ATLANTA MARINE D 3005 BN5</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -3225,13 +3622,18 @@
           <t>TALUSIA HR 140 BN140</t>
         </is>
       </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H79" s="4" t="inlineStr"/>
+      <c r="I79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -3259,13 +3661,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100</t>
         </is>
       </c>
-      <c r="F80" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -3293,13 +3700,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H81" s="4" t="inlineStr"/>
+      <c r="I81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -3327,13 +3739,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F82" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -3361,13 +3778,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H83" s="4" t="inlineStr"/>
+      <c r="I83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -3395,13 +3817,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F84" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -3429,13 +3856,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H85" s="4" t="inlineStr"/>
+      <c r="I85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -3463,13 +3895,18 @@
           <t>TALUSIA HD 40 BN40 [GP.II BASE OIL]</t>
         </is>
       </c>
-      <c r="F86" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -3497,13 +3934,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H87" s="4" t="inlineStr"/>
+      <c r="I87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -3531,13 +3973,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -3565,13 +4012,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H89" s="4" t="inlineStr"/>
+      <c r="I89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -3599,13 +4051,18 @@
           <t>ATLANTA MARINE D 3005 BN5</t>
         </is>
       </c>
-      <c r="F90" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -3633,13 +4090,18 @@
           <t>TALUSIA HR 140 BN140</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H91" s="4" t="inlineStr"/>
+      <c r="I91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -3667,13 +4129,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100</t>
         </is>
       </c>
-      <c r="F92" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -3701,13 +4168,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H93" s="4" t="inlineStr"/>
+      <c r="I93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -3735,13 +4207,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F94" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -3769,13 +4246,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H95" s="4" t="inlineStr"/>
+      <c r="I95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -3803,13 +4285,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -3837,13 +4324,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H97" s="4" t="inlineStr"/>
+      <c r="I97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -3871,13 +4363,18 @@
           <t>TALUSIA HD 40 BN40 [GP.II BASE OIL]</t>
         </is>
       </c>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -3905,13 +4402,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H99" s="4" t="inlineStr"/>
+      <c r="I99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -3939,13 +4441,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F100" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -3973,13 +4480,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H101" s="4" t="inlineStr"/>
+      <c r="I101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -4007,13 +4519,18 @@
           <t>ATLANTA MARINE D 3005 BN5</t>
         </is>
       </c>
-      <c r="F102" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -4041,13 +4558,18 @@
           <t>TALUSIA HR 140 BN140</t>
         </is>
       </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H103" s="4" t="inlineStr"/>
+      <c r="I103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -4075,13 +4597,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100</t>
         </is>
       </c>
-      <c r="F104" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -4109,13 +4636,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G105" s="4" t="inlineStr"/>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H105" s="4" t="inlineStr"/>
+      <c r="I105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -4143,13 +4675,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F106" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -4177,13 +4714,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G107" s="4" t="inlineStr"/>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H107" s="4" t="inlineStr"/>
+      <c r="I107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -4211,13 +4753,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F108" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -4245,13 +4792,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H109" s="4" t="inlineStr"/>
+      <c r="I109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -4279,13 +4831,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F110" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -4313,13 +4870,18 @@
           <t>TALUSIA HD 40 BN40 [GP.II BASE OIL]</t>
         </is>
       </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H111" s="4" t="inlineStr"/>
+      <c r="I111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -4347,13 +4909,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F112" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -4381,13 +4948,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H113" s="4" t="inlineStr"/>
+      <c r="I113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -4415,13 +4987,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F114" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -4449,13 +5026,18 @@
           <t>ATLANTA MARINE D 3005 BN5</t>
         </is>
       </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H115" s="4" t="inlineStr"/>
+      <c r="I115" s="4" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -4483,13 +5065,18 @@
           <t>TALUSIA HR 140 BN140</t>
         </is>
       </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -4517,13 +5104,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100</t>
         </is>
       </c>
-      <c r="F117" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H117" s="4" t="inlineStr"/>
+      <c r="I117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -4551,13 +5143,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -4585,13 +5182,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H119" s="4" t="inlineStr"/>
+      <c r="I119" s="4" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -4619,13 +5221,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -4653,13 +5260,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H121" s="4" t="inlineStr"/>
+      <c r="I121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -4687,13 +5299,18 @@
           <t>TALUSIA UNIVERSAL 57 BN57</t>
         </is>
       </c>
-      <c r="F122" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -4721,13 +5338,18 @@
           <t>TALUSIA HD 40 BN40 [GP.II BASE OIL]</t>
         </is>
       </c>
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H123" s="4" t="inlineStr"/>
+      <c r="I123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -4755,13 +5377,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F124" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -4789,13 +5416,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H125" s="4" t="inlineStr"/>
+      <c r="I125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -4823,13 +5455,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F126" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -4857,13 +5494,18 @@
           <t>ATLANTA MARINE D 3005 BN5</t>
         </is>
       </c>
-      <c r="F127" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H127" s="4" t="inlineStr"/>
+      <c r="I127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -4891,13 +5533,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F128" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -4925,13 +5572,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F129" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H129" s="4" t="inlineStr"/>
+      <c r="I129" s="4" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -4959,13 +5611,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F130" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H130" s="2" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -4993,13 +5650,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F131" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H131" s="4" t="inlineStr"/>
+      <c r="I131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -5027,13 +5689,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F132" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr"/>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -5061,13 +5728,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F133" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H133" s="4" t="inlineStr"/>
+      <c r="I133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -5095,13 +5767,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F134" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -5129,13 +5806,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H135" s="4" t="inlineStr"/>
+      <c r="I135" s="4" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -5163,13 +5845,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H136" s="2" t="inlineStr"/>
+      <c r="I136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -5197,13 +5884,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F137" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H137" s="4" t="inlineStr"/>
+      <c r="I137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -5231,13 +5923,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F138" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -5265,13 +5962,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F139" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G139" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H139" s="4" t="inlineStr"/>
+      <c r="I139" s="4" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -5299,13 +6001,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F140" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr"/>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H140" s="2" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -5333,13 +6040,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F141" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G141" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H141" s="4" t="inlineStr"/>
+      <c r="I141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -5367,13 +6079,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F142" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr"/>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -5401,13 +6118,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F143" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G143" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H143" s="4" t="inlineStr"/>
+      <c r="I143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -5435,13 +6157,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F144" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr"/>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H144" s="2" t="inlineStr"/>
+      <c r="I144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -5469,13 +6196,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F145" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G145" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H145" s="4" t="inlineStr"/>
+      <c r="I145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -5503,13 +6235,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F146" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="inlineStr"/>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H146" s="2" t="inlineStr"/>
+      <c r="I146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -5537,13 +6274,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F147" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G147" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H147" s="4" t="inlineStr"/>
+      <c r="I147" s="4" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -5571,13 +6313,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F148" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="inlineStr"/>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H148" s="2" t="inlineStr"/>
+      <c r="I148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -5605,13 +6352,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F149" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G149" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H149" s="4" t="inlineStr"/>
+      <c r="I149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -5639,13 +6391,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F150" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr"/>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H150" s="2" t="inlineStr"/>
+      <c r="I150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -5673,13 +6430,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F151" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G151" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H151" s="4" t="inlineStr"/>
+      <c r="I151" s="4" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -5707,13 +6469,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F152" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr"/>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H152" s="2" t="inlineStr"/>
+      <c r="I152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -5741,13 +6508,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F153" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G153" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H153" s="4" t="inlineStr"/>
+      <c r="I153" s="4" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -5775,13 +6547,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F154" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="inlineStr"/>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H154" s="2" t="inlineStr"/>
+      <c r="I154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -5809,13 +6586,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F155" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G155" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H155" s="4" t="inlineStr"/>
+      <c r="I155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -5843,13 +6625,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F156" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr"/>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H156" s="2" t="inlineStr"/>
+      <c r="I156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -5877,13 +6664,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F157" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G157" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H157" s="4" t="inlineStr"/>
+      <c r="I157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -5911,13 +6703,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F158" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr"/>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H158" s="2" t="inlineStr"/>
+      <c r="I158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -5945,13 +6742,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F159" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G159" s="4" t="inlineStr"/>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H159" s="4" t="inlineStr"/>
+      <c r="I159" s="4" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -5979,13 +6781,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F160" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="inlineStr"/>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H160" s="2" t="inlineStr"/>
+      <c r="I160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -6013,13 +6820,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F161" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G161" s="4" t="inlineStr"/>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H161" s="4" t="inlineStr"/>
+      <c r="I161" s="4" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -6047,13 +6859,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F162" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G162" s="2" t="inlineStr"/>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H162" s="2" t="inlineStr"/>
+      <c r="I162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
@@ -6081,13 +6898,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F163" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G163" s="4" t="inlineStr"/>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H163" s="4" t="inlineStr"/>
+      <c r="I163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -6115,13 +6937,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F164" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr"/>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H164" s="2" t="inlineStr"/>
+      <c r="I164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -6149,13 +6976,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F165" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G165" s="4" t="inlineStr"/>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G165" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H165" s="4" t="inlineStr"/>
+      <c r="I165" s="4" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -6183,13 +7015,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F166" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr"/>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H166" s="2" t="inlineStr"/>
+      <c r="I166" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -6217,13 +7054,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F167" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G167" s="4" t="inlineStr"/>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G167" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H167" s="4" t="inlineStr"/>
+      <c r="I167" s="4" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -6251,13 +7093,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F168" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr"/>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H168" s="2" t="inlineStr"/>
+      <c r="I168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -6285,13 +7132,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F169" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G169" s="4" t="inlineStr"/>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G169" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H169" s="4" t="inlineStr"/>
+      <c r="I169" s="4" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -6319,13 +7171,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F170" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G170" s="2" t="inlineStr"/>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H170" s="2" t="inlineStr"/>
+      <c r="I170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
@@ -6353,13 +7210,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F171" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G171" s="4" t="inlineStr"/>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G171" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H171" s="4" t="inlineStr"/>
+      <c r="I171" s="4" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -6387,13 +7249,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F172" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G172" s="2" t="inlineStr"/>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H172" s="2" t="inlineStr"/>
+      <c r="I172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
@@ -6421,13 +7288,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F173" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G173" s="4" t="inlineStr"/>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G173" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H173" s="4" t="inlineStr"/>
+      <c r="I173" s="4" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -6455,13 +7327,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F174" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G174" s="2" t="inlineStr"/>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H174" s="2" t="inlineStr"/>
+      <c r="I174" s="2" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -6489,13 +7366,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F175" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G175" s="4" t="inlineStr"/>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G175" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H175" s="4" t="inlineStr"/>
+      <c r="I175" s="4" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -6523,13 +7405,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F176" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G176" s="2" t="inlineStr"/>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H176" s="2" t="inlineStr"/>
+      <c r="I176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
@@ -6557,13 +7444,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F177" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G177" s="4" t="inlineStr"/>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G177" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H177" s="4" t="inlineStr"/>
+      <c r="I177" s="4" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -6591,13 +7483,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F178" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G178" s="2" t="inlineStr"/>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H178" s="2" t="inlineStr"/>
+      <c r="I178" s="2" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
@@ -6625,13 +7522,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F179" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G179" s="4" t="inlineStr"/>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G179" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H179" s="4" t="inlineStr"/>
+      <c r="I179" s="4" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -6659,13 +7561,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F180" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G180" s="2" t="inlineStr"/>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H180" s="2" t="inlineStr"/>
+      <c r="I180" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
@@ -6693,13 +7600,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F181" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G181" s="4" t="inlineStr"/>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G181" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H181" s="4" t="inlineStr"/>
+      <c r="I181" s="4" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -6727,13 +7639,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F182" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G182" s="2" t="inlineStr"/>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H182" s="2" t="inlineStr"/>
+      <c r="I182" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -6761,13 +7678,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F183" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G183" s="4" t="inlineStr"/>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H183" s="4" t="inlineStr"/>
+      <c r="I183" s="4" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -6795,13 +7717,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F184" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G184" s="2" t="inlineStr"/>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H184" s="2" t="inlineStr"/>
+      <c r="I184" s="2" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
@@ -6829,13 +7756,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F185" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G185" s="4" t="inlineStr"/>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G185" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H185" s="4" t="inlineStr"/>
+      <c r="I185" s="4" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -6863,13 +7795,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F186" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G186" s="2" t="inlineStr"/>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H186" s="2" t="inlineStr"/>
+      <c r="I186" s="2" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -6897,13 +7834,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F187" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G187" s="4" t="inlineStr"/>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H187" s="4" t="inlineStr"/>
+      <c r="I187" s="4" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -6931,13 +7873,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F188" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G188" s="2" t="inlineStr"/>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H188" s="2" t="inlineStr"/>
+      <c r="I188" s="2" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
@@ -6965,13 +7912,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F189" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G189" s="4" t="inlineStr"/>
+      <c r="F189" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H189" s="4" t="inlineStr"/>
+      <c r="I189" s="4" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -6999,13 +7951,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F190" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G190" s="2" t="inlineStr"/>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G190" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H190" s="2" t="inlineStr"/>
+      <c r="I190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
@@ -7033,13 +7990,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F191" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G191" s="4" t="inlineStr"/>
+      <c r="F191" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G191" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H191" s="4" t="inlineStr"/>
+      <c r="I191" s="4" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -7067,13 +8029,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F192" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G192" s="2" t="inlineStr"/>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H192" s="2" t="inlineStr"/>
+      <c r="I192" s="2" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
@@ -7101,13 +8068,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F193" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G193" s="4" t="inlineStr"/>
+      <c r="F193" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G193" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H193" s="4" t="inlineStr"/>
+      <c r="I193" s="4" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -7135,13 +8107,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F194" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G194" s="2" t="inlineStr"/>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H194" s="2" t="inlineStr"/>
+      <c r="I194" s="2" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
@@ -7169,13 +8146,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F195" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G195" s="4" t="inlineStr"/>
+      <c r="F195" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G195" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H195" s="4" t="inlineStr"/>
+      <c r="I195" s="4" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -7203,13 +8185,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F196" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G196" s="2" t="inlineStr"/>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H196" s="2" t="inlineStr"/>
+      <c r="I196" s="2" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
@@ -7237,13 +8224,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F197" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G197" s="4" t="inlineStr"/>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G197" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H197" s="4" t="inlineStr"/>
+      <c r="I197" s="4" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -7271,13 +8263,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F198" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G198" s="2" t="inlineStr"/>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H198" s="2" t="inlineStr"/>
+      <c r="I198" s="2" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
@@ -7305,13 +8302,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F199" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G199" s="4" t="inlineStr"/>
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G199" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H199" s="4" t="inlineStr"/>
+      <c r="I199" s="4" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -7339,13 +8341,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F200" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G200" s="2" t="inlineStr"/>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H200" s="2" t="inlineStr"/>
+      <c r="I200" s="2" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
@@ -7373,13 +8380,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F201" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G201" s="4" t="inlineStr"/>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G201" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H201" s="4" t="inlineStr"/>
+      <c r="I201" s="4" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -7407,13 +8419,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F202" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G202" s="2" t="inlineStr"/>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H202" s="2" t="inlineStr"/>
+      <c r="I202" s="2" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
@@ -7441,13 +8458,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F203" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G203" s="4" t="inlineStr"/>
+      <c r="F203" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G203" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H203" s="4" t="inlineStr"/>
+      <c r="I203" s="4" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -7475,13 +8497,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F204" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G204" s="2" t="inlineStr"/>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H204" s="2" t="inlineStr"/>
+      <c r="I204" s="2" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
@@ -7509,13 +8536,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F205" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G205" s="4" t="inlineStr"/>
+      <c r="F205" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G205" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H205" s="4" t="inlineStr"/>
+      <c r="I205" s="4" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -7543,13 +8575,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F206" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G206" s="2" t="inlineStr"/>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H206" s="2" t="inlineStr"/>
+      <c r="I206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
@@ -7577,13 +8614,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F207" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G207" s="4" t="inlineStr"/>
+      <c r="F207" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G207" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H207" s="4" t="inlineStr"/>
+      <c r="I207" s="4" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -7611,13 +8653,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F208" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G208" s="2" t="inlineStr"/>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H208" s="2" t="inlineStr"/>
+      <c r="I208" s="2" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
@@ -7645,13 +8692,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F209" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G209" s="4" t="inlineStr"/>
+      <c r="F209" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G209" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H209" s="4" t="inlineStr"/>
+      <c r="I209" s="4" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -7679,13 +8731,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F210" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G210" s="2" t="inlineStr"/>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H210" s="2" t="inlineStr"/>
+      <c r="I210" s="2" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
@@ -7713,13 +8770,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F211" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G211" s="4" t="inlineStr"/>
+      <c r="F211" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G211" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H211" s="4" t="inlineStr"/>
+      <c r="I211" s="4" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -7747,13 +8809,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F212" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G212" s="2" t="inlineStr"/>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H212" s="2" t="inlineStr"/>
+      <c r="I212" s="2" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
@@ -7781,13 +8848,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F213" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G213" s="4" t="inlineStr"/>
+      <c r="F213" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H213" s="4" t="inlineStr"/>
+      <c r="I213" s="4" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -7815,13 +8887,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F214" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G214" s="2" t="inlineStr"/>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H214" s="2" t="inlineStr"/>
+      <c r="I214" s="2" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
@@ -7849,13 +8926,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F215" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G215" s="4" t="inlineStr"/>
+      <c r="F215" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G215" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H215" s="4" t="inlineStr"/>
+      <c r="I215" s="4" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -7883,13 +8965,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F216" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G216" s="2" t="inlineStr"/>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H216" s="2" t="inlineStr"/>
+      <c r="I216" s="2" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
@@ -7917,13 +9004,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F217" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G217" s="4" t="inlineStr"/>
+      <c r="F217" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G217" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H217" s="4" t="inlineStr"/>
+      <c r="I217" s="4" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -7951,13 +9043,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F218" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G218" s="2" t="inlineStr"/>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H218" s="2" t="inlineStr"/>
+      <c r="I218" s="2" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
@@ -7985,13 +9082,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F219" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G219" s="4" t="inlineStr"/>
+      <c r="F219" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G219" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H219" s="4" t="inlineStr"/>
+      <c r="I219" s="4" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -8019,13 +9121,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F220" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G220" s="2" t="inlineStr"/>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H220" s="2" t="inlineStr"/>
+      <c r="I220" s="2" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
@@ -8053,13 +9160,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F221" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G221" s="4" t="inlineStr"/>
+      <c r="F221" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G221" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H221" s="4" t="inlineStr"/>
+      <c r="I221" s="4" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -8087,13 +9199,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F222" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G222" s="2" t="inlineStr"/>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H222" s="2" t="inlineStr"/>
+      <c r="I222" s="2" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
@@ -8121,13 +9238,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F223" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G223" s="4" t="inlineStr"/>
+      <c r="F223" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G223" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H223" s="4" t="inlineStr"/>
+      <c r="I223" s="4" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -8155,13 +9277,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F224" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G224" s="2" t="inlineStr"/>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H224" s="2" t="inlineStr"/>
+      <c r="I224" s="2" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
@@ -8189,13 +9316,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F225" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G225" s="4" t="inlineStr"/>
+      <c r="F225" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G225" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H225" s="4" t="inlineStr"/>
+      <c r="I225" s="4" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -8223,13 +9355,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F226" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G226" s="2" t="inlineStr"/>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H226" s="2" t="inlineStr"/>
+      <c r="I226" s="2" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
@@ -8257,13 +9394,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F227" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G227" s="4" t="inlineStr"/>
+      <c r="F227" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G227" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H227" s="4" t="inlineStr"/>
+      <c r="I227" s="4" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -8291,13 +9433,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F228" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G228" s="2" t="inlineStr"/>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G228" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H228" s="2" t="inlineStr"/>
+      <c r="I228" s="2" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
@@ -8325,13 +9472,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F229" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G229" s="4" t="inlineStr"/>
+      <c r="F229" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G229" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H229" s="4" t="inlineStr"/>
+      <c r="I229" s="4" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -8359,13 +9511,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F230" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G230" s="2" t="inlineStr"/>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G230" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H230" s="2" t="inlineStr"/>
+      <c r="I230" s="2" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
@@ -8393,13 +9550,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F231" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G231" s="4" t="inlineStr"/>
+      <c r="F231" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G231" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H231" s="4" t="inlineStr"/>
+      <c r="I231" s="4" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -8427,13 +9589,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F232" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G232" s="2" t="inlineStr"/>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H232" s="2" t="inlineStr"/>
+      <c r="I232" s="2" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
@@ -8461,13 +9628,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F233" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G233" s="4" t="inlineStr"/>
+      <c r="F233" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G233" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H233" s="4" t="inlineStr"/>
+      <c r="I233" s="4" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -8495,13 +9667,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F234" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G234" s="2" t="inlineStr"/>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H234" s="2" t="inlineStr"/>
+      <c r="I234" s="2" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
@@ -8529,13 +9706,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F235" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G235" s="4" t="inlineStr"/>
+      <c r="F235" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G235" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H235" s="4" t="inlineStr"/>
+      <c r="I235" s="4" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -8563,13 +9745,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F236" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G236" s="2" t="inlineStr"/>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H236" s="2" t="inlineStr"/>
+      <c r="I236" s="2" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
@@ -8597,13 +9784,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F237" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G237" s="4" t="inlineStr"/>
+      <c r="F237" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G237" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H237" s="4" t="inlineStr"/>
+      <c r="I237" s="4" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -8631,13 +9823,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F238" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G238" s="2" t="inlineStr"/>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G238" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H238" s="2" t="inlineStr"/>
+      <c r="I238" s="2" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
@@ -8665,13 +9862,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F239" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G239" s="4" t="inlineStr"/>
+      <c r="F239" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G239" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H239" s="4" t="inlineStr"/>
+      <c r="I239" s="4" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -8699,13 +9901,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F240" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G240" s="2" t="inlineStr"/>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G240" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H240" s="2" t="inlineStr"/>
+      <c r="I240" s="2" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
@@ -8733,13 +9940,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F241" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G241" s="4" t="inlineStr"/>
+      <c r="F241" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G241" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H241" s="4" t="inlineStr"/>
+      <c r="I241" s="4" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -8767,13 +9979,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F242" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G242" s="2" t="inlineStr"/>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G242" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H242" s="2" t="inlineStr"/>
+      <c r="I242" s="2" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
@@ -8801,13 +10018,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F243" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G243" s="4" t="inlineStr"/>
+      <c r="F243" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G243" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H243" s="4" t="inlineStr"/>
+      <c r="I243" s="4" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -8835,13 +10057,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F244" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G244" s="2" t="inlineStr"/>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G244" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H244" s="2" t="inlineStr"/>
+      <c r="I244" s="2" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
@@ -8869,13 +10096,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F245" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G245" s="4" t="inlineStr"/>
+      <c r="F245" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G245" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H245" s="4" t="inlineStr"/>
+      <c r="I245" s="4" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -8903,13 +10135,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F246" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G246" s="2" t="inlineStr"/>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G246" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H246" s="2" t="inlineStr"/>
+      <c r="I246" s="2" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
@@ -8937,13 +10174,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F247" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G247" s="4" t="inlineStr"/>
+      <c r="F247" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G247" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H247" s="4" t="inlineStr"/>
+      <c r="I247" s="4" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -8971,13 +10213,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F248" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G248" s="2" t="inlineStr"/>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G248" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H248" s="2" t="inlineStr"/>
+      <c r="I248" s="2" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
@@ -9005,13 +10252,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F249" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G249" s="4" t="inlineStr"/>
+      <c r="F249" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G249" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H249" s="4" t="inlineStr"/>
+      <c r="I249" s="4" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -9039,13 +10291,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F250" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G250" s="2" t="inlineStr"/>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G250" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H250" s="2" t="inlineStr"/>
+      <c r="I250" s="2" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
@@ -9073,13 +10330,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F251" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G251" s="4" t="inlineStr"/>
+      <c r="F251" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G251" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H251" s="4" t="inlineStr"/>
+      <c r="I251" s="4" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -9107,13 +10369,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F252" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G252" s="2" t="inlineStr"/>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G252" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H252" s="2" t="inlineStr"/>
+      <c r="I252" s="2" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
@@ -9141,13 +10408,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F253" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G253" s="4" t="inlineStr"/>
+      <c r="F253" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G253" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H253" s="4" t="inlineStr"/>
+      <c r="I253" s="4" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -9175,13 +10447,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F254" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G254" s="2" t="inlineStr"/>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G254" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H254" s="2" t="inlineStr"/>
+      <c r="I254" s="2" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
@@ -9209,13 +10486,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F255" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G255" s="4" t="inlineStr"/>
+      <c r="F255" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G255" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H255" s="4" t="inlineStr"/>
+      <c r="I255" s="4" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -9243,13 +10525,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F256" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G256" s="2" t="inlineStr"/>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G256" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H256" s="2" t="inlineStr"/>
+      <c r="I256" s="2" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
@@ -9277,13 +10564,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F257" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G257" s="4" t="inlineStr"/>
+      <c r="F257" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G257" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H257" s="4" t="inlineStr"/>
+      <c r="I257" s="4" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -9311,13 +10603,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F258" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G258" s="2" t="inlineStr"/>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G258" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H258" s="2" t="inlineStr"/>
+      <c r="I258" s="2" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
@@ -9345,13 +10642,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F259" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G259" s="4" t="inlineStr"/>
+      <c r="F259" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G259" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H259" s="4" t="inlineStr"/>
+      <c r="I259" s="4" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -9379,13 +10681,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F260" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G260" s="2" t="inlineStr"/>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G260" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H260" s="2" t="inlineStr"/>
+      <c r="I260" s="2" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
@@ -9413,13 +10720,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F261" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G261" s="4" t="inlineStr"/>
+      <c r="F261" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G261" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H261" s="4" t="inlineStr"/>
+      <c r="I261" s="4" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -9447,13 +10759,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F262" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G262" s="2" t="inlineStr"/>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G262" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H262" s="2" t="inlineStr"/>
+      <c r="I262" s="2" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
@@ -9481,13 +10798,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F263" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G263" s="4" t="inlineStr"/>
+      <c r="F263" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G263" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H263" s="4" t="inlineStr"/>
+      <c r="I263" s="4" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -9515,13 +10837,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F264" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G264" s="2" t="inlineStr"/>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G264" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H264" s="2" t="inlineStr"/>
+      <c r="I264" s="2" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
@@ -9549,13 +10876,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F265" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G265" s="4" t="inlineStr"/>
+      <c r="F265" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G265" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H265" s="4" t="inlineStr"/>
+      <c r="I265" s="4" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -9583,13 +10915,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F266" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G266" s="2" t="inlineStr"/>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G266" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H266" s="2" t="inlineStr"/>
+      <c r="I266" s="2" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
@@ -9617,13 +10954,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F267" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G267" s="4" t="inlineStr"/>
+      <c r="F267" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G267" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H267" s="4" t="inlineStr"/>
+      <c r="I267" s="4" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -9651,13 +10993,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F268" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G268" s="2" t="inlineStr"/>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G268" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H268" s="2" t="inlineStr"/>
+      <c r="I268" s="2" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
@@ -9685,13 +11032,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F269" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G269" s="4" t="inlineStr"/>
+      <c r="F269" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G269" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H269" s="4" t="inlineStr"/>
+      <c r="I269" s="4" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -9719,13 +11071,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F270" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G270" s="2" t="inlineStr"/>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G270" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H270" s="2" t="inlineStr"/>
+      <c r="I270" s="2" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
@@ -9753,13 +11110,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F271" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G271" s="4" t="inlineStr"/>
+      <c r="F271" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G271" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H271" s="4" t="inlineStr"/>
+      <c r="I271" s="4" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -9787,13 +11149,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F272" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G272" s="2" t="inlineStr"/>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G272" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H272" s="2" t="inlineStr"/>
+      <c r="I272" s="2" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
@@ -9821,13 +11188,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F273" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G273" s="4" t="inlineStr"/>
+      <c r="F273" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G273" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H273" s="4" t="inlineStr"/>
+      <c r="I273" s="4" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -9855,13 +11227,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F274" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G274" s="2" t="inlineStr"/>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G274" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H274" s="2" t="inlineStr"/>
+      <c r="I274" s="2" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
@@ -9889,13 +11266,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F275" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G275" s="4" t="inlineStr"/>
+      <c r="F275" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G275" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H275" s="4" t="inlineStr"/>
+      <c r="I275" s="4" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -9923,13 +11305,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F276" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G276" s="2" t="inlineStr"/>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G276" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H276" s="2" t="inlineStr"/>
+      <c r="I276" s="2" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
@@ -9957,13 +11344,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F277" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G277" s="4" t="inlineStr"/>
+      <c r="F277" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G277" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H277" s="4" t="inlineStr"/>
+      <c r="I277" s="4" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -9991,13 +11383,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F278" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G278" s="2" t="inlineStr"/>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G278" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H278" s="2" t="inlineStr"/>
+      <c r="I278" s="2" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
@@ -10025,13 +11422,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F279" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G279" s="4" t="inlineStr"/>
+      <c r="F279" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G279" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H279" s="4" t="inlineStr"/>
+      <c r="I279" s="4" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -10059,13 +11461,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F280" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G280" s="2" t="inlineStr"/>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G280" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H280" s="2" t="inlineStr"/>
+      <c r="I280" s="2" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
@@ -10093,13 +11500,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F281" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G281" s="4" t="inlineStr"/>
+      <c r="F281" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G281" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H281" s="4" t="inlineStr"/>
+      <c r="I281" s="4" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -10127,13 +11539,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F282" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G282" s="2" t="inlineStr"/>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G282" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H282" s="2" t="inlineStr"/>
+      <c r="I282" s="2" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
@@ -10161,13 +11578,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F283" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G283" s="4" t="inlineStr"/>
+      <c r="F283" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G283" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H283" s="4" t="inlineStr"/>
+      <c r="I283" s="4" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -10195,13 +11617,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F284" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G284" s="2" t="inlineStr"/>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G284" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H284" s="2" t="inlineStr"/>
+      <c r="I284" s="2" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
@@ -10229,13 +11656,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F285" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G285" s="4" t="inlineStr"/>
+      <c r="F285" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G285" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H285" s="4" t="inlineStr"/>
+      <c r="I285" s="4" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -10263,13 +11695,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F286" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G286" s="2" t="inlineStr"/>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G286" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H286" s="2" t="inlineStr"/>
+      <c r="I286" s="2" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
@@ -10297,13 +11734,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F287" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G287" s="4" t="inlineStr"/>
+      <c r="F287" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G287" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H287" s="4" t="inlineStr"/>
+      <c r="I287" s="4" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -10331,13 +11773,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F288" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G288" s="2" t="inlineStr"/>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G288" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H288" s="2" t="inlineStr"/>
+      <c r="I288" s="2" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
@@ -10365,13 +11812,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F289" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G289" s="4" t="inlineStr"/>
+      <c r="F289" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G289" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H289" s="4" t="inlineStr"/>
+      <c r="I289" s="4" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -10399,13 +11851,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F290" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G290" s="2" t="inlineStr"/>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G290" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H290" s="2" t="inlineStr"/>
+      <c r="I290" s="2" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
@@ -10433,13 +11890,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F291" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G291" s="4" t="inlineStr"/>
+      <c r="F291" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G291" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H291" s="4" t="inlineStr"/>
+      <c r="I291" s="4" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -10467,13 +11929,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F292" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G292" s="2" t="inlineStr"/>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G292" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H292" s="2" t="inlineStr"/>
+      <c r="I292" s="2" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
@@ -10501,13 +11968,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F293" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G293" s="4" t="inlineStr"/>
+      <c r="F293" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G293" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H293" s="4" t="inlineStr"/>
+      <c r="I293" s="4" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -10535,13 +12007,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F294" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G294" s="2" t="inlineStr"/>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G294" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H294" s="2" t="inlineStr"/>
+      <c r="I294" s="2" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
@@ -10569,13 +12046,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F295" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G295" s="4" t="inlineStr"/>
+      <c r="F295" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G295" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H295" s="4" t="inlineStr"/>
+      <c r="I295" s="4" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -10603,13 +12085,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F296" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G296" s="2" t="inlineStr"/>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G296" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H296" s="2" t="inlineStr"/>
+      <c r="I296" s="2" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
@@ -10637,13 +12124,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F297" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G297" s="4" t="inlineStr"/>
+      <c r="F297" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G297" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H297" s="4" t="inlineStr"/>
+      <c r="I297" s="4" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -10671,13 +12163,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F298" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G298" s="2" t="inlineStr"/>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G298" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H298" s="2" t="inlineStr"/>
+      <c r="I298" s="2" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
@@ -10705,13 +12202,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F299" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G299" s="4" t="inlineStr"/>
+      <c r="F299" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G299" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H299" s="4" t="inlineStr"/>
+      <c r="I299" s="4" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -10739,13 +12241,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F300" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G300" s="2" t="inlineStr"/>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G300" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H300" s="2" t="inlineStr"/>
+      <c r="I300" s="2" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
@@ -10773,13 +12280,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F301" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G301" s="4" t="inlineStr"/>
+      <c r="F301" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G301" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H301" s="4" t="inlineStr"/>
+      <c r="I301" s="4" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -10807,13 +12319,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F302" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G302" s="2" t="inlineStr"/>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G302" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H302" s="2" t="inlineStr"/>
+      <c r="I302" s="2" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
@@ -10841,13 +12358,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F303" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G303" s="4" t="inlineStr"/>
+      <c r="F303" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G303" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H303" s="4" t="inlineStr"/>
+      <c r="I303" s="4" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -10875,13 +12397,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F304" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G304" s="2" t="inlineStr"/>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G304" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H304" s="2" t="inlineStr"/>
+      <c r="I304" s="2" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
@@ -10909,13 +12436,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F305" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G305" s="4" t="inlineStr"/>
+      <c r="F305" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G305" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H305" s="4" t="inlineStr"/>
+      <c r="I305" s="4" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -10943,13 +12475,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F306" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G306" s="2" t="inlineStr"/>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G306" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H306" s="2" t="inlineStr"/>
+      <c r="I306" s="2" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
@@ -10977,13 +12514,18 @@
           <t>TALUSIA LS 40 BN40 (CAT.I)</t>
         </is>
       </c>
-      <c r="F307" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G307" s="4" t="inlineStr"/>
+      <c r="F307" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G307" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H307" s="4" t="inlineStr"/>
+      <c r="I307" s="4" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -11011,13 +12553,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F308" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G308" s="2" t="inlineStr"/>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G308" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H308" s="2" t="inlineStr"/>
+      <c r="I308" s="2" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
@@ -11045,13 +12592,18 @@
           <t>TALUSIA LS 40 BN40 (CAT.I)</t>
         </is>
       </c>
-      <c r="F309" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G309" s="4" t="inlineStr"/>
+      <c r="F309" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G309" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H309" s="4" t="inlineStr"/>
+      <c r="I309" s="4" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -11079,13 +12631,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F310" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G310" s="2" t="inlineStr"/>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G310" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H310" s="2" t="inlineStr"/>
+      <c r="I310" s="2" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
@@ -11113,13 +12670,18 @@
           <t>TALUSIA HR 70 BN70 (CAT.I)</t>
         </is>
       </c>
-      <c r="F311" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G311" s="4" t="inlineStr"/>
+      <c r="F311" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G311" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H311" s="4" t="inlineStr"/>
+      <c r="I311" s="4" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -11147,13 +12709,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F312" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G312" s="2" t="inlineStr"/>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G312" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H312" s="2" t="inlineStr"/>
+      <c r="I312" s="2" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
@@ -11181,13 +12748,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F313" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G313" s="4" t="inlineStr"/>
+      <c r="F313" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G313" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H313" s="4" t="inlineStr"/>
+      <c r="I313" s="4" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -11215,13 +12787,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F314" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G314" s="2" t="inlineStr"/>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G314" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H314" s="2" t="inlineStr"/>
+      <c r="I314" s="2" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
@@ -11249,13 +12826,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F315" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G315" s="4" t="inlineStr"/>
+      <c r="F315" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G315" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H315" s="4" t="inlineStr"/>
+      <c r="I315" s="4" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -11283,13 +12865,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F316" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G316" s="2" t="inlineStr"/>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G316" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H316" s="2" t="inlineStr"/>
+      <c r="I316" s="2" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
@@ -11317,13 +12904,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F317" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G317" s="4" t="inlineStr"/>
+      <c r="F317" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G317" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H317" s="4" t="inlineStr"/>
+      <c r="I317" s="4" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -11351,13 +12943,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F318" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G318" s="2" t="inlineStr"/>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G318" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H318" s="2" t="inlineStr"/>
+      <c r="I318" s="2" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
@@ -11385,13 +12982,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F319" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G319" s="4" t="inlineStr"/>
+      <c r="F319" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G319" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H319" s="4" t="inlineStr"/>
+      <c r="I319" s="4" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -11419,13 +13021,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F320" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G320" s="2" t="inlineStr"/>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G320" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H320" s="2" t="inlineStr"/>
+      <c r="I320" s="2" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
@@ -11453,13 +13060,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F321" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G321" s="4" t="inlineStr"/>
+      <c r="F321" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G321" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H321" s="4" t="inlineStr"/>
+      <c r="I321" s="4" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -11487,13 +13099,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F322" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G322" s="2" t="inlineStr"/>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G322" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H322" s="2" t="inlineStr"/>
+      <c r="I322" s="2" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
@@ -11521,13 +13138,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F323" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G323" s="4" t="inlineStr"/>
+      <c r="F323" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G323" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H323" s="4" t="inlineStr"/>
+      <c r="I323" s="4" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -11555,13 +13177,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F324" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G324" s="2" t="inlineStr"/>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G324" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H324" s="2" t="inlineStr"/>
+      <c r="I324" s="2" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
@@ -11589,13 +13216,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F325" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G325" s="4" t="inlineStr"/>
+      <c r="F325" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G325" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H325" s="4" t="inlineStr"/>
+      <c r="I325" s="4" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -11623,13 +13255,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F326" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G326" s="2" t="inlineStr"/>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G326" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H326" s="2" t="inlineStr"/>
+      <c r="I326" s="2" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
@@ -11657,13 +13294,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F327" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G327" s="4" t="inlineStr"/>
+      <c r="F327" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G327" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H327" s="4" t="inlineStr"/>
+      <c r="I327" s="4" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -11691,13 +13333,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F328" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G328" s="2" t="inlineStr"/>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G328" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H328" s="2" t="inlineStr"/>
+      <c r="I328" s="2" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
@@ -11725,13 +13372,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F329" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G329" s="4" t="inlineStr"/>
+      <c r="F329" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G329" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H329" s="4" t="inlineStr"/>
+      <c r="I329" s="4" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -11759,13 +13411,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F330" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G330" s="2" t="inlineStr"/>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G330" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H330" s="2" t="inlineStr"/>
+      <c r="I330" s="2" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
@@ -11793,13 +13450,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F331" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G331" s="4" t="inlineStr"/>
+      <c r="F331" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G331" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H331" s="4" t="inlineStr"/>
+      <c r="I331" s="4" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -11827,13 +13489,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F332" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G332" s="2" t="inlineStr"/>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G332" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H332" s="2" t="inlineStr"/>
+      <c r="I332" s="2" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
@@ -11861,13 +13528,18 @@
           <t>TALUSIA HD 40 BN40 (CAT.II)</t>
         </is>
       </c>
-      <c r="F333" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G333" s="4" t="inlineStr"/>
+      <c r="F333" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G333" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H333" s="4" t="inlineStr"/>
+      <c r="I333" s="4" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -11895,13 +13567,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100 (CAT.II)</t>
         </is>
       </c>
-      <c r="F334" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G334" s="2" t="inlineStr"/>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G334" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H334" s="2" t="inlineStr"/>
+      <c r="I334" s="2" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
@@ -11929,13 +13606,18 @@
           <t>TALUSIA HR 140 BN140 (CAT.II)</t>
         </is>
       </c>
-      <c r="F335" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G335" s="4" t="inlineStr"/>
+      <c r="F335" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G335" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H335" s="4" t="inlineStr"/>
+      <c r="I335" s="4" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -11963,13 +13645,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F336" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G336" s="2" t="inlineStr"/>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G336" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H336" s="2" t="inlineStr"/>
+      <c r="I336" s="2" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
@@ -11997,13 +13684,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F337" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G337" s="4" t="inlineStr"/>
+      <c r="F337" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G337" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H337" s="4" t="inlineStr"/>
+      <c r="I337" s="4" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -12031,13 +13723,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F338" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G338" s="2" t="inlineStr"/>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G338" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H338" s="2" t="inlineStr"/>
+      <c r="I338" s="2" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
@@ -12065,13 +13762,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100</t>
         </is>
       </c>
-      <c r="F339" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G339" s="4" t="inlineStr"/>
+      <c r="F339" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G339" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H339" s="4" t="inlineStr"/>
+      <c r="I339" s="4" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -12099,13 +13801,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100</t>
         </is>
       </c>
-      <c r="F340" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G340" s="2" t="inlineStr"/>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G340" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H340" s="2" t="inlineStr"/>
+      <c r="I340" s="2" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
@@ -12133,13 +13840,18 @@
           <t>ATLANTA MARINE D 3005 BN5</t>
         </is>
       </c>
-      <c r="F341" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G341" s="4" t="inlineStr"/>
+      <c r="F341" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G341" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H341" s="4" t="inlineStr"/>
+      <c r="I341" s="4" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -12167,13 +13879,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F342" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G342" s="2" t="inlineStr"/>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G342" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H342" s="2" t="inlineStr"/>
+      <c r="I342" s="2" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
@@ -12201,13 +13918,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F343" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G343" s="4" t="inlineStr"/>
+      <c r="F343" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G343" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H343" s="4" t="inlineStr"/>
+      <c r="I343" s="4" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -12235,13 +13957,18 @@
           <t>TALUSIA UNIVERSAL BN57</t>
         </is>
       </c>
-      <c r="F344" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G344" s="2" t="inlineStr"/>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G344" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H344" s="2" t="inlineStr"/>
+      <c r="I344" s="2" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
@@ -12269,13 +13996,18 @@
           <t>TALUSIA LS 40 BN40</t>
         </is>
       </c>
-      <c r="F345" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G345" s="4" t="inlineStr"/>
+      <c r="F345" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G345" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H345" s="4" t="inlineStr"/>
+      <c r="I345" s="4" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -12303,13 +14035,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F346" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G346" s="2" t="inlineStr"/>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G346" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H346" s="2" t="inlineStr"/>
+      <c r="I346" s="2" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
@@ -12337,13 +14074,18 @@
           <t>TALUSIA UNIVERSAL BN57</t>
         </is>
       </c>
-      <c r="F347" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G347" s="4" t="inlineStr"/>
+      <c r="F347" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G347" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H347" s="4" t="inlineStr"/>
+      <c r="I347" s="4" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -12371,13 +14113,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F348" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G348" s="2" t="inlineStr"/>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G348" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H348" s="2" t="inlineStr"/>
+      <c r="I348" s="2" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
@@ -12405,13 +14152,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100</t>
         </is>
       </c>
-      <c r="F349" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G349" s="4" t="inlineStr"/>
+      <c r="F349" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G349" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H349" s="4" t="inlineStr"/>
+      <c r="I349" s="4" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -12439,13 +14191,18 @@
           <t>TALUSIA HR 70 BN70</t>
         </is>
       </c>
-      <c r="F350" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G350" s="2" t="inlineStr"/>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G350" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H350" s="2" t="inlineStr"/>
+      <c r="I350" s="2" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
@@ -12473,13 +14230,18 @@
           <t>TALUSIA UNIVERSAL 100 BN100</t>
         </is>
       </c>
-      <c r="F351" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G351" s="4" t="inlineStr"/>
+      <c r="F351" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G351" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H351" s="4" t="inlineStr"/>
+      <c r="I351" s="4" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -12507,13 +14269,18 @@
           <t>ATLANTA MARINE D 3005 BN5</t>
         </is>
       </c>
-      <c r="F352" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G352" s="2" t="inlineStr"/>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G352" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H352" s="2" t="inlineStr"/>
+      <c r="I352" s="2" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
@@ -12541,13 +14308,18 @@
           <t>CAT. II BN 40 SAE 50</t>
         </is>
       </c>
-      <c r="F353" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G353" s="4" t="inlineStr"/>
+      <c r="F353" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G353" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H353" s="4" t="inlineStr"/>
+      <c r="I353" s="4" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -12575,13 +14347,18 @@
           <t>CAT. II BN 100-140+</t>
         </is>
       </c>
-      <c r="F354" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G354" s="2" t="inlineStr"/>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G354" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H354" s="2" t="inlineStr"/>
+      <c r="I354" s="2" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
@@ -12609,13 +14386,18 @@
           <t>CAT. I OR CAT. II BN 40 SAE 50</t>
         </is>
       </c>
-      <c r="F355" s="5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G355" s="4" t="inlineStr"/>
+      <c r="F355" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G355" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H355" s="4" t="inlineStr"/>
+      <c r="I355" s="4" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -12643,13 +14425,18 @@
           <t>CAT. I BN 70 OR CAT. II BN 100-140+</t>
         </is>
       </c>
-      <c r="F356" s="3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="G356" s="2" t="inlineStr"/>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G356" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
       <c r="H356" s="2" t="inlineStr"/>
+      <c r="I356" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/oem_master.xlsx
+++ b/output/oem_master.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="manual_data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="manual_data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,82 +459,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Maker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Model / Type</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Part to be lubricated</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Lubricant</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>source_file</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>source_sheet</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I356"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
@@ -14438,6 +14365,123 @@
       <c r="H356" s="2" t="inlineStr"/>
       <c r="I356" s="2" t="inlineStr"/>
     </row>
+    <row r="357">
+      <c r="A357" s="4" t="inlineStr">
+        <is>
+          <t>DIESEL GENERATOR ENGINE</t>
+        </is>
+      </c>
+      <c r="B357" s="4" t="inlineStr">
+        <is>
+          <t>HIMSEN</t>
+        </is>
+      </c>
+      <c r="C357" s="4" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D357" s="4" t="inlineStr">
+        <is>
+          <t>CYLINDERS &amp; CRANKCASE (LNG)</t>
+        </is>
+      </c>
+      <c r="E357" s="4" t="inlineStr">
+        <is>
+          <t>AURELIA NGX 40</t>
+        </is>
+      </c>
+      <c r="F357" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G357" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="H357" s="4" t="inlineStr"/>
+      <c r="I357" s="4" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>DIESEL GENERATOR ENGINE</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>WARTSILA</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>CYLINDERS &amp; CRANKCASE (LNG)</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>AURELIA NGX 40</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G358" s="3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="H358" s="2" t="inlineStr"/>
+      <c r="I358" s="2" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="4" t="inlineStr">
+        <is>
+          <t>DIESEL GENERATOR ENGINE</t>
+        </is>
+      </c>
+      <c r="B359" s="4" t="inlineStr">
+        <is>
+          <t>EVERLLENCE</t>
+        </is>
+      </c>
+      <c r="C359" s="4" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D359" s="4" t="inlineStr">
+        <is>
+          <t>CYLINDERS &amp; CRANKCASE (LNG)</t>
+        </is>
+      </c>
+      <c r="E359" s="4" t="inlineStr">
+        <is>
+          <t>AURELIA NGX 40</t>
+        </is>
+      </c>
+      <c r="F359" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G359" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="H359" s="4" t="inlineStr"/>
+      <c r="I359" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/oem_master.xlsx
+++ b/output/oem_master.xlsx
@@ -5452,7 +5452,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E213" s="4" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -8923,7 +8923,7 @@
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E217" s="4" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E219" s="4" t="inlineStr">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -9274,7 +9274,7 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E231" s="4" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E233" s="4" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E237" s="4" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E239" s="4" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E241" s="4" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E243" s="4" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E245" s="4" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="D247" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E247" s="4" t="inlineStr">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E251" s="4" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E253" s="4" t="inlineStr">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E255" s="4" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E257" s="4" t="inlineStr">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E259" s="4" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E261" s="4" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -10795,7 +10795,7 @@
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E265" s="4" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E267" s="4" t="inlineStr">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E269" s="4" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E271" s="4" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E273" s="4" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E275" s="4" t="inlineStr">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E277" s="4" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E279" s="4" t="inlineStr">
@@ -11380,7 +11380,7 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E283" s="4" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E285" s="4" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E287" s="4" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E289" s="4" t="inlineStr">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E291" s="4" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E293" s="4" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -11965,7 +11965,7 @@
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E295" s="4" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E297" s="4" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -12160,7 +12160,7 @@
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E301" s="4" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="D303" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E303" s="4" t="inlineStr">
@@ -12355,7 +12355,7 @@
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E305" s="4" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
@@ -12433,7 +12433,7 @@
       </c>
       <c r="D307" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E307" s="4" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E309" s="4" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E311" s="4" t="inlineStr">
@@ -12628,7 +12628,7 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E313" s="4" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E315" s="4" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E317" s="4" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E319" s="4" t="inlineStr">
@@ -12940,7 +12940,7 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
@@ -12979,7 +12979,7 @@
       </c>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E321" s="4" t="inlineStr">
@@ -13018,7 +13018,7 @@
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
@@ -13057,7 +13057,7 @@
       </c>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E323" s="4" t="inlineStr">
@@ -13135,7 +13135,7 @@
       </c>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E325" s="4" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
@@ -13213,7 +13213,7 @@
       </c>
       <c r="D327" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E327" s="4" t="inlineStr">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
@@ -13330,7 +13330,7 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
@@ -13369,7 +13369,7 @@
       </c>
       <c r="D331" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E331" s="4" t="inlineStr">
@@ -13408,7 +13408,7 @@
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (ULSFO)</t>
+          <t>CYLINDER (ULSFO)</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
@@ -13447,7 +13447,7 @@
       </c>
       <c r="D333" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (VLSFO)</t>
+          <t>CYLINDER (VLSFO)</t>
         </is>
       </c>
       <c r="E333" s="4" t="inlineStr">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
@@ -13525,7 +13525,7 @@
       </c>
       <c r="D335" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS (HSFO)</t>
+          <t>CYLINDER (HSFO)</t>
         </is>
       </c>
       <c r="E335" s="4" t="inlineStr">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="D357" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS &amp; CRANKCASE (LNG)</t>
+          <t>CYLINDER &amp; CRANKCASE (LNG)</t>
         </is>
       </c>
       <c r="E357" s="4" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>CYLINDERS &amp; CRANKCASE (LNG)</t>
+          <t>CYLINDER &amp; CRANKCASE (LNG)</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="D359" s="4" t="inlineStr">
         <is>
-          <t>CYLINDERS &amp; CRANKCASE (LNG)</t>
+          <t>CYLINDER &amp; CRANKCASE (LNG)</t>
         </is>
       </c>
       <c r="E359" s="4" t="inlineStr">

--- a/output/oem_master.xlsx
+++ b/output/oem_master.xlsx
@@ -22700,7 +22700,7 @@
       </c>
       <c r="D581" s="4" t="inlineStr">
         <is>
-          <t>Ambient Temperature         -20°C…+5°C</t>
+          <t>Ambient Temperature -20°C…+5°C</t>
         </is>
       </c>
       <c r="E581" s="4" t="inlineStr">
@@ -22739,7 +22739,7 @@
       </c>
       <c r="D582" s="2" t="inlineStr">
         <is>
-          <t>Ambient Temperature         5°C…40°C</t>
+          <t>Ambient Temperature 5°C…40°C</t>
         </is>
       </c>
       <c r="E582" s="2" t="inlineStr">
@@ -22778,7 +22778,7 @@
       </c>
       <c r="D583" s="4" t="inlineStr">
         <is>
-          <t>Ambient Temperature         30°C…65°C</t>
+          <t>Ambient Temperature 30°C…65°C</t>
         </is>
       </c>
       <c r="E583" s="4" t="inlineStr">
@@ -23517,8 +23517,7 @@
       </c>
       <c r="D604" s="2" t="inlineStr">
         <is>
-          <t>Ambient Temperature
- -20°C…10°C</t>
+          <t>Ambient Temperature -20°C…10°C</t>
         </is>
       </c>
       <c r="E604" s="2" t="inlineStr">
@@ -23557,8 +23556,7 @@
       </c>
       <c r="D605" s="4" t="inlineStr">
         <is>
-          <t>Ambient Temperature
- 10°C…50°C</t>
+          <t>Ambient Temperature 10°C…50°C</t>
         </is>
       </c>
       <c r="E605" s="4" t="inlineStr">
@@ -23597,8 +23595,7 @@
       </c>
       <c r="D606" s="2" t="inlineStr">
         <is>
-          <t>Ambient Temperature
- -20°C…10°C</t>
+          <t>Ambient Temperature -20°C…10°C</t>
         </is>
       </c>
       <c r="E606" s="2" t="inlineStr">
@@ -23637,8 +23634,7 @@
       </c>
       <c r="D607" s="4" t="inlineStr">
         <is>
-          <t>Ambient Temperature
- 10°C…50°C</t>
+          <t>Ambient Temperature 10°C…50°C</t>
         </is>
       </c>
       <c r="E607" s="4" t="inlineStr">
@@ -28701,7 +28697,7 @@
       <c r="C748" s="2" t="inlineStr"/>
       <c r="D748" s="2" t="inlineStr">
         <is>
-          <t>Initial Fill  - Viscosity 50/55cSt at 40°C</t>
+          <t>Initial Fill - Viscosity 50/55cSt at 40°C</t>
         </is>
       </c>
       <c r="E748" s="2" t="inlineStr">
@@ -28802,8 +28798,7 @@
       </c>
       <c r="D751" s="4" t="inlineStr">
         <is>
-          <t>Ambient Temperature
-0…15°C</t>
+          <t>Ambient Temperature 0…15°C</t>
         </is>
       </c>
       <c r="E751" s="4" t="inlineStr">
@@ -28842,8 +28837,7 @@
       </c>
       <c r="D752" s="2" t="inlineStr">
         <is>
-          <t>Ambient Temperature
-15…25°C</t>
+          <t>Ambient Temperature 15…25°C</t>
         </is>
       </c>
       <c r="E752" s="2" t="inlineStr">
@@ -28882,8 +28876,7 @@
       </c>
       <c r="D753" s="4" t="inlineStr">
         <is>
-          <t>Ambient Temperature
-25…35°C</t>
+          <t>Ambient Temperature 25…35°C</t>
         </is>
       </c>
       <c r="E753" s="4" t="inlineStr">
@@ -28922,8 +28915,7 @@
       </c>
       <c r="D754" s="2" t="inlineStr">
         <is>
-          <t>Ambient Temperature
-35…45°C</t>
+          <t>Ambient Temperature 35…45°C</t>
         </is>
       </c>
       <c r="E754" s="2" t="inlineStr">
@@ -32032,7 +32024,7 @@
       <c r="C841" s="4" t="inlineStr"/>
       <c r="D841" s="4" t="inlineStr">
         <is>
-          <t>Initial Fill  - Viscosity 50/55cSt at 40°C</t>
+          <t>Initial Fill - Viscosity 50/55cSt at 40°C</t>
         </is>
       </c>
       <c r="E841" s="4" t="inlineStr">
@@ -32451,7 +32443,7 @@
       </c>
       <c r="C853" s="4" t="inlineStr">
         <is>
-          <t>all types</t>
+          <t>all types-CFC</t>
         </is>
       </c>
       <c r="D853" s="4" t="inlineStr">
@@ -32490,7 +32482,7 @@
       </c>
       <c r="C854" s="2" t="inlineStr">
         <is>
-          <t>all types</t>
+          <t>all types-HCFC</t>
         </is>
       </c>
       <c r="D854" s="2" t="inlineStr">
@@ -32529,7 +32521,7 @@
       </c>
       <c r="C855" s="4" t="inlineStr">
         <is>
-          <t>all types</t>
+          <t>all types-HCFC</t>
         </is>
       </c>
       <c r="D855" s="4" t="inlineStr">
@@ -32568,7 +32560,7 @@
       </c>
       <c r="C856" s="2" t="inlineStr">
         <is>
-          <t>all types</t>
+          <t>all types-HCFC</t>
         </is>
       </c>
       <c r="D856" s="2" t="inlineStr">
@@ -32607,7 +32599,7 @@
       </c>
       <c r="C857" s="4" t="inlineStr">
         <is>
-          <t>all types</t>
+          <t>all types-HFC</t>
         </is>
       </c>
       <c r="D857" s="4" t="inlineStr">
@@ -32646,7 +32638,7 @@
       </c>
       <c r="C858" s="2" t="inlineStr">
         <is>
-          <t>all types</t>
+          <t>all types-R717 (NH3)</t>
         </is>
       </c>
       <c r="D858" s="2" t="inlineStr">
@@ -32685,7 +32677,7 @@
       </c>
       <c r="C859" s="4" t="inlineStr">
         <is>
-          <t>all types</t>
+          <t>all types-R717 (NH3)</t>
         </is>
       </c>
       <c r="D859" s="4" t="inlineStr">
@@ -32724,7 +32716,7 @@
       </c>
       <c r="C860" s="2" t="inlineStr">
         <is>
-          <t>all types</t>
+          <t>all types-R717 (NH3)</t>
         </is>
       </c>
       <c r="D860" s="2" t="inlineStr">
@@ -32763,7 +32755,7 @@
       </c>
       <c r="C861" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-HFC</t>
         </is>
       </c>
       <c r="D861" s="4" t="inlineStr"/>
@@ -32798,7 +32790,7 @@
       </c>
       <c r="C862" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B-HFC</t>
         </is>
       </c>
       <c r="D862" s="2" t="inlineStr"/>
@@ -32833,7 +32825,7 @@
       </c>
       <c r="C863" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-HFC</t>
         </is>
       </c>
       <c r="D863" s="4" t="inlineStr"/>
@@ -32868,7 +32860,7 @@
       </c>
       <c r="C864" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D-HFC</t>
         </is>
       </c>
       <c r="D864" s="2" t="inlineStr"/>
@@ -32903,7 +32895,7 @@
       </c>
       <c r="C865" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>F-HFC</t>
         </is>
       </c>
       <c r="D865" s="4" t="inlineStr"/>
@@ -32938,7 +32930,7 @@
       </c>
       <c r="C866" s="2" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>Q-HFC</t>
         </is>
       </c>
       <c r="D866" s="2" t="inlineStr"/>
@@ -32973,7 +32965,7 @@
       </c>
       <c r="C867" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-HFC</t>
         </is>
       </c>
       <c r="D867" s="4" t="inlineStr"/>
@@ -33008,7 +33000,7 @@
       </c>
       <c r="C868" s="2" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>V-HFC</t>
         </is>
       </c>
       <c r="D868" s="2" t="inlineStr"/>
@@ -33043,7 +33035,7 @@
       </c>
       <c r="C869" s="4" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>Z-HFC</t>
         </is>
       </c>
       <c r="D869" s="4" t="inlineStr"/>
@@ -33078,7 +33070,7 @@
       </c>
       <c r="C870" s="2" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W-HFC</t>
         </is>
       </c>
       <c r="D870" s="2" t="inlineStr"/>
@@ -33113,7 +33105,7 @@
       </c>
       <c r="C871" s="4" t="inlineStr">
         <is>
-          <t>all types</t>
+          <t>all types-HFC</t>
         </is>
       </c>
       <c r="D871" s="4" t="inlineStr"/>
@@ -33148,7 +33140,7 @@
       </c>
       <c r="C872" s="2" t="inlineStr">
         <is>
-          <t>all types</t>
+          <t>all types-HFC</t>
         </is>
       </c>
       <c r="D872" s="2" t="inlineStr"/>
@@ -33183,7 +33175,7 @@
       </c>
       <c r="C873" s="4" t="inlineStr">
         <is>
-          <t>Serie 6</t>
+          <t>Serie 6-R717 (NH3)</t>
         </is>
       </c>
       <c r="D873" s="4" t="inlineStr">
@@ -33222,7 +33214,7 @@
       </c>
       <c r="C874" s="2" t="inlineStr">
         <is>
-          <t>Serie 6</t>
+          <t>Serie 6-HCFC</t>
         </is>
       </c>
       <c r="D874" s="2" t="inlineStr">
@@ -33261,7 +33253,7 @@
       </c>
       <c r="C875" s="4" t="inlineStr">
         <is>
-          <t>Serie 6</t>
+          <t>Serie 6-HFC</t>
         </is>
       </c>
       <c r="D875" s="4" t="inlineStr">
@@ -33300,7 +33292,7 @@
       </c>
       <c r="C876" s="2" t="inlineStr">
         <is>
-          <t>Serie 10</t>
+          <t>Serie 10-R717 (NH3)</t>
         </is>
       </c>
       <c r="D876" s="2" t="inlineStr">
@@ -33339,7 +33331,7 @@
       </c>
       <c r="C877" s="4" t="inlineStr">
         <is>
-          <t>Serie 10</t>
+          <t>Serie 10-HCFC</t>
         </is>
       </c>
       <c r="D877" s="4" t="inlineStr">
@@ -33378,7 +33370,7 @@
       </c>
       <c r="C878" s="2" t="inlineStr">
         <is>
-          <t>Serie 10</t>
+          <t>Serie 10-HFC</t>
         </is>
       </c>
       <c r="D878" s="2" t="inlineStr">
@@ -33417,7 +33409,7 @@
       </c>
       <c r="C879" s="4" t="inlineStr">
         <is>
-          <t>Serie 12/12E</t>
+          <t>Serie 12/12E-R717 (NH3)</t>
         </is>
       </c>
       <c r="D879" s="4" t="inlineStr">
@@ -33456,7 +33448,7 @@
       </c>
       <c r="C880" s="2" t="inlineStr">
         <is>
-          <t>Serie 12/12E</t>
+          <t>Serie 12/12E-HCFC</t>
         </is>
       </c>
       <c r="D880" s="2" t="inlineStr">
@@ -33495,7 +33487,7 @@
       </c>
       <c r="C881" s="4" t="inlineStr">
         <is>
-          <t>Serie 12/12E</t>
+          <t>Serie 12/12E-HFC</t>
         </is>
       </c>
       <c r="D881" s="4" t="inlineStr">
@@ -33534,7 +33526,7 @@
       </c>
       <c r="C882" s="2" t="inlineStr">
         <is>
-          <t>all types</t>
+          <t>all types-R717 (NH3)</t>
         </is>
       </c>
       <c r="D882" s="2" t="inlineStr">
@@ -33573,7 +33565,7 @@
       </c>
       <c r="C883" s="4" t="inlineStr">
         <is>
-          <t>all types</t>
+          <t>all types-R717 (NH3)</t>
         </is>
       </c>
       <c r="D883" s="4" t="inlineStr">
@@ -33612,7 +33604,7 @@
       </c>
       <c r="C884" s="2" t="inlineStr">
         <is>
-          <t>all types</t>
+          <t>all types-R717 (NH3)</t>
         </is>
       </c>
       <c r="D884" s="2" t="inlineStr">
@@ -33651,7 +33643,7 @@
       </c>
       <c r="C885" s="4" t="inlineStr">
         <is>
-          <t>all types</t>
+          <t>all types-R22 (HCFC)</t>
         </is>
       </c>
       <c r="D885" s="4" t="inlineStr"/>
@@ -33686,7 +33678,7 @@
       </c>
       <c r="C886" s="2" t="inlineStr">
         <is>
-          <t>all types</t>
+          <t>all types-HFC</t>
         </is>
       </c>
       <c r="D886" s="2" t="inlineStr">
@@ -33725,7 +33717,7 @@
       </c>
       <c r="C887" s="4" t="inlineStr">
         <is>
-          <t>all types</t>
+          <t>all types-Natural Gas</t>
         </is>
       </c>
       <c r="D887" s="4" t="inlineStr"/>
@@ -33760,7 +33752,7 @@
       </c>
       <c r="C888" s="2" t="inlineStr">
         <is>
-          <t>XRV</t>
+          <t>XRV-HFC</t>
         </is>
       </c>
       <c r="D888" s="2" t="inlineStr">
@@ -33799,7 +33791,7 @@
       </c>
       <c r="C889" s="4" t="inlineStr">
         <is>
-          <t>XRV</t>
+          <t>XRV-R717 (NH3)</t>
         </is>
       </c>
       <c r="D889" s="4" t="inlineStr"/>
@@ -33834,7 +33826,7 @@
       </c>
       <c r="C890" s="2" t="inlineStr">
         <is>
-          <t>WRV</t>
+          <t>WRV-HFC</t>
         </is>
       </c>
       <c r="D890" s="2" t="inlineStr">
@@ -33873,7 +33865,7 @@
       </c>
       <c r="C891" s="4" t="inlineStr">
         <is>
-          <t>WRV</t>
+          <t>WRV-R717 (NH3)</t>
         </is>
       </c>
       <c r="D891" s="4" t="inlineStr"/>
@@ -33906,7 +33898,11 @@
           <t>York (Johnson Controls)</t>
         </is>
       </c>
-      <c r="C892" s="2" t="inlineStr"/>
+      <c r="C892" s="2" t="inlineStr">
+        <is>
+          <t>HFC</t>
+        </is>
+      </c>
       <c r="D892" s="2" t="inlineStr">
         <is>
           <t>Type and Grade chosen according to operating conditions</t>
@@ -33941,7 +33937,11 @@
           <t>York (Johnson Controls)</t>
         </is>
       </c>
-      <c r="C893" s="4" t="inlineStr"/>
+      <c r="C893" s="4" t="inlineStr">
+        <is>
+          <t>HFC</t>
+        </is>
+      </c>
       <c r="D893" s="4" t="inlineStr">
         <is>
           <t>Type and Grade chosen according to operating conditions</t>
@@ -36086,7 +36086,7 @@
       </c>
       <c r="C962" s="2" t="inlineStr">
         <is>
-          <t>BWPX</t>
+          <t>BWPX-307</t>
         </is>
       </c>
       <c r="D962" s="2" t="inlineStr"/>
@@ -36121,7 +36121,7 @@
       </c>
       <c r="C963" s="4" t="inlineStr">
         <is>
-          <t>BWPX</t>
+          <t>BWPX-307</t>
         </is>
       </c>
       <c r="D963" s="4" t="inlineStr"/>
@@ -36156,7 +36156,7 @@
       </c>
       <c r="C964" s="2" t="inlineStr">
         <is>
-          <t>BWPX</t>
+          <t>BWPX-307</t>
         </is>
       </c>
       <c r="D964" s="2" t="inlineStr"/>
@@ -36191,7 +36191,7 @@
       </c>
       <c r="C965" s="4" t="inlineStr">
         <is>
-          <t>BWPX</t>
+          <t>BWPX-307</t>
         </is>
       </c>
       <c r="D965" s="4" t="inlineStr"/>
@@ -36226,7 +36226,7 @@
       </c>
       <c r="C966" s="2" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-605</t>
         </is>
       </c>
       <c r="D966" s="2" t="inlineStr"/>
@@ -36261,7 +36261,7 @@
       </c>
       <c r="C967" s="4" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-605</t>
         </is>
       </c>
       <c r="D967" s="4" t="inlineStr"/>
@@ -36296,7 +36296,7 @@
       </c>
       <c r="C968" s="2" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-605</t>
         </is>
       </c>
       <c r="D968" s="2" t="inlineStr"/>
@@ -36331,7 +36331,7 @@
       </c>
       <c r="C969" s="4" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-605</t>
         </is>
       </c>
       <c r="D969" s="4" t="inlineStr"/>
@@ -36366,7 +36366,7 @@
       </c>
       <c r="C970" s="2" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-605</t>
         </is>
       </c>
       <c r="D970" s="2" t="inlineStr"/>
@@ -36401,7 +36401,7 @@
       </c>
       <c r="C971" s="4" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-607</t>
         </is>
       </c>
       <c r="D971" s="4" t="inlineStr"/>
@@ -36436,7 +36436,7 @@
       </c>
       <c r="C972" s="2" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-607</t>
         </is>
       </c>
       <c r="D972" s="2" t="inlineStr"/>
@@ -36471,7 +36471,7 @@
       </c>
       <c r="C973" s="4" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-607</t>
         </is>
       </c>
       <c r="D973" s="4" t="inlineStr"/>
@@ -36506,7 +36506,7 @@
       </c>
       <c r="C974" s="2" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-607</t>
         </is>
       </c>
       <c r="D974" s="2" t="inlineStr"/>
@@ -36541,7 +36541,7 @@
       </c>
       <c r="C975" s="4" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-607</t>
         </is>
       </c>
       <c r="D975" s="4" t="inlineStr"/>
@@ -36576,7 +36576,7 @@
       </c>
       <c r="C976" s="2" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-609</t>
         </is>
       </c>
       <c r="D976" s="2" t="inlineStr"/>
@@ -36611,7 +36611,7 @@
       </c>
       <c r="C977" s="4" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-609</t>
         </is>
       </c>
       <c r="D977" s="4" t="inlineStr"/>
@@ -36646,7 +36646,7 @@
       </c>
       <c r="C978" s="2" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-609</t>
         </is>
       </c>
       <c r="D978" s="2" t="inlineStr"/>
@@ -36681,7 +36681,7 @@
       </c>
       <c r="C979" s="4" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-609</t>
         </is>
       </c>
       <c r="D979" s="4" t="inlineStr"/>
@@ -36716,7 +36716,7 @@
       </c>
       <c r="C980" s="2" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-609</t>
         </is>
       </c>
       <c r="D980" s="2" t="inlineStr"/>
@@ -36751,7 +36751,7 @@
       </c>
       <c r="C981" s="4" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-610</t>
         </is>
       </c>
       <c r="D981" s="4" t="inlineStr"/>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="C982" s="2" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-610</t>
         </is>
       </c>
       <c r="D982" s="2" t="inlineStr"/>
@@ -36821,7 +36821,7 @@
       </c>
       <c r="C983" s="4" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-610</t>
         </is>
       </c>
       <c r="D983" s="4" t="inlineStr"/>
@@ -36856,7 +36856,7 @@
       </c>
       <c r="C984" s="2" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-610</t>
         </is>
       </c>
       <c r="D984" s="2" t="inlineStr"/>
@@ -36891,7 +36891,7 @@
       </c>
       <c r="C985" s="4" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-610</t>
         </is>
       </c>
       <c r="D985" s="4" t="inlineStr"/>
@@ -36926,7 +36926,7 @@
       </c>
       <c r="C986" s="2" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-611</t>
         </is>
       </c>
       <c r="D986" s="2" t="inlineStr"/>
@@ -36961,7 +36961,7 @@
       </c>
       <c r="C987" s="4" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-611</t>
         </is>
       </c>
       <c r="D987" s="4" t="inlineStr"/>
@@ -36996,7 +36996,7 @@
       </c>
       <c r="C988" s="2" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-611</t>
         </is>
       </c>
       <c r="D988" s="2" t="inlineStr"/>
@@ -37031,7 +37031,7 @@
       </c>
       <c r="C989" s="4" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-611</t>
         </is>
       </c>
       <c r="D989" s="4" t="inlineStr"/>
@@ -37066,7 +37066,7 @@
       </c>
       <c r="C990" s="2" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-611</t>
         </is>
       </c>
       <c r="D990" s="2" t="inlineStr"/>
@@ -37101,7 +37101,7 @@
       </c>
       <c r="C991" s="4" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-613</t>
         </is>
       </c>
       <c r="D991" s="4" t="inlineStr"/>
@@ -37136,7 +37136,7 @@
       </c>
       <c r="C992" s="2" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-613</t>
         </is>
       </c>
       <c r="D992" s="2" t="inlineStr"/>
@@ -37171,7 +37171,7 @@
       </c>
       <c r="C993" s="4" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-613</t>
         </is>
       </c>
       <c r="D993" s="4" t="inlineStr"/>
@@ -37206,7 +37206,7 @@
       </c>
       <c r="C994" s="2" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-613</t>
         </is>
       </c>
       <c r="D994" s="2" t="inlineStr"/>
@@ -37241,7 +37241,7 @@
       </c>
       <c r="C995" s="4" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-613</t>
         </is>
       </c>
       <c r="D995" s="4" t="inlineStr"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="C996" s="2" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-614</t>
         </is>
       </c>
       <c r="D996" s="2" t="inlineStr"/>
@@ -37311,7 +37311,7 @@
       </c>
       <c r="C997" s="4" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-614</t>
         </is>
       </c>
       <c r="D997" s="4" t="inlineStr"/>
@@ -37346,7 +37346,7 @@
       </c>
       <c r="C998" s="2" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-614</t>
         </is>
       </c>
       <c r="D998" s="2" t="inlineStr"/>
@@ -37381,7 +37381,7 @@
       </c>
       <c r="C999" s="4" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-614</t>
         </is>
       </c>
       <c r="D999" s="4" t="inlineStr"/>
@@ -37416,7 +37416,7 @@
       </c>
       <c r="C1000" s="2" t="inlineStr">
         <is>
-          <t>FOPX</t>
+          <t>FOPX-614</t>
         </is>
       </c>
       <c r="D1000" s="2" t="inlineStr"/>
@@ -37451,7 +37451,7 @@
       </c>
       <c r="C1001" s="4" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-705</t>
         </is>
       </c>
       <c r="D1001" s="4" t="inlineStr"/>
@@ -37486,7 +37486,7 @@
       </c>
       <c r="C1002" s="2" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-705</t>
         </is>
       </c>
       <c r="D1002" s="2" t="inlineStr"/>
@@ -37521,7 +37521,7 @@
       </c>
       <c r="C1003" s="4" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-705</t>
         </is>
       </c>
       <c r="D1003" s="4" t="inlineStr"/>
@@ -37556,7 +37556,7 @@
       </c>
       <c r="C1004" s="2" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-705</t>
         </is>
       </c>
       <c r="D1004" s="2" t="inlineStr"/>
@@ -37591,7 +37591,7 @@
       </c>
       <c r="C1005" s="4" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-705</t>
         </is>
       </c>
       <c r="D1005" s="4" t="inlineStr"/>
@@ -37626,7 +37626,7 @@
       </c>
       <c r="C1006" s="2" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-707</t>
         </is>
       </c>
       <c r="D1006" s="2" t="inlineStr"/>
@@ -37661,7 +37661,7 @@
       </c>
       <c r="C1007" s="4" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-707</t>
         </is>
       </c>
       <c r="D1007" s="4" t="inlineStr"/>
@@ -37696,7 +37696,7 @@
       </c>
       <c r="C1008" s="2" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-707</t>
         </is>
       </c>
       <c r="D1008" s="2" t="inlineStr"/>
@@ -37731,7 +37731,7 @@
       </c>
       <c r="C1009" s="4" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-707</t>
         </is>
       </c>
       <c r="D1009" s="4" t="inlineStr"/>
@@ -37766,7 +37766,7 @@
       </c>
       <c r="C1010" s="2" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-707</t>
         </is>
       </c>
       <c r="D1010" s="2" t="inlineStr"/>
@@ -37801,7 +37801,7 @@
       </c>
       <c r="C1011" s="4" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-709</t>
         </is>
       </c>
       <c r="D1011" s="4" t="inlineStr"/>
@@ -37836,7 +37836,7 @@
       </c>
       <c r="C1012" s="2" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-709</t>
         </is>
       </c>
       <c r="D1012" s="2" t="inlineStr"/>
@@ -37871,7 +37871,7 @@
       </c>
       <c r="C1013" s="4" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-709</t>
         </is>
       </c>
       <c r="D1013" s="4" t="inlineStr"/>
@@ -37906,7 +37906,7 @@
       </c>
       <c r="C1014" s="2" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-709</t>
         </is>
       </c>
       <c r="D1014" s="2" t="inlineStr"/>
@@ -37941,7 +37941,7 @@
       </c>
       <c r="C1015" s="4" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-709</t>
         </is>
       </c>
       <c r="D1015" s="4" t="inlineStr"/>
@@ -37976,7 +37976,7 @@
       </c>
       <c r="C1016" s="2" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-710</t>
         </is>
       </c>
       <c r="D1016" s="2" t="inlineStr"/>
@@ -38011,7 +38011,7 @@
       </c>
       <c r="C1017" s="4" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-710</t>
         </is>
       </c>
       <c r="D1017" s="4" t="inlineStr"/>
@@ -38046,7 +38046,7 @@
       </c>
       <c r="C1018" s="2" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-710</t>
         </is>
       </c>
       <c r="D1018" s="2" t="inlineStr"/>
@@ -38081,7 +38081,7 @@
       </c>
       <c r="C1019" s="4" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-710</t>
         </is>
       </c>
       <c r="D1019" s="4" t="inlineStr"/>
@@ -38116,7 +38116,7 @@
       </c>
       <c r="C1020" s="2" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-710</t>
         </is>
       </c>
       <c r="D1020" s="2" t="inlineStr"/>
@@ -38151,7 +38151,7 @@
       </c>
       <c r="C1021" s="4" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-711</t>
         </is>
       </c>
       <c r="D1021" s="4" t="inlineStr"/>
@@ -38186,7 +38186,7 @@
       </c>
       <c r="C1022" s="2" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-711</t>
         </is>
       </c>
       <c r="D1022" s="2" t="inlineStr"/>
@@ -38221,7 +38221,7 @@
       </c>
       <c r="C1023" s="4" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-711</t>
         </is>
       </c>
       <c r="D1023" s="4" t="inlineStr"/>
@@ -38256,7 +38256,7 @@
       </c>
       <c r="C1024" s="2" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-711</t>
         </is>
       </c>
       <c r="D1024" s="2" t="inlineStr"/>
@@ -38291,7 +38291,7 @@
       </c>
       <c r="C1025" s="4" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-711</t>
         </is>
       </c>
       <c r="D1025" s="4" t="inlineStr"/>
@@ -38326,7 +38326,7 @@
       </c>
       <c r="C1026" s="2" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-713</t>
         </is>
       </c>
       <c r="D1026" s="2" t="inlineStr"/>
@@ -38361,7 +38361,7 @@
       </c>
       <c r="C1027" s="4" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-713</t>
         </is>
       </c>
       <c r="D1027" s="4" t="inlineStr"/>
@@ -38396,7 +38396,7 @@
       </c>
       <c r="C1028" s="2" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-713</t>
         </is>
       </c>
       <c r="D1028" s="2" t="inlineStr"/>
@@ -38431,7 +38431,7 @@
       </c>
       <c r="C1029" s="4" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-713</t>
         </is>
       </c>
       <c r="D1029" s="4" t="inlineStr"/>
@@ -38466,7 +38466,7 @@
       </c>
       <c r="C1030" s="2" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-713</t>
         </is>
       </c>
       <c r="D1030" s="2" t="inlineStr"/>
@@ -38501,7 +38501,7 @@
       </c>
       <c r="C1031" s="4" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-714</t>
         </is>
       </c>
       <c r="D1031" s="4" t="inlineStr"/>
@@ -38536,7 +38536,7 @@
       </c>
       <c r="C1032" s="2" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-714</t>
         </is>
       </c>
       <c r="D1032" s="2" t="inlineStr"/>
@@ -38571,7 +38571,7 @@
       </c>
       <c r="C1033" s="4" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-714</t>
         </is>
       </c>
       <c r="D1033" s="4" t="inlineStr"/>
@@ -38606,7 +38606,7 @@
       </c>
       <c r="C1034" s="2" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-714</t>
         </is>
       </c>
       <c r="D1034" s="2" t="inlineStr"/>
@@ -38641,7 +38641,7 @@
       </c>
       <c r="C1035" s="4" t="inlineStr">
         <is>
-          <t>LOPX</t>
+          <t>LOPX-714</t>
         </is>
       </c>
       <c r="D1035" s="4" t="inlineStr"/>
@@ -38676,7 +38676,7 @@
       </c>
       <c r="C1036" s="2" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-102</t>
         </is>
       </c>
       <c r="D1036" s="2" t="inlineStr"/>
@@ -38711,7 +38711,7 @@
       </c>
       <c r="C1037" s="4" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-102</t>
         </is>
       </c>
       <c r="D1037" s="4" t="inlineStr"/>
@@ -38746,7 +38746,7 @@
       </c>
       <c r="C1038" s="2" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-102</t>
         </is>
       </c>
       <c r="D1038" s="2" t="inlineStr"/>
@@ -38781,7 +38781,7 @@
       </c>
       <c r="C1039" s="4" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-102</t>
         </is>
       </c>
       <c r="D1039" s="4" t="inlineStr"/>
@@ -38816,7 +38816,7 @@
       </c>
       <c r="C1040" s="2" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-102</t>
         </is>
       </c>
       <c r="D1040" s="2" t="inlineStr"/>
@@ -38851,7 +38851,7 @@
       </c>
       <c r="C1041" s="4" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-103</t>
         </is>
       </c>
       <c r="D1041" s="4" t="inlineStr"/>
@@ -38886,7 +38886,7 @@
       </c>
       <c r="C1042" s="2" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-103</t>
         </is>
       </c>
       <c r="D1042" s="2" t="inlineStr"/>
@@ -38921,7 +38921,7 @@
       </c>
       <c r="C1043" s="4" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-103</t>
         </is>
       </c>
       <c r="D1043" s="4" t="inlineStr"/>
@@ -38956,7 +38956,7 @@
       </c>
       <c r="C1044" s="2" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-103</t>
         </is>
       </c>
       <c r="D1044" s="2" t="inlineStr"/>
@@ -38991,7 +38991,7 @@
       </c>
       <c r="C1045" s="4" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-103</t>
         </is>
       </c>
       <c r="D1045" s="4" t="inlineStr"/>
@@ -39026,7 +39026,7 @@
       </c>
       <c r="C1046" s="2" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-104</t>
         </is>
       </c>
       <c r="D1046" s="2" t="inlineStr"/>
@@ -39061,7 +39061,7 @@
       </c>
       <c r="C1047" s="4" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-104</t>
         </is>
       </c>
       <c r="D1047" s="4" t="inlineStr"/>
@@ -39096,7 +39096,7 @@
       </c>
       <c r="C1048" s="2" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-104</t>
         </is>
       </c>
       <c r="D1048" s="2" t="inlineStr"/>
@@ -39131,7 +39131,7 @@
       </c>
       <c r="C1049" s="4" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-104</t>
         </is>
       </c>
       <c r="D1049" s="4" t="inlineStr"/>
@@ -39166,7 +39166,7 @@
       </c>
       <c r="C1050" s="2" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-104</t>
         </is>
       </c>
       <c r="D1050" s="2" t="inlineStr"/>
@@ -39201,7 +39201,7 @@
       </c>
       <c r="C1051" s="4" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-204</t>
         </is>
       </c>
       <c r="D1051" s="4" t="inlineStr"/>
@@ -39236,7 +39236,7 @@
       </c>
       <c r="C1052" s="2" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-204</t>
         </is>
       </c>
       <c r="D1052" s="2" t="inlineStr"/>
@@ -39271,7 +39271,7 @@
       </c>
       <c r="C1053" s="4" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-204</t>
         </is>
       </c>
       <c r="D1053" s="4" t="inlineStr"/>
@@ -39306,7 +39306,7 @@
       </c>
       <c r="C1054" s="2" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-204</t>
         </is>
       </c>
       <c r="D1054" s="2" t="inlineStr"/>
@@ -39341,7 +39341,7 @@
       </c>
       <c r="C1055" s="4" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-204</t>
         </is>
       </c>
       <c r="D1055" s="4" t="inlineStr"/>
@@ -39376,7 +39376,7 @@
       </c>
       <c r="C1056" s="2" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-205</t>
         </is>
       </c>
       <c r="D1056" s="2" t="inlineStr"/>
@@ -39411,7 +39411,7 @@
       </c>
       <c r="C1057" s="4" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-205</t>
         </is>
       </c>
       <c r="D1057" s="4" t="inlineStr"/>
@@ -39446,7 +39446,7 @@
       </c>
       <c r="C1058" s="2" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-205</t>
         </is>
       </c>
       <c r="D1058" s="2" t="inlineStr"/>
@@ -39481,7 +39481,7 @@
       </c>
       <c r="C1059" s="4" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-205</t>
         </is>
       </c>
       <c r="D1059" s="4" t="inlineStr"/>
@@ -39516,7 +39516,7 @@
       </c>
       <c r="C1060" s="2" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-205</t>
         </is>
       </c>
       <c r="D1060" s="2" t="inlineStr"/>
@@ -39551,7 +39551,7 @@
       </c>
       <c r="C1061" s="4" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-206</t>
         </is>
       </c>
       <c r="D1061" s="4" t="inlineStr"/>
@@ -39586,7 +39586,7 @@
       </c>
       <c r="C1062" s="2" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-206</t>
         </is>
       </c>
       <c r="D1062" s="2" t="inlineStr"/>
@@ -39621,7 +39621,7 @@
       </c>
       <c r="C1063" s="4" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-206</t>
         </is>
       </c>
       <c r="D1063" s="4" t="inlineStr"/>
@@ -39656,7 +39656,7 @@
       </c>
       <c r="C1064" s="2" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-206</t>
         </is>
       </c>
       <c r="D1064" s="2" t="inlineStr"/>
@@ -39691,7 +39691,7 @@
       </c>
       <c r="C1065" s="4" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-206</t>
         </is>
       </c>
       <c r="D1065" s="4" t="inlineStr"/>
@@ -39726,7 +39726,7 @@
       </c>
       <c r="C1066" s="2" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-207</t>
         </is>
       </c>
       <c r="D1066" s="2" t="inlineStr"/>
@@ -39761,7 +39761,7 @@
       </c>
       <c r="C1067" s="4" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-207</t>
         </is>
       </c>
       <c r="D1067" s="4" t="inlineStr"/>
@@ -39796,7 +39796,7 @@
       </c>
       <c r="C1068" s="2" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-207</t>
         </is>
       </c>
       <c r="D1068" s="2" t="inlineStr"/>
@@ -39831,7 +39831,7 @@
       </c>
       <c r="C1069" s="4" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-207</t>
         </is>
       </c>
       <c r="D1069" s="4" t="inlineStr"/>
@@ -39866,7 +39866,7 @@
       </c>
       <c r="C1070" s="2" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-207</t>
         </is>
       </c>
       <c r="D1070" s="2" t="inlineStr"/>
@@ -39901,7 +39901,7 @@
       </c>
       <c r="C1071" s="4" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-209</t>
         </is>
       </c>
       <c r="D1071" s="4" t="inlineStr"/>
@@ -39936,7 +39936,7 @@
       </c>
       <c r="C1072" s="2" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-209</t>
         </is>
       </c>
       <c r="D1072" s="2" t="inlineStr"/>
@@ -39971,7 +39971,7 @@
       </c>
       <c r="C1073" s="4" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-209</t>
         </is>
       </c>
       <c r="D1073" s="4" t="inlineStr"/>
@@ -40006,7 +40006,7 @@
       </c>
       <c r="C1074" s="2" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-209</t>
         </is>
       </c>
       <c r="D1074" s="2" t="inlineStr"/>
@@ -40041,7 +40041,7 @@
       </c>
       <c r="C1075" s="4" t="inlineStr">
         <is>
-          <t>MAB</t>
+          <t>MAB-209</t>
         </is>
       </c>
       <c r="D1075" s="4" t="inlineStr"/>
@@ -40076,7 +40076,7 @@
       </c>
       <c r="C1076" s="2" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-204</t>
         </is>
       </c>
       <c r="D1076" s="2" t="inlineStr"/>
@@ -40111,7 +40111,7 @@
       </c>
       <c r="C1077" s="4" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-204</t>
         </is>
       </c>
       <c r="D1077" s="4" t="inlineStr"/>
@@ -40146,7 +40146,7 @@
       </c>
       <c r="C1078" s="2" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-204</t>
         </is>
       </c>
       <c r="D1078" s="2" t="inlineStr"/>
@@ -40181,7 +40181,7 @@
       </c>
       <c r="C1079" s="4" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-204</t>
         </is>
       </c>
       <c r="D1079" s="4" t="inlineStr"/>
@@ -40216,7 +40216,7 @@
       </c>
       <c r="C1080" s="2" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-204</t>
         </is>
       </c>
       <c r="D1080" s="2" t="inlineStr"/>
@@ -40251,7 +40251,7 @@
       </c>
       <c r="C1081" s="4" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-205</t>
         </is>
       </c>
       <c r="D1081" s="4" t="inlineStr"/>
@@ -40286,7 +40286,7 @@
       </c>
       <c r="C1082" s="2" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-205</t>
         </is>
       </c>
       <c r="D1082" s="2" t="inlineStr"/>
@@ -40321,7 +40321,7 @@
       </c>
       <c r="C1083" s="4" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-205</t>
         </is>
       </c>
       <c r="D1083" s="4" t="inlineStr"/>
@@ -40356,7 +40356,7 @@
       </c>
       <c r="C1084" s="2" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-205</t>
         </is>
       </c>
       <c r="D1084" s="2" t="inlineStr"/>
@@ -40391,7 +40391,7 @@
       </c>
       <c r="C1085" s="4" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-205</t>
         </is>
       </c>
       <c r="D1085" s="4" t="inlineStr"/>
@@ -40426,7 +40426,7 @@
       </c>
       <c r="C1086" s="2" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-207</t>
         </is>
       </c>
       <c r="D1086" s="2" t="inlineStr"/>
@@ -40461,7 +40461,7 @@
       </c>
       <c r="C1087" s="4" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-207</t>
         </is>
       </c>
       <c r="D1087" s="4" t="inlineStr"/>
@@ -40496,7 +40496,7 @@
       </c>
       <c r="C1088" s="2" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-207</t>
         </is>
       </c>
       <c r="D1088" s="2" t="inlineStr"/>
@@ -40531,7 +40531,7 @@
       </c>
       <c r="C1089" s="4" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-210</t>
         </is>
       </c>
       <c r="D1089" s="4" t="inlineStr"/>
@@ -40566,7 +40566,7 @@
       </c>
       <c r="C1090" s="2" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-210</t>
         </is>
       </c>
       <c r="D1090" s="2" t="inlineStr"/>
@@ -40601,7 +40601,7 @@
       </c>
       <c r="C1091" s="4" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-210</t>
         </is>
       </c>
       <c r="D1091" s="4" t="inlineStr"/>
@@ -40636,7 +40636,7 @@
       </c>
       <c r="C1092" s="2" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-210</t>
         </is>
       </c>
       <c r="D1092" s="2" t="inlineStr"/>
@@ -40671,7 +40671,7 @@
       </c>
       <c r="C1093" s="4" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-210</t>
         </is>
       </c>
       <c r="D1093" s="4" t="inlineStr"/>
@@ -40706,7 +40706,7 @@
       </c>
       <c r="C1094" s="2" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-309</t>
         </is>
       </c>
       <c r="D1094" s="2" t="inlineStr"/>
@@ -40741,7 +40741,7 @@
       </c>
       <c r="C1095" s="4" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-309</t>
         </is>
       </c>
       <c r="D1095" s="4" t="inlineStr"/>
@@ -40776,7 +40776,7 @@
       </c>
       <c r="C1096" s="2" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-309</t>
         </is>
       </c>
       <c r="D1096" s="2" t="inlineStr"/>
@@ -40811,7 +40811,7 @@
       </c>
       <c r="C1097" s="4" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-309</t>
         </is>
       </c>
       <c r="D1097" s="4" t="inlineStr"/>
@@ -40846,7 +40846,7 @@
       </c>
       <c r="C1098" s="2" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-309</t>
         </is>
       </c>
       <c r="D1098" s="2" t="inlineStr"/>
@@ -40881,7 +40881,7 @@
       </c>
       <c r="C1099" s="4" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-313</t>
         </is>
       </c>
       <c r="D1099" s="4" t="inlineStr"/>
@@ -40916,7 +40916,7 @@
       </c>
       <c r="C1100" s="2" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-313</t>
         </is>
       </c>
       <c r="D1100" s="2" t="inlineStr"/>
@@ -40951,7 +40951,7 @@
       </c>
       <c r="C1101" s="4" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-313</t>
         </is>
       </c>
       <c r="D1101" s="4" t="inlineStr"/>
@@ -40986,7 +40986,7 @@
       </c>
       <c r="C1102" s="2" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-313</t>
         </is>
       </c>
       <c r="D1102" s="2" t="inlineStr"/>
@@ -41021,7 +41021,7 @@
       </c>
       <c r="C1103" s="4" t="inlineStr">
         <is>
-          <t>MAPX</t>
+          <t>MAPX-313</t>
         </is>
       </c>
       <c r="D1103" s="4" t="inlineStr"/>
@@ -41056,7 +41056,7 @@
       </c>
       <c r="C1104" s="2" t="inlineStr">
         <is>
-          <t>MFPX</t>
+          <t>MFPX-307</t>
         </is>
       </c>
       <c r="D1104" s="2" t="inlineStr"/>
@@ -41091,7 +41091,7 @@
       </c>
       <c r="C1105" s="4" t="inlineStr">
         <is>
-          <t>MFPX</t>
+          <t>MFPX-307</t>
         </is>
       </c>
       <c r="D1105" s="4" t="inlineStr"/>
@@ -41126,7 +41126,7 @@
       </c>
       <c r="C1106" s="2" t="inlineStr">
         <is>
-          <t>MFPX</t>
+          <t>MFPX-307</t>
         </is>
       </c>
       <c r="D1106" s="2" t="inlineStr"/>
@@ -41161,7 +41161,7 @@
       </c>
       <c r="C1107" s="4" t="inlineStr">
         <is>
-          <t>MFPX</t>
+          <t>MFPX-307</t>
         </is>
       </c>
       <c r="D1107" s="4" t="inlineStr"/>
@@ -41196,7 +41196,7 @@
       </c>
       <c r="C1108" s="2" t="inlineStr">
         <is>
-          <t>MMB</t>
+          <t>MMB-304</t>
         </is>
       </c>
       <c r="D1108" s="2" t="inlineStr"/>
@@ -41231,7 +41231,7 @@
       </c>
       <c r="C1109" s="4" t="inlineStr">
         <is>
-          <t>MMB</t>
+          <t>MMB-304</t>
         </is>
       </c>
       <c r="D1109" s="4" t="inlineStr"/>
@@ -41266,7 +41266,7 @@
       </c>
       <c r="C1110" s="2" t="inlineStr">
         <is>
-          <t>MMB</t>
+          <t>MMB-304</t>
         </is>
       </c>
       <c r="D1110" s="2" t="inlineStr"/>
@@ -41301,7 +41301,7 @@
       </c>
       <c r="C1111" s="4" t="inlineStr">
         <is>
-          <t>MMB</t>
+          <t>MMB-304</t>
         </is>
       </c>
       <c r="D1111" s="4" t="inlineStr"/>
@@ -41336,7 +41336,7 @@
       </c>
       <c r="C1112" s="2" t="inlineStr">
         <is>
-          <t>MMB</t>
+          <t>MMB-305</t>
         </is>
       </c>
       <c r="D1112" s="2" t="inlineStr"/>
@@ -41371,7 +41371,7 @@
       </c>
       <c r="C1113" s="4" t="inlineStr">
         <is>
-          <t>MMB</t>
+          <t>MMB-305</t>
         </is>
       </c>
       <c r="D1113" s="4" t="inlineStr"/>
@@ -41406,7 +41406,7 @@
       </c>
       <c r="C1114" s="2" t="inlineStr">
         <is>
-          <t>MMB</t>
+          <t>MMB-305</t>
         </is>
       </c>
       <c r="D1114" s="2" t="inlineStr"/>
@@ -41441,7 +41441,7 @@
       </c>
       <c r="C1115" s="4" t="inlineStr">
         <is>
-          <t>MMB</t>
+          <t>MMB-305</t>
         </is>
       </c>
       <c r="D1115" s="4" t="inlineStr"/>
@@ -41476,7 +41476,7 @@
       </c>
       <c r="C1116" s="2" t="inlineStr">
         <is>
-          <t>MMPX</t>
+          <t>MMPX-303</t>
         </is>
       </c>
       <c r="D1116" s="2" t="inlineStr"/>
@@ -41511,7 +41511,7 @@
       </c>
       <c r="C1117" s="4" t="inlineStr">
         <is>
-          <t>MMPX</t>
+          <t>MMPX-303</t>
         </is>
       </c>
       <c r="D1117" s="4" t="inlineStr"/>
@@ -41546,7 +41546,7 @@
       </c>
       <c r="C1118" s="2" t="inlineStr">
         <is>
-          <t>MMPX</t>
+          <t>MMPX-303</t>
         </is>
       </c>
       <c r="D1118" s="2" t="inlineStr"/>
@@ -41581,7 +41581,7 @@
       </c>
       <c r="C1119" s="4" t="inlineStr">
         <is>
-          <t>MMPX</t>
+          <t>MMPX-303</t>
         </is>
       </c>
       <c r="D1119" s="4" t="inlineStr"/>
@@ -41616,7 +41616,7 @@
       </c>
       <c r="C1120" s="2" t="inlineStr">
         <is>
-          <t>MMPX</t>
+          <t>MMPX-304</t>
         </is>
       </c>
       <c r="D1120" s="2" t="inlineStr"/>
@@ -41651,7 +41651,7 @@
       </c>
       <c r="C1121" s="4" t="inlineStr">
         <is>
-          <t>MMPX</t>
+          <t>MMPX-304</t>
         </is>
       </c>
       <c r="D1121" s="4" t="inlineStr"/>
@@ -41686,7 +41686,7 @@
       </c>
       <c r="C1122" s="2" t="inlineStr">
         <is>
-          <t>MMPX</t>
+          <t>MMPX-304</t>
         </is>
       </c>
       <c r="D1122" s="2" t="inlineStr"/>
@@ -41721,7 +41721,7 @@
       </c>
       <c r="C1123" s="4" t="inlineStr">
         <is>
-          <t>MMPX</t>
+          <t>MMPX-304</t>
         </is>
       </c>
       <c r="D1123" s="4" t="inlineStr"/>
@@ -41756,7 +41756,7 @@
       </c>
       <c r="C1124" s="2" t="inlineStr">
         <is>
-          <t>MMPX</t>
+          <t>MMPX-403</t>
         </is>
       </c>
       <c r="D1124" s="2" t="inlineStr"/>
@@ -41791,7 +41791,7 @@
       </c>
       <c r="C1125" s="4" t="inlineStr">
         <is>
-          <t>MMPX</t>
+          <t>MMPX-403</t>
         </is>
       </c>
       <c r="D1125" s="4" t="inlineStr"/>
@@ -41826,7 +41826,7 @@
       </c>
       <c r="C1126" s="2" t="inlineStr">
         <is>
-          <t>MMPX</t>
+          <t>MMPX-403</t>
         </is>
       </c>
       <c r="D1126" s="2" t="inlineStr"/>
@@ -41861,7 +41861,7 @@
       </c>
       <c r="C1127" s="4" t="inlineStr">
         <is>
-          <t>MMPX</t>
+          <t>MMPX-403</t>
         </is>
       </c>
       <c r="D1127" s="4" t="inlineStr"/>
@@ -41896,7 +41896,7 @@
       </c>
       <c r="C1128" s="2" t="inlineStr">
         <is>
-          <t>MMPX</t>
+          <t>MMPX-404</t>
         </is>
       </c>
       <c r="D1128" s="2" t="inlineStr"/>
@@ -41931,7 +41931,7 @@
       </c>
       <c r="C1129" s="4" t="inlineStr">
         <is>
-          <t>MMPX</t>
+          <t>MMPX-404</t>
         </is>
       </c>
       <c r="D1129" s="4" t="inlineStr"/>
@@ -41966,7 +41966,7 @@
       </c>
       <c r="C1130" s="2" t="inlineStr">
         <is>
-          <t>MMPX</t>
+          <t>MMPX-404</t>
         </is>
       </c>
       <c r="D1130" s="2" t="inlineStr"/>
@@ -42001,7 +42001,7 @@
       </c>
       <c r="C1131" s="4" t="inlineStr">
         <is>
-          <t>MMPX</t>
+          <t>MMPX-404</t>
         </is>
       </c>
       <c r="D1131" s="4" t="inlineStr"/>
@@ -42036,7 +42036,7 @@
       </c>
       <c r="C1132" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-204</t>
         </is>
       </c>
       <c r="D1132" s="2" t="inlineStr"/>
@@ -42071,7 +42071,7 @@
       </c>
       <c r="C1133" s="4" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-204</t>
         </is>
       </c>
       <c r="D1133" s="4" t="inlineStr"/>
@@ -42106,7 +42106,7 @@
       </c>
       <c r="C1134" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-204</t>
         </is>
       </c>
       <c r="D1134" s="2" t="inlineStr"/>
@@ -42141,7 +42141,7 @@
       </c>
       <c r="C1135" s="4" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-204</t>
         </is>
       </c>
       <c r="D1135" s="4" t="inlineStr"/>
@@ -42176,7 +42176,7 @@
       </c>
       <c r="C1136" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-204</t>
         </is>
       </c>
       <c r="D1136" s="2" t="inlineStr"/>
@@ -42211,7 +42211,7 @@
       </c>
       <c r="C1137" s="4" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-205</t>
         </is>
       </c>
       <c r="D1137" s="4" t="inlineStr"/>
@@ -42246,7 +42246,7 @@
       </c>
       <c r="C1138" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-205</t>
         </is>
       </c>
       <c r="D1138" s="2" t="inlineStr"/>
@@ -42281,7 +42281,7 @@
       </c>
       <c r="C1139" s="4" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-205</t>
         </is>
       </c>
       <c r="D1139" s="4" t="inlineStr"/>
@@ -42316,7 +42316,7 @@
       </c>
       <c r="C1140" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-205</t>
         </is>
       </c>
       <c r="D1140" s="2" t="inlineStr"/>
@@ -42351,7 +42351,7 @@
       </c>
       <c r="C1141" s="4" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-205</t>
         </is>
       </c>
       <c r="D1141" s="4" t="inlineStr"/>
@@ -42386,7 +42386,7 @@
       </c>
       <c r="C1142" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-207</t>
         </is>
       </c>
       <c r="D1142" s="2" t="inlineStr"/>
@@ -42421,7 +42421,7 @@
       </c>
       <c r="C1143" s="4" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-207</t>
         </is>
       </c>
       <c r="D1143" s="4" t="inlineStr"/>
@@ -42456,7 +42456,7 @@
       </c>
       <c r="C1144" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-207</t>
         </is>
       </c>
       <c r="D1144" s="2" t="inlineStr"/>
@@ -42491,7 +42491,7 @@
       </c>
       <c r="C1145" s="4" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-209</t>
         </is>
       </c>
       <c r="D1145" s="4" t="inlineStr"/>
@@ -42526,7 +42526,7 @@
       </c>
       <c r="C1146" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-209</t>
         </is>
       </c>
       <c r="D1146" s="2" t="inlineStr"/>
@@ -42561,7 +42561,7 @@
       </c>
       <c r="C1147" s="4" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-209</t>
         </is>
       </c>
       <c r="D1147" s="4" t="inlineStr"/>
@@ -42596,7 +42596,7 @@
       </c>
       <c r="C1148" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-209</t>
         </is>
       </c>
       <c r="D1148" s="2" t="inlineStr"/>
@@ -42631,7 +42631,7 @@
       </c>
       <c r="C1149" s="4" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-209</t>
         </is>
       </c>
       <c r="D1149" s="4" t="inlineStr"/>
@@ -42666,7 +42666,7 @@
       </c>
       <c r="C1150" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-210</t>
         </is>
       </c>
       <c r="D1150" s="2" t="inlineStr"/>
@@ -42701,7 +42701,7 @@
       </c>
       <c r="C1151" s="4" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-210</t>
         </is>
       </c>
       <c r="D1151" s="4" t="inlineStr"/>
@@ -42736,7 +42736,7 @@
       </c>
       <c r="C1152" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-210</t>
         </is>
       </c>
       <c r="D1152" s="2" t="inlineStr"/>
@@ -42771,7 +42771,7 @@
       </c>
       <c r="C1153" s="4" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-210</t>
         </is>
       </c>
       <c r="D1153" s="4" t="inlineStr"/>
@@ -42806,7 +42806,7 @@
       </c>
       <c r="C1154" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-210</t>
         </is>
       </c>
       <c r="D1154" s="2" t="inlineStr"/>
@@ -42841,7 +42841,7 @@
       </c>
       <c r="C1155" s="4" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-213</t>
         </is>
       </c>
       <c r="D1155" s="4" t="inlineStr"/>
@@ -42876,7 +42876,7 @@
       </c>
       <c r="C1156" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-213</t>
         </is>
       </c>
       <c r="D1156" s="2" t="inlineStr"/>
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C1157" s="4" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-213</t>
         </is>
       </c>
       <c r="D1157" s="4" t="inlineStr"/>
@@ -42946,7 +42946,7 @@
       </c>
       <c r="C1158" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-213</t>
         </is>
       </c>
       <c r="D1158" s="2" t="inlineStr"/>
@@ -42981,7 +42981,7 @@
       </c>
       <c r="C1159" s="4" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-213</t>
         </is>
       </c>
       <c r="D1159" s="4" t="inlineStr"/>
@@ -43016,7 +43016,7 @@
       </c>
       <c r="C1160" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-309</t>
         </is>
       </c>
       <c r="D1160" s="2" t="inlineStr"/>
@@ -43051,7 +43051,7 @@
       </c>
       <c r="C1161" s="4" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-309</t>
         </is>
       </c>
       <c r="D1161" s="4" t="inlineStr"/>
@@ -43086,7 +43086,7 @@
       </c>
       <c r="C1162" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-309</t>
         </is>
       </c>
       <c r="D1162" s="2" t="inlineStr"/>
@@ -43121,7 +43121,7 @@
       </c>
       <c r="C1163" s="4" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-309</t>
         </is>
       </c>
       <c r="D1163" s="4" t="inlineStr"/>
@@ -43156,7 +43156,7 @@
       </c>
       <c r="C1164" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-309</t>
         </is>
       </c>
       <c r="D1164" s="2" t="inlineStr"/>
@@ -43191,7 +43191,7 @@
       </c>
       <c r="C1165" s="4" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-310</t>
         </is>
       </c>
       <c r="D1165" s="4" t="inlineStr"/>
@@ -43226,7 +43226,7 @@
       </c>
       <c r="C1166" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-310</t>
         </is>
       </c>
       <c r="D1166" s="2" t="inlineStr"/>
@@ -43261,7 +43261,7 @@
       </c>
       <c r="C1167" s="4" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-310</t>
         </is>
       </c>
       <c r="D1167" s="4" t="inlineStr"/>
@@ -43296,7 +43296,7 @@
       </c>
       <c r="C1168" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-310</t>
         </is>
       </c>
       <c r="D1168" s="2" t="inlineStr"/>
@@ -43331,7 +43331,7 @@
       </c>
       <c r="C1169" s="4" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-310</t>
         </is>
       </c>
       <c r="D1169" s="4" t="inlineStr"/>
@@ -43366,7 +43366,7 @@
       </c>
       <c r="C1170" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-313</t>
         </is>
       </c>
       <c r="D1170" s="2" t="inlineStr"/>
@@ -43401,7 +43401,7 @@
       </c>
       <c r="C1171" s="4" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-313</t>
         </is>
       </c>
       <c r="D1171" s="4" t="inlineStr"/>
@@ -43436,7 +43436,7 @@
       </c>
       <c r="C1172" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-313</t>
         </is>
       </c>
       <c r="D1172" s="2" t="inlineStr"/>
@@ -43471,7 +43471,7 @@
       </c>
       <c r="C1173" s="4" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-313</t>
         </is>
       </c>
       <c r="D1173" s="4" t="inlineStr"/>
@@ -43506,7 +43506,7 @@
       </c>
       <c r="C1174" s="2" t="inlineStr">
         <is>
-          <t>MOPX</t>
+          <t>MOPX-313</t>
         </is>
       </c>
       <c r="D1174" s="2" t="inlineStr"/>
@@ -43541,7 +43541,7 @@
       </c>
       <c r="C1175" s="4" t="inlineStr">
         <is>
-          <t>MSPX</t>
+          <t>MSPX-303</t>
         </is>
       </c>
       <c r="D1175" s="4" t="inlineStr"/>
@@ -43576,7 +43576,7 @@
       </c>
       <c r="C1176" s="2" t="inlineStr">
         <is>
-          <t>MSPX</t>
+          <t>MSPX-303</t>
         </is>
       </c>
       <c r="D1176" s="2" t="inlineStr"/>
@@ -43611,7 +43611,7 @@
       </c>
       <c r="C1177" s="4" t="inlineStr">
         <is>
-          <t>MSPX</t>
+          <t>MSPX-303</t>
         </is>
       </c>
       <c r="D1177" s="4" t="inlineStr"/>
@@ -43646,7 +43646,7 @@
       </c>
       <c r="C1178" s="2" t="inlineStr">
         <is>
-          <t>MSPX</t>
+          <t>MSPX-303</t>
         </is>
       </c>
       <c r="D1178" s="2" t="inlineStr"/>
@@ -43681,7 +43681,7 @@
       </c>
       <c r="C1179" s="4" t="inlineStr">
         <is>
-          <t>MSPX</t>
+          <t>MSPX-403</t>
         </is>
       </c>
       <c r="D1179" s="4" t="inlineStr"/>
@@ -43716,7 +43716,7 @@
       </c>
       <c r="C1180" s="2" t="inlineStr">
         <is>
-          <t>MSPX</t>
+          <t>MSPX-403</t>
         </is>
       </c>
       <c r="D1180" s="2" t="inlineStr"/>
@@ -43751,7 +43751,7 @@
       </c>
       <c r="C1181" s="4" t="inlineStr">
         <is>
-          <t>MSPX</t>
+          <t>MSPX-403</t>
         </is>
       </c>
       <c r="D1181" s="4" t="inlineStr"/>
@@ -43786,7 +43786,7 @@
       </c>
       <c r="C1182" s="2" t="inlineStr">
         <is>
-          <t>MSPX</t>
+          <t>MSPX-403</t>
         </is>
       </c>
       <c r="D1182" s="2" t="inlineStr"/>
@@ -43821,7 +43821,7 @@
       </c>
       <c r="C1183" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PA-600</t>
         </is>
       </c>
       <c r="D1183" s="4" t="inlineStr"/>
@@ -43856,7 +43856,7 @@
       </c>
       <c r="C1184" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PA-600</t>
         </is>
       </c>
       <c r="D1184" s="2" t="inlineStr"/>
@@ -43891,7 +43891,7 @@
       </c>
       <c r="C1185" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PA-600</t>
         </is>
       </c>
       <c r="D1185" s="4" t="inlineStr"/>
@@ -43926,7 +43926,7 @@
       </c>
       <c r="C1186" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PA-600</t>
         </is>
       </c>
       <c r="D1186" s="2" t="inlineStr"/>
@@ -43961,7 +43961,7 @@
       </c>
       <c r="C1187" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PA-605</t>
         </is>
       </c>
       <c r="D1187" s="4" t="inlineStr"/>
@@ -43996,7 +43996,7 @@
       </c>
       <c r="C1188" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PA-605</t>
         </is>
       </c>
       <c r="D1188" s="2" t="inlineStr"/>
@@ -44031,7 +44031,7 @@
       </c>
       <c r="C1189" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PA-605</t>
         </is>
       </c>
       <c r="D1189" s="4" t="inlineStr"/>
@@ -44066,7 +44066,7 @@
       </c>
       <c r="C1190" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PA-605</t>
         </is>
       </c>
       <c r="D1190" s="2" t="inlineStr"/>
@@ -44101,7 +44101,7 @@
       </c>
       <c r="C1191" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PA-610</t>
         </is>
       </c>
       <c r="D1191" s="4" t="inlineStr"/>
@@ -44136,7 +44136,7 @@
       </c>
       <c r="C1192" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PA-610</t>
         </is>
       </c>
       <c r="D1192" s="2" t="inlineStr"/>
@@ -44171,7 +44171,7 @@
       </c>
       <c r="C1193" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PA-610</t>
         </is>
       </c>
       <c r="D1193" s="4" t="inlineStr"/>
@@ -44206,7 +44206,7 @@
       </c>
       <c r="C1194" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PA-610</t>
         </is>
       </c>
       <c r="D1194" s="2" t="inlineStr"/>
@@ -44241,7 +44241,7 @@
       </c>
       <c r="C1195" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PA-615</t>
         </is>
       </c>
       <c r="D1195" s="4" t="inlineStr"/>
@@ -44276,7 +44276,7 @@
       </c>
       <c r="C1196" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PA-615</t>
         </is>
       </c>
       <c r="D1196" s="2" t="inlineStr"/>
@@ -44311,7 +44311,7 @@
       </c>
       <c r="C1197" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PA-615</t>
         </is>
       </c>
       <c r="D1197" s="4" t="inlineStr"/>
@@ -44346,7 +44346,7 @@
       </c>
       <c r="C1198" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PA-615</t>
         </is>
       </c>
       <c r="D1198" s="2" t="inlineStr"/>
@@ -44381,7 +44381,7 @@
       </c>
       <c r="C1199" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PA-625</t>
         </is>
       </c>
       <c r="D1199" s="4" t="inlineStr">
@@ -44420,7 +44420,7 @@
       </c>
       <c r="C1200" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PA-625</t>
         </is>
       </c>
       <c r="D1200" s="2" t="inlineStr">
@@ -44459,7 +44459,7 @@
       </c>
       <c r="C1201" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PA-635</t>
         </is>
       </c>
       <c r="D1201" s="4" t="inlineStr">
@@ -44498,7 +44498,7 @@
       </c>
       <c r="C1202" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PA-635</t>
         </is>
       </c>
       <c r="D1202" s="2" t="inlineStr">
@@ -44537,7 +44537,7 @@
       </c>
       <c r="C1203" s="4" t="inlineStr">
         <is>
-          <t>PU</t>
+          <t>PU-100</t>
         </is>
       </c>
       <c r="D1203" s="4" t="inlineStr"/>
@@ -44572,7 +44572,7 @@
       </c>
       <c r="C1204" s="2" t="inlineStr">
         <is>
-          <t>PU</t>
+          <t>PU-100</t>
         </is>
       </c>
       <c r="D1204" s="2" t="inlineStr"/>
@@ -44607,7 +44607,7 @@
       </c>
       <c r="C1205" s="4" t="inlineStr">
         <is>
-          <t>PU</t>
+          <t>PU-100</t>
         </is>
       </c>
       <c r="D1205" s="4" t="inlineStr"/>
@@ -44642,7 +44642,7 @@
       </c>
       <c r="C1206" s="2" t="inlineStr">
         <is>
-          <t>PU</t>
+          <t>PU-100</t>
         </is>
       </c>
       <c r="D1206" s="2" t="inlineStr"/>
@@ -44677,7 +44677,7 @@
       </c>
       <c r="C1207" s="4" t="inlineStr">
         <is>
-          <t>PU</t>
+          <t>PU-150</t>
         </is>
       </c>
       <c r="D1207" s="4" t="inlineStr"/>
@@ -44712,7 +44712,7 @@
       </c>
       <c r="C1208" s="2" t="inlineStr">
         <is>
-          <t>PU</t>
+          <t>PU-150</t>
         </is>
       </c>
       <c r="D1208" s="2" t="inlineStr"/>
@@ -44747,7 +44747,7 @@
       </c>
       <c r="C1209" s="4" t="inlineStr">
         <is>
-          <t>PU</t>
+          <t>PU-150</t>
         </is>
       </c>
       <c r="D1209" s="4" t="inlineStr"/>
@@ -44782,7 +44782,7 @@
       </c>
       <c r="C1210" s="2" t="inlineStr">
         <is>
-          <t>PU</t>
+          <t>PU-150</t>
         </is>
       </c>
       <c r="D1210" s="2" t="inlineStr"/>
@@ -44817,7 +44817,7 @@
       </c>
       <c r="C1211" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-300</t>
         </is>
       </c>
       <c r="D1211" s="4" t="inlineStr">
@@ -44856,7 +44856,7 @@
       </c>
       <c r="C1212" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-300</t>
         </is>
       </c>
       <c r="D1212" s="2" t="inlineStr">
@@ -44895,7 +44895,7 @@
       </c>
       <c r="C1213" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-300</t>
         </is>
       </c>
       <c r="D1213" s="4" t="inlineStr">
@@ -44934,7 +44934,7 @@
       </c>
       <c r="C1214" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-500</t>
         </is>
       </c>
       <c r="D1214" s="2" t="inlineStr">
@@ -44973,7 +44973,7 @@
       </c>
       <c r="C1215" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-500</t>
         </is>
       </c>
       <c r="D1215" s="4" t="inlineStr">
@@ -45012,7 +45012,7 @@
       </c>
       <c r="C1216" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-500</t>
         </is>
       </c>
       <c r="D1216" s="2" t="inlineStr">
@@ -45051,7 +45051,7 @@
       </c>
       <c r="C1217" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-811</t>
         </is>
       </c>
       <c r="D1217" s="4" t="inlineStr">
@@ -45090,7 +45090,7 @@
       </c>
       <c r="C1218" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-811</t>
         </is>
       </c>
       <c r="D1218" s="2" t="inlineStr">
@@ -45129,7 +45129,7 @@
       </c>
       <c r="C1219" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-816</t>
         </is>
       </c>
       <c r="D1219" s="4" t="inlineStr">
@@ -45168,7 +45168,7 @@
       </c>
       <c r="C1220" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-816</t>
         </is>
       </c>
       <c r="D1220" s="2" t="inlineStr">
@@ -45207,7 +45207,7 @@
       </c>
       <c r="C1221" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-820</t>
         </is>
       </c>
       <c r="D1221" s="4" t="inlineStr">
@@ -45246,7 +45246,7 @@
       </c>
       <c r="C1222" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-820</t>
         </is>
       </c>
       <c r="D1222" s="2" t="inlineStr">
@@ -45285,7 +45285,7 @@
       </c>
       <c r="C1223" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-821</t>
         </is>
       </c>
       <c r="D1223" s="4" t="inlineStr">
@@ -45324,7 +45324,7 @@
       </c>
       <c r="C1224" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-821</t>
         </is>
       </c>
       <c r="D1224" s="2" t="inlineStr">
@@ -45363,7 +45363,7 @@
       </c>
       <c r="C1225" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-825</t>
         </is>
       </c>
       <c r="D1225" s="4" t="inlineStr">
@@ -45402,7 +45402,7 @@
       </c>
       <c r="C1226" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-825</t>
         </is>
       </c>
       <c r="D1226" s="2" t="inlineStr">
@@ -45441,7 +45441,7 @@
       </c>
       <c r="C1227" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-826</t>
         </is>
       </c>
       <c r="D1227" s="4" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="C1228" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-826</t>
         </is>
       </c>
       <c r="D1228" s="2" t="inlineStr">
@@ -45519,7 +45519,7 @@
       </c>
       <c r="C1229" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-830</t>
         </is>
       </c>
       <c r="D1229" s="4" t="inlineStr">
@@ -45558,7 +45558,7 @@
       </c>
       <c r="C1230" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-830</t>
         </is>
       </c>
       <c r="D1230" s="2" t="inlineStr">
@@ -45597,7 +45597,7 @@
       </c>
       <c r="C1231" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-831</t>
         </is>
       </c>
       <c r="D1231" s="4" t="inlineStr">
@@ -45636,7 +45636,7 @@
       </c>
       <c r="C1232" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-831</t>
         </is>
       </c>
       <c r="D1232" s="2" t="inlineStr">
@@ -45675,7 +45675,7 @@
       </c>
       <c r="C1233" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-835</t>
         </is>
       </c>
       <c r="D1233" s="4" t="inlineStr">
@@ -45714,7 +45714,7 @@
       </c>
       <c r="C1234" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-835</t>
         </is>
       </c>
       <c r="D1234" s="2" t="inlineStr">
@@ -45753,7 +45753,7 @@
       </c>
       <c r="C1235" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-836</t>
         </is>
       </c>
       <c r="D1235" s="4" t="inlineStr">
@@ -45792,7 +45792,7 @@
       </c>
       <c r="C1236" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-836</t>
         </is>
       </c>
       <c r="D1236" s="2" t="inlineStr">
@@ -45831,7 +45831,7 @@
       </c>
       <c r="C1237" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-840</t>
         </is>
       </c>
       <c r="D1237" s="4" t="inlineStr">
@@ -45870,7 +45870,7 @@
       </c>
       <c r="C1238" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-840</t>
         </is>
       </c>
       <c r="D1238" s="2" t="inlineStr">
@@ -45909,7 +45909,7 @@
       </c>
       <c r="C1239" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-841</t>
         </is>
       </c>
       <c r="D1239" s="4" t="inlineStr">
@@ -45948,7 +45948,7 @@
       </c>
       <c r="C1240" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-841</t>
         </is>
       </c>
       <c r="D1240" s="2" t="inlineStr">
@@ -45987,7 +45987,7 @@
       </c>
       <c r="C1241" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-845</t>
         </is>
       </c>
       <c r="D1241" s="4" t="inlineStr">
@@ -46026,7 +46026,7 @@
       </c>
       <c r="C1242" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-845</t>
         </is>
       </c>
       <c r="D1242" s="2" t="inlineStr">
@@ -46065,7 +46065,7 @@
       </c>
       <c r="C1243" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-846</t>
         </is>
       </c>
       <c r="D1243" s="4" t="inlineStr">
@@ -46104,7 +46104,7 @@
       </c>
       <c r="C1244" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-846</t>
         </is>
       </c>
       <c r="D1244" s="2" t="inlineStr">
@@ -46143,7 +46143,7 @@
       </c>
       <c r="C1245" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-850</t>
         </is>
       </c>
       <c r="D1245" s="4" t="inlineStr">
@@ -46182,7 +46182,7 @@
       </c>
       <c r="C1246" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-850</t>
         </is>
       </c>
       <c r="D1246" s="2" t="inlineStr">
@@ -46221,7 +46221,7 @@
       </c>
       <c r="C1247" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-851</t>
         </is>
       </c>
       <c r="D1247" s="4" t="inlineStr">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C1248" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-851</t>
         </is>
       </c>
       <c r="D1248" s="2" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="C1249" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-855</t>
         </is>
       </c>
       <c r="D1249" s="4" t="inlineStr">
@@ -46338,7 +46338,7 @@
       </c>
       <c r="C1250" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-855</t>
         </is>
       </c>
       <c r="D1250" s="2" t="inlineStr">
@@ -46377,7 +46377,7 @@
       </c>
       <c r="C1251" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-856</t>
         </is>
       </c>
       <c r="D1251" s="4" t="inlineStr">
@@ -46416,7 +46416,7 @@
       </c>
       <c r="C1252" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-856</t>
         </is>
       </c>
       <c r="D1252" s="2" t="inlineStr">
@@ -46455,7 +46455,7 @@
       </c>
       <c r="C1253" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-860</t>
         </is>
       </c>
       <c r="D1253" s="4" t="inlineStr">
@@ -46494,7 +46494,7 @@
       </c>
       <c r="C1254" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-860</t>
         </is>
       </c>
       <c r="D1254" s="2" t="inlineStr">
@@ -46533,7 +46533,7 @@
       </c>
       <c r="C1255" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-861</t>
         </is>
       </c>
       <c r="D1255" s="4" t="inlineStr">
@@ -46572,7 +46572,7 @@
       </c>
       <c r="C1256" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-861</t>
         </is>
       </c>
       <c r="D1256" s="2" t="inlineStr">
@@ -46611,7 +46611,7 @@
       </c>
       <c r="C1257" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-865</t>
         </is>
       </c>
       <c r="D1257" s="4" t="inlineStr">
@@ -46650,7 +46650,7 @@
       </c>
       <c r="C1258" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-865</t>
         </is>
       </c>
       <c r="D1258" s="2" t="inlineStr">
@@ -46689,7 +46689,7 @@
       </c>
       <c r="C1259" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-866</t>
         </is>
       </c>
       <c r="D1259" s="4" t="inlineStr">
@@ -46728,7 +46728,7 @@
       </c>
       <c r="C1260" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-866</t>
         </is>
       </c>
       <c r="D1260" s="2" t="inlineStr">
@@ -46767,7 +46767,7 @@
       </c>
       <c r="C1261" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-870</t>
         </is>
       </c>
       <c r="D1261" s="4" t="inlineStr">
@@ -46806,7 +46806,7 @@
       </c>
       <c r="C1262" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-870</t>
         </is>
       </c>
       <c r="D1262" s="2" t="inlineStr">
@@ -46845,7 +46845,7 @@
       </c>
       <c r="C1263" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-871</t>
         </is>
       </c>
       <c r="D1263" s="4" t="inlineStr">
@@ -46884,7 +46884,7 @@
       </c>
       <c r="C1264" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-871</t>
         </is>
       </c>
       <c r="D1264" s="2" t="inlineStr">
@@ -46923,7 +46923,7 @@
       </c>
       <c r="C1265" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-875</t>
         </is>
       </c>
       <c r="D1265" s="4" t="inlineStr">
@@ -46962,7 +46962,7 @@
       </c>
       <c r="C1266" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-875</t>
         </is>
       </c>
       <c r="D1266" s="2" t="inlineStr">
@@ -47001,7 +47001,7 @@
       </c>
       <c r="C1267" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-876</t>
         </is>
       </c>
       <c r="D1267" s="4" t="inlineStr">
@@ -47040,7 +47040,7 @@
       </c>
       <c r="C1268" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-876</t>
         </is>
       </c>
       <c r="D1268" s="2" t="inlineStr">
@@ -47079,7 +47079,7 @@
       </c>
       <c r="C1269" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-880</t>
         </is>
       </c>
       <c r="D1269" s="4" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="C1270" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-880</t>
         </is>
       </c>
       <c r="D1270" s="2" t="inlineStr">
@@ -47157,7 +47157,7 @@
       </c>
       <c r="C1271" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-881</t>
         </is>
       </c>
       <c r="D1271" s="4" t="inlineStr">
@@ -47196,7 +47196,7 @@
       </c>
       <c r="C1272" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-881</t>
         </is>
       </c>
       <c r="D1272" s="2" t="inlineStr">
@@ -47235,7 +47235,7 @@
       </c>
       <c r="C1273" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-885</t>
         </is>
       </c>
       <c r="D1273" s="4" t="inlineStr">
@@ -47274,7 +47274,7 @@
       </c>
       <c r="C1274" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-885</t>
         </is>
       </c>
       <c r="D1274" s="2" t="inlineStr">
@@ -47313,7 +47313,7 @@
       </c>
       <c r="C1275" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-886</t>
         </is>
       </c>
       <c r="D1275" s="4" t="inlineStr">
@@ -47352,7 +47352,7 @@
       </c>
       <c r="C1276" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S-886</t>
         </is>
       </c>
       <c r="D1276" s="2" t="inlineStr">
@@ -47391,7 +47391,7 @@
       </c>
       <c r="C1277" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-405</t>
         </is>
       </c>
       <c r="D1277" s="4" t="inlineStr"/>
@@ -47426,7 +47426,7 @@
       </c>
       <c r="C1278" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-405</t>
         </is>
       </c>
       <c r="D1278" s="2" t="inlineStr"/>
@@ -47461,7 +47461,7 @@
       </c>
       <c r="C1279" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-405</t>
         </is>
       </c>
       <c r="D1279" s="4" t="inlineStr"/>
@@ -47496,7 +47496,7 @@
       </c>
       <c r="C1280" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-405</t>
         </is>
       </c>
       <c r="D1280" s="2" t="inlineStr"/>
@@ -47531,7 +47531,7 @@
       </c>
       <c r="C1281" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-405</t>
         </is>
       </c>
       <c r="D1281" s="4" t="inlineStr"/>
@@ -47566,7 +47566,7 @@
       </c>
       <c r="C1282" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-505</t>
         </is>
       </c>
       <c r="D1282" s="2" t="inlineStr"/>
@@ -47601,7 +47601,7 @@
       </c>
       <c r="C1283" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-505</t>
         </is>
       </c>
       <c r="D1283" s="4" t="inlineStr"/>
@@ -47636,7 +47636,7 @@
       </c>
       <c r="C1284" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-505</t>
         </is>
       </c>
       <c r="D1284" s="2" t="inlineStr"/>
@@ -47671,7 +47671,7 @@
       </c>
       <c r="C1285" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-505</t>
         </is>
       </c>
       <c r="D1285" s="4" t="inlineStr"/>
@@ -47706,7 +47706,7 @@
       </c>
       <c r="C1286" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-505</t>
         </is>
       </c>
       <c r="D1286" s="2" t="inlineStr"/>
@@ -47741,7 +47741,7 @@
       </c>
       <c r="C1287" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-407</t>
         </is>
       </c>
       <c r="D1287" s="4" t="inlineStr"/>
@@ -47776,7 +47776,7 @@
       </c>
       <c r="C1288" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-407</t>
         </is>
       </c>
       <c r="D1288" s="2" t="inlineStr"/>
@@ -47811,7 +47811,7 @@
       </c>
       <c r="C1289" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-407</t>
         </is>
       </c>
       <c r="D1289" s="4" t="inlineStr"/>
@@ -47846,7 +47846,7 @@
       </c>
       <c r="C1290" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-407</t>
         </is>
       </c>
       <c r="D1290" s="2" t="inlineStr"/>
@@ -47881,7 +47881,7 @@
       </c>
       <c r="C1291" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-407</t>
         </is>
       </c>
       <c r="D1291" s="4" t="inlineStr"/>
@@ -47916,7 +47916,7 @@
       </c>
       <c r="C1292" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-409</t>
         </is>
       </c>
       <c r="D1292" s="2" t="inlineStr"/>
@@ -47951,7 +47951,7 @@
       </c>
       <c r="C1293" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-409</t>
         </is>
       </c>
       <c r="D1293" s="4" t="inlineStr"/>
@@ -47986,7 +47986,7 @@
       </c>
       <c r="C1294" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-409</t>
         </is>
       </c>
       <c r="D1294" s="2" t="inlineStr"/>
@@ -48021,7 +48021,7 @@
       </c>
       <c r="C1295" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-409</t>
         </is>
       </c>
       <c r="D1295" s="4" t="inlineStr"/>
@@ -48056,7 +48056,7 @@
       </c>
       <c r="C1296" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-409</t>
         </is>
       </c>
       <c r="D1296" s="2" t="inlineStr"/>
@@ -48091,7 +48091,7 @@
       </c>
       <c r="C1297" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-410</t>
         </is>
       </c>
       <c r="D1297" s="4" t="inlineStr"/>
@@ -48126,7 +48126,7 @@
       </c>
       <c r="C1298" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-410</t>
         </is>
       </c>
       <c r="D1298" s="2" t="inlineStr"/>
@@ -48161,7 +48161,7 @@
       </c>
       <c r="C1299" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-410</t>
         </is>
       </c>
       <c r="D1299" s="4" t="inlineStr"/>
@@ -48196,7 +48196,7 @@
       </c>
       <c r="C1300" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-410</t>
         </is>
       </c>
       <c r="D1300" s="2" t="inlineStr"/>
@@ -48231,7 +48231,7 @@
       </c>
       <c r="C1301" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-410</t>
         </is>
       </c>
       <c r="D1301" s="4" t="inlineStr"/>
@@ -48266,7 +48266,7 @@
       </c>
       <c r="C1302" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-413</t>
         </is>
       </c>
       <c r="D1302" s="2" t="inlineStr"/>
@@ -48301,7 +48301,7 @@
       </c>
       <c r="C1303" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-413</t>
         </is>
       </c>
       <c r="D1303" s="4" t="inlineStr"/>
@@ -48336,7 +48336,7 @@
       </c>
       <c r="C1304" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-413</t>
         </is>
       </c>
       <c r="D1304" s="2" t="inlineStr"/>
@@ -48371,7 +48371,7 @@
       </c>
       <c r="C1305" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-413</t>
         </is>
       </c>
       <c r="D1305" s="4" t="inlineStr"/>
@@ -48406,7 +48406,7 @@
       </c>
       <c r="C1306" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-413</t>
         </is>
       </c>
       <c r="D1306" s="2" t="inlineStr"/>
@@ -48441,7 +48441,7 @@
       </c>
       <c r="C1307" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-507</t>
         </is>
       </c>
       <c r="D1307" s="4" t="inlineStr"/>
@@ -48476,7 +48476,7 @@
       </c>
       <c r="C1308" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-507</t>
         </is>
       </c>
       <c r="D1308" s="2" t="inlineStr"/>
@@ -48511,7 +48511,7 @@
       </c>
       <c r="C1309" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-507</t>
         </is>
       </c>
       <c r="D1309" s="4" t="inlineStr"/>
@@ -48546,7 +48546,7 @@
       </c>
       <c r="C1310" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-507</t>
         </is>
       </c>
       <c r="D1310" s="2" t="inlineStr"/>
@@ -48581,7 +48581,7 @@
       </c>
       <c r="C1311" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-507</t>
         </is>
       </c>
       <c r="D1311" s="4" t="inlineStr"/>
@@ -48616,7 +48616,7 @@
       </c>
       <c r="C1312" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-508</t>
         </is>
       </c>
       <c r="D1312" s="2" t="inlineStr"/>
@@ -48651,7 +48651,7 @@
       </c>
       <c r="C1313" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-508</t>
         </is>
       </c>
       <c r="D1313" s="4" t="inlineStr"/>
@@ -48686,7 +48686,7 @@
       </c>
       <c r="C1314" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-508</t>
         </is>
       </c>
       <c r="D1314" s="2" t="inlineStr"/>
@@ -48721,7 +48721,7 @@
       </c>
       <c r="C1315" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-508</t>
         </is>
       </c>
       <c r="D1315" s="4" t="inlineStr"/>
@@ -48756,7 +48756,7 @@
       </c>
       <c r="C1316" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-508</t>
         </is>
       </c>
       <c r="D1316" s="2" t="inlineStr"/>
@@ -48791,7 +48791,7 @@
       </c>
       <c r="C1317" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-513</t>
         </is>
       </c>
       <c r="D1317" s="4" t="inlineStr"/>
@@ -48826,7 +48826,7 @@
       </c>
       <c r="C1318" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-513</t>
         </is>
       </c>
       <c r="D1318" s="2" t="inlineStr"/>
@@ -48861,7 +48861,7 @@
       </c>
       <c r="C1319" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-513</t>
         </is>
       </c>
       <c r="D1319" s="4" t="inlineStr"/>
@@ -48896,7 +48896,7 @@
       </c>
       <c r="C1320" s="2" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-513</t>
         </is>
       </c>
       <c r="D1320" s="2" t="inlineStr"/>
@@ -48931,7 +48931,7 @@
       </c>
       <c r="C1321" s="4" t="inlineStr">
         <is>
-          <t>WHPX</t>
+          <t>WHPX-513</t>
         </is>
       </c>
       <c r="D1321" s="4" t="inlineStr"/>
@@ -48966,7 +48966,7 @@
       </c>
       <c r="C1322" s="2" t="inlineStr">
         <is>
-          <t>SJ-E</t>
+          <t>SJ-E-all types</t>
         </is>
       </c>
       <c r="D1322" s="2" t="inlineStr"/>
@@ -49001,7 +49001,7 @@
       </c>
       <c r="C1323" s="4" t="inlineStr">
         <is>
-          <t>SJ-G</t>
+          <t>SJ-G-all types</t>
         </is>
       </c>
       <c r="D1323" s="4" t="inlineStr"/>
@@ -49071,7 +49071,7 @@
       </c>
       <c r="C1325" s="4" t="inlineStr">
         <is>
-          <t>OSA</t>
+          <t>OSA-7</t>
         </is>
       </c>
       <c r="D1325" s="4" t="inlineStr"/>
@@ -49106,7 +49106,7 @@
       </c>
       <c r="C1326" s="2" t="inlineStr">
         <is>
-          <t>OSA</t>
+          <t>OSA-7</t>
         </is>
       </c>
       <c r="D1326" s="2" t="inlineStr"/>
@@ -49141,7 +49141,7 @@
       </c>
       <c r="C1327" s="4" t="inlineStr">
         <is>
-          <t>OSA</t>
+          <t>OSA-20</t>
         </is>
       </c>
       <c r="D1327" s="4" t="inlineStr"/>
@@ -49176,7 +49176,7 @@
       </c>
       <c r="C1328" s="2" t="inlineStr">
         <is>
-          <t>OSA</t>
+          <t>OSA-35</t>
         </is>
       </c>
       <c r="D1328" s="2" t="inlineStr"/>
@@ -49211,7 +49211,7 @@
       </c>
       <c r="C1329" s="4" t="inlineStr">
         <is>
-          <t>OSB</t>
+          <t>OSB-20</t>
         </is>
       </c>
       <c r="D1329" s="4" t="inlineStr"/>
@@ -49246,7 +49246,7 @@
       </c>
       <c r="C1330" s="2" t="inlineStr">
         <is>
-          <t>OSB</t>
+          <t>OSB-30</t>
         </is>
       </c>
       <c r="D1330" s="2" t="inlineStr"/>
@@ -49281,7 +49281,7 @@
       </c>
       <c r="C1331" s="4" t="inlineStr">
         <is>
-          <t>OSB</t>
+          <t>OSB-35</t>
         </is>
       </c>
       <c r="D1331" s="4" t="inlineStr"/>
@@ -49316,7 +49316,7 @@
       </c>
       <c r="C1332" s="2" t="inlineStr">
         <is>
-          <t>OSC</t>
+          <t>OSC-4</t>
         </is>
       </c>
       <c r="D1332" s="2" t="inlineStr"/>
@@ -49351,7 +49351,7 @@
       </c>
       <c r="C1333" s="4" t="inlineStr">
         <is>
-          <t>OSC</t>
+          <t>OSC-4</t>
         </is>
       </c>
       <c r="D1333" s="4" t="inlineStr"/>
@@ -49386,7 +49386,7 @@
       </c>
       <c r="C1334" s="2" t="inlineStr">
         <is>
-          <t>OSC</t>
+          <t>OSC-5</t>
         </is>
       </c>
       <c r="D1334" s="2" t="inlineStr"/>
@@ -49421,7 +49421,7 @@
       </c>
       <c r="C1335" s="4" t="inlineStr">
         <is>
-          <t>OSC</t>
+          <t>OSC-5</t>
         </is>
       </c>
       <c r="D1335" s="4" t="inlineStr"/>
@@ -49456,7 +49456,7 @@
       </c>
       <c r="C1336" s="2" t="inlineStr">
         <is>
-          <t>OSC</t>
+          <t>OSC-15</t>
         </is>
       </c>
       <c r="D1336" s="2" t="inlineStr"/>
@@ -49491,7 +49491,7 @@
       </c>
       <c r="C1337" s="4" t="inlineStr">
         <is>
-          <t>OSC</t>
+          <t>OSC-18</t>
         </is>
       </c>
       <c r="D1337" s="4" t="inlineStr"/>
@@ -49526,7 +49526,7 @@
       </c>
       <c r="C1338" s="2" t="inlineStr">
         <is>
-          <t>OSC</t>
+          <t>OSC-25</t>
         </is>
       </c>
       <c r="D1338" s="2" t="inlineStr"/>
@@ -49561,7 +49561,7 @@
       </c>
       <c r="C1339" s="4" t="inlineStr">
         <is>
-          <t>OSC</t>
+          <t>OSC-30</t>
         </is>
       </c>
       <c r="D1339" s="4" t="inlineStr"/>
@@ -49596,7 +49596,7 @@
       </c>
       <c r="C1340" s="2" t="inlineStr">
         <is>
-          <t>OSC</t>
+          <t>OSC-40</t>
         </is>
       </c>
       <c r="D1340" s="2" t="inlineStr"/>
@@ -49631,7 +49631,7 @@
       </c>
       <c r="C1341" s="4" t="inlineStr">
         <is>
-          <t>OSC</t>
+          <t>OSC-50</t>
         </is>
       </c>
       <c r="D1341" s="4" t="inlineStr"/>
@@ -49666,7 +49666,7 @@
       </c>
       <c r="C1342" s="2" t="inlineStr">
         <is>
-          <t>OSD</t>
+          <t>OSD-all types</t>
         </is>
       </c>
       <c r="D1342" s="2" t="inlineStr"/>
@@ -49701,7 +49701,7 @@
       </c>
       <c r="C1343" s="4" t="inlineStr">
         <is>
-          <t>OSD</t>
+          <t>OSD-all types</t>
         </is>
       </c>
       <c r="D1343" s="4" t="inlineStr"/>
@@ -49736,7 +49736,7 @@
       </c>
       <c r="C1344" s="2" t="inlineStr">
         <is>
-          <t>OSE</t>
+          <t>OSE-all types</t>
         </is>
       </c>
       <c r="D1344" s="2" t="inlineStr"/>
@@ -49771,7 +49771,7 @@
       </c>
       <c r="C1345" s="4" t="inlineStr">
         <is>
-          <t>OSE</t>
+          <t>OSE-all types</t>
         </is>
       </c>
       <c r="D1345" s="4" t="inlineStr"/>
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C1346" s="2" t="inlineStr">
         <is>
-          <t>OTA</t>
+          <t>OTA-2</t>
         </is>
       </c>
       <c r="D1346" s="2" t="inlineStr"/>
@@ -49841,7 +49841,7 @@
       </c>
       <c r="C1347" s="4" t="inlineStr">
         <is>
-          <t>OTA</t>
+          <t>OTA-7</t>
         </is>
       </c>
       <c r="D1347" s="4" t="inlineStr"/>
@@ -49876,7 +49876,7 @@
       </c>
       <c r="C1348" s="2" t="inlineStr">
         <is>
-          <t>OTA</t>
+          <t>OTA-14</t>
         </is>
       </c>
       <c r="D1348" s="2" t="inlineStr"/>
@@ -49911,7 +49911,7 @@
       </c>
       <c r="C1349" s="4" t="inlineStr">
         <is>
-          <t>OTA</t>
+          <t>OTA-14</t>
         </is>
       </c>
       <c r="D1349" s="4" t="inlineStr"/>
@@ -49946,7 +49946,7 @@
       </c>
       <c r="C1350" s="2" t="inlineStr">
         <is>
-          <t>OTA</t>
+          <t>OTA-14</t>
         </is>
       </c>
       <c r="D1350" s="2" t="inlineStr"/>
@@ -49981,7 +49981,7 @@
       </c>
       <c r="C1351" s="4" t="inlineStr">
         <is>
-          <t>OTA</t>
+          <t>OTA-18</t>
         </is>
       </c>
       <c r="D1351" s="4" t="inlineStr"/>
@@ -50016,7 +50016,7 @@
       </c>
       <c r="C1352" s="2" t="inlineStr">
         <is>
-          <t>OTA</t>
+          <t>OTA-30</t>
         </is>
       </c>
       <c r="D1352" s="2" t="inlineStr"/>
@@ -50051,7 +50051,7 @@
       </c>
       <c r="C1353" s="4" t="inlineStr">
         <is>
-          <t>OTB</t>
+          <t>OTB-1</t>
         </is>
       </c>
       <c r="D1353" s="4" t="inlineStr"/>
@@ -50086,7 +50086,7 @@
       </c>
       <c r="C1354" s="2" t="inlineStr">
         <is>
-          <t>OTB</t>
+          <t>OTB-1</t>
         </is>
       </c>
       <c r="D1354" s="2" t="inlineStr"/>
@@ -50121,7 +50121,7 @@
       </c>
       <c r="C1355" s="4" t="inlineStr">
         <is>
-          <t>OTB</t>
+          <t>OTB-3</t>
         </is>
       </c>
       <c r="D1355" s="4" t="inlineStr"/>
@@ -50156,7 +50156,7 @@
       </c>
       <c r="C1356" s="2" t="inlineStr">
         <is>
-          <t>OTB</t>
+          <t>OTB-3</t>
         </is>
       </c>
       <c r="D1356" s="2" t="inlineStr"/>
@@ -50191,7 +50191,7 @@
       </c>
       <c r="C1357" s="4" t="inlineStr">
         <is>
-          <t>OTB</t>
+          <t>OTB-9</t>
         </is>
       </c>
       <c r="D1357" s="4" t="inlineStr"/>
@@ -50226,7 +50226,7 @@
       </c>
       <c r="C1358" s="2" t="inlineStr">
         <is>
-          <t>OTB</t>
+          <t>OTB-9</t>
         </is>
       </c>
       <c r="D1358" s="2" t="inlineStr"/>
@@ -50261,7 +50261,7 @@
       </c>
       <c r="C1359" s="4" t="inlineStr">
         <is>
-          <t>OTB</t>
+          <t>OTB-18</t>
         </is>
       </c>
       <c r="D1359" s="4" t="inlineStr"/>
@@ -50296,7 +50296,7 @@
       </c>
       <c r="C1360" s="2" t="inlineStr">
         <is>
-          <t>OTB</t>
+          <t>OTB-35</t>
         </is>
       </c>
       <c r="D1360" s="2" t="inlineStr"/>
@@ -50331,7 +50331,7 @@
       </c>
       <c r="C1361" s="4" t="inlineStr">
         <is>
-          <t>OTC</t>
+          <t>OTC-all types</t>
         </is>
       </c>
       <c r="D1361" s="4" t="inlineStr"/>
@@ -50366,7 +50366,7 @@
       </c>
       <c r="C1362" s="2" t="inlineStr">
         <is>
-          <t>OTC</t>
+          <t>OTC-all types</t>
         </is>
       </c>
       <c r="D1362" s="2" t="inlineStr"/>
@@ -51444,7 +51444,7 @@
       </c>
       <c r="C1392" s="2" t="inlineStr">
         <is>
-          <t>VTR..0  With rolling contact bearings and INTEGRAL lubrication</t>
+          <t>VTR..0 With rolling contact bearings and INTEGRAL lubrication</t>
         </is>
       </c>
       <c r="D1392" s="2" t="inlineStr">
@@ -51483,7 +51483,7 @@
       </c>
       <c r="C1393" s="4" t="inlineStr">
         <is>
-          <t>VTR..0  With rolling contact bearings and INTEGRAL lubrication</t>
+          <t>VTR..0 With rolling contact bearings and INTEGRAL lubrication</t>
         </is>
       </c>
       <c r="D1393" s="4" t="inlineStr">
@@ -51522,7 +51522,7 @@
       </c>
       <c r="C1394" s="2" t="inlineStr">
         <is>
-          <t>VTR..0  With rolling contact bearings and INTEGRAL lubrication</t>
+          <t>VTR..0 With rolling contact bearings and INTEGRAL lubrication</t>
         </is>
       </c>
       <c r="D1394" s="2" t="inlineStr">
@@ -51561,7 +51561,7 @@
       </c>
       <c r="C1395" s="4" t="inlineStr">
         <is>
-          <t>VTR..1  With rolling contact bearings and INTEGRAL lubrication</t>
+          <t>VTR..1 With rolling contact bearings and INTEGRAL lubrication</t>
         </is>
       </c>
       <c r="D1395" s="4" t="inlineStr">
@@ -51600,7 +51600,7 @@
       </c>
       <c r="C1396" s="2" t="inlineStr">
         <is>
-          <t>VTR..1  With rolling contact bearings and INTEGRAL lubrication</t>
+          <t>VTR..1 With rolling contact bearings and INTEGRAL lubrication</t>
         </is>
       </c>
       <c r="D1396" s="2" t="inlineStr">
@@ -51639,7 +51639,7 @@
       </c>
       <c r="C1397" s="4" t="inlineStr">
         <is>
-          <t>VTR..1  With rolling contact bearings and INTEGRAL lubrication</t>
+          <t>VTR..1 With rolling contact bearings and INTEGRAL lubrication</t>
         </is>
       </c>
       <c r="D1397" s="4" t="inlineStr">

--- a/output/oem_master.xlsx
+++ b/output/oem_master.xlsx
@@ -36086,7 +36086,7 @@
       </c>
       <c r="C962" s="2" t="inlineStr">
         <is>
-          <t>BWPX-307</t>
+          <t>BWPX 307</t>
         </is>
       </c>
       <c r="D962" s="2" t="inlineStr"/>
@@ -36121,7 +36121,7 @@
       </c>
       <c r="C963" s="4" t="inlineStr">
         <is>
-          <t>BWPX-307</t>
+          <t>BWPX 307</t>
         </is>
       </c>
       <c r="D963" s="4" t="inlineStr"/>
@@ -36156,7 +36156,7 @@
       </c>
       <c r="C964" s="2" t="inlineStr">
         <is>
-          <t>BWPX-307</t>
+          <t>BWPX 307</t>
         </is>
       </c>
       <c r="D964" s="2" t="inlineStr"/>
@@ -36191,7 +36191,7 @@
       </c>
       <c r="C965" s="4" t="inlineStr">
         <is>
-          <t>BWPX-307</t>
+          <t>BWPX 307</t>
         </is>
       </c>
       <c r="D965" s="4" t="inlineStr"/>
@@ -36226,7 +36226,7 @@
       </c>
       <c r="C966" s="2" t="inlineStr">
         <is>
-          <t>FOPX-605</t>
+          <t>FOPX 605</t>
         </is>
       </c>
       <c r="D966" s="2" t="inlineStr"/>
@@ -36261,7 +36261,7 @@
       </c>
       <c r="C967" s="4" t="inlineStr">
         <is>
-          <t>FOPX-605</t>
+          <t>FOPX 605</t>
         </is>
       </c>
       <c r="D967" s="4" t="inlineStr"/>
@@ -36296,7 +36296,7 @@
       </c>
       <c r="C968" s="2" t="inlineStr">
         <is>
-          <t>FOPX-605</t>
+          <t>FOPX 605</t>
         </is>
       </c>
       <c r="D968" s="2" t="inlineStr"/>
@@ -36331,7 +36331,7 @@
       </c>
       <c r="C969" s="4" t="inlineStr">
         <is>
-          <t>FOPX-605</t>
+          <t>FOPX 605</t>
         </is>
       </c>
       <c r="D969" s="4" t="inlineStr"/>
@@ -36366,7 +36366,7 @@
       </c>
       <c r="C970" s="2" t="inlineStr">
         <is>
-          <t>FOPX-605</t>
+          <t>FOPX 605</t>
         </is>
       </c>
       <c r="D970" s="2" t="inlineStr"/>
@@ -36401,7 +36401,7 @@
       </c>
       <c r="C971" s="4" t="inlineStr">
         <is>
-          <t>FOPX-607</t>
+          <t>FOPX 607</t>
         </is>
       </c>
       <c r="D971" s="4" t="inlineStr"/>
@@ -36436,7 +36436,7 @@
       </c>
       <c r="C972" s="2" t="inlineStr">
         <is>
-          <t>FOPX-607</t>
+          <t>FOPX 607</t>
         </is>
       </c>
       <c r="D972" s="2" t="inlineStr"/>
@@ -36471,7 +36471,7 @@
       </c>
       <c r="C973" s="4" t="inlineStr">
         <is>
-          <t>FOPX-607</t>
+          <t>FOPX 607</t>
         </is>
       </c>
       <c r="D973" s="4" t="inlineStr"/>
@@ -36506,7 +36506,7 @@
       </c>
       <c r="C974" s="2" t="inlineStr">
         <is>
-          <t>FOPX-607</t>
+          <t>FOPX 607</t>
         </is>
       </c>
       <c r="D974" s="2" t="inlineStr"/>
@@ -36541,7 +36541,7 @@
       </c>
       <c r="C975" s="4" t="inlineStr">
         <is>
-          <t>FOPX-607</t>
+          <t>FOPX 607</t>
         </is>
       </c>
       <c r="D975" s="4" t="inlineStr"/>
@@ -36576,7 +36576,7 @@
       </c>
       <c r="C976" s="2" t="inlineStr">
         <is>
-          <t>FOPX-609</t>
+          <t>FOPX 609</t>
         </is>
       </c>
       <c r="D976" s="2" t="inlineStr"/>
@@ -36611,7 +36611,7 @@
       </c>
       <c r="C977" s="4" t="inlineStr">
         <is>
-          <t>FOPX-609</t>
+          <t>FOPX 609</t>
         </is>
       </c>
       <c r="D977" s="4" t="inlineStr"/>
@@ -36646,7 +36646,7 @@
       </c>
       <c r="C978" s="2" t="inlineStr">
         <is>
-          <t>FOPX-609</t>
+          <t>FOPX 609</t>
         </is>
       </c>
       <c r="D978" s="2" t="inlineStr"/>
@@ -36681,7 +36681,7 @@
       </c>
       <c r="C979" s="4" t="inlineStr">
         <is>
-          <t>FOPX-609</t>
+          <t>FOPX 609</t>
         </is>
       </c>
       <c r="D979" s="4" t="inlineStr"/>
@@ -36716,7 +36716,7 @@
       </c>
       <c r="C980" s="2" t="inlineStr">
         <is>
-          <t>FOPX-609</t>
+          <t>FOPX 609</t>
         </is>
       </c>
       <c r="D980" s="2" t="inlineStr"/>
@@ -36751,7 +36751,7 @@
       </c>
       <c r="C981" s="4" t="inlineStr">
         <is>
-          <t>FOPX-610</t>
+          <t>FOPX 610</t>
         </is>
       </c>
       <c r="D981" s="4" t="inlineStr"/>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="C982" s="2" t="inlineStr">
         <is>
-          <t>FOPX-610</t>
+          <t>FOPX 610</t>
         </is>
       </c>
       <c r="D982" s="2" t="inlineStr"/>
@@ -36821,7 +36821,7 @@
       </c>
       <c r="C983" s="4" t="inlineStr">
         <is>
-          <t>FOPX-610</t>
+          <t>FOPX 610</t>
         </is>
       </c>
       <c r="D983" s="4" t="inlineStr"/>
@@ -36856,7 +36856,7 @@
       </c>
       <c r="C984" s="2" t="inlineStr">
         <is>
-          <t>FOPX-610</t>
+          <t>FOPX 610</t>
         </is>
       </c>
       <c r="D984" s="2" t="inlineStr"/>
@@ -36891,7 +36891,7 @@
       </c>
       <c r="C985" s="4" t="inlineStr">
         <is>
-          <t>FOPX-610</t>
+          <t>FOPX 610</t>
         </is>
       </c>
       <c r="D985" s="4" t="inlineStr"/>
@@ -36926,7 +36926,7 @@
       </c>
       <c r="C986" s="2" t="inlineStr">
         <is>
-          <t>FOPX-611</t>
+          <t>FOPX 611</t>
         </is>
       </c>
       <c r="D986" s="2" t="inlineStr"/>
@@ -36961,7 +36961,7 @@
       </c>
       <c r="C987" s="4" t="inlineStr">
         <is>
-          <t>FOPX-611</t>
+          <t>FOPX 611</t>
         </is>
       </c>
       <c r="D987" s="4" t="inlineStr"/>
@@ -36996,7 +36996,7 @@
       </c>
       <c r="C988" s="2" t="inlineStr">
         <is>
-          <t>FOPX-611</t>
+          <t>FOPX 611</t>
         </is>
       </c>
       <c r="D988" s="2" t="inlineStr"/>
@@ -37031,7 +37031,7 @@
       </c>
       <c r="C989" s="4" t="inlineStr">
         <is>
-          <t>FOPX-611</t>
+          <t>FOPX 611</t>
         </is>
       </c>
       <c r="D989" s="4" t="inlineStr"/>
@@ -37066,7 +37066,7 @@
       </c>
       <c r="C990" s="2" t="inlineStr">
         <is>
-          <t>FOPX-611</t>
+          <t>FOPX 611</t>
         </is>
       </c>
       <c r="D990" s="2" t="inlineStr"/>
@@ -37101,7 +37101,7 @@
       </c>
       <c r="C991" s="4" t="inlineStr">
         <is>
-          <t>FOPX-613</t>
+          <t>FOPX 613</t>
         </is>
       </c>
       <c r="D991" s="4" t="inlineStr"/>
@@ -37136,7 +37136,7 @@
       </c>
       <c r="C992" s="2" t="inlineStr">
         <is>
-          <t>FOPX-613</t>
+          <t>FOPX 613</t>
         </is>
       </c>
       <c r="D992" s="2" t="inlineStr"/>
@@ -37171,7 +37171,7 @@
       </c>
       <c r="C993" s="4" t="inlineStr">
         <is>
-          <t>FOPX-613</t>
+          <t>FOPX 613</t>
         </is>
       </c>
       <c r="D993" s="4" t="inlineStr"/>
@@ -37206,7 +37206,7 @@
       </c>
       <c r="C994" s="2" t="inlineStr">
         <is>
-          <t>FOPX-613</t>
+          <t>FOPX 613</t>
         </is>
       </c>
       <c r="D994" s="2" t="inlineStr"/>
@@ -37241,7 +37241,7 @@
       </c>
       <c r="C995" s="4" t="inlineStr">
         <is>
-          <t>FOPX-613</t>
+          <t>FOPX 613</t>
         </is>
       </c>
       <c r="D995" s="4" t="inlineStr"/>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="C996" s="2" t="inlineStr">
         <is>
-          <t>FOPX-614</t>
+          <t>FOPX 614</t>
         </is>
       </c>
       <c r="D996" s="2" t="inlineStr"/>
@@ -37311,7 +37311,7 @@
       </c>
       <c r="C997" s="4" t="inlineStr">
         <is>
-          <t>FOPX-614</t>
+          <t>FOPX 614</t>
         </is>
       </c>
       <c r="D997" s="4" t="inlineStr"/>
@@ -37346,7 +37346,7 @@
       </c>
       <c r="C998" s="2" t="inlineStr">
         <is>
-          <t>FOPX-614</t>
+          <t>FOPX 614</t>
         </is>
       </c>
       <c r="D998" s="2" t="inlineStr"/>
@@ -37381,7 +37381,7 @@
       </c>
       <c r="C999" s="4" t="inlineStr">
         <is>
-          <t>FOPX-614</t>
+          <t>FOPX 614</t>
         </is>
       </c>
       <c r="D999" s="4" t="inlineStr"/>
@@ -37416,7 +37416,7 @@
       </c>
       <c r="C1000" s="2" t="inlineStr">
         <is>
-          <t>FOPX-614</t>
+          <t>FOPX 614</t>
         </is>
       </c>
       <c r="D1000" s="2" t="inlineStr"/>
@@ -37451,7 +37451,7 @@
       </c>
       <c r="C1001" s="4" t="inlineStr">
         <is>
-          <t>LOPX-705</t>
+          <t>LOPX 705</t>
         </is>
       </c>
       <c r="D1001" s="4" t="inlineStr"/>
@@ -37486,7 +37486,7 @@
       </c>
       <c r="C1002" s="2" t="inlineStr">
         <is>
-          <t>LOPX-705</t>
+          <t>LOPX 705</t>
         </is>
       </c>
       <c r="D1002" s="2" t="inlineStr"/>
@@ -37521,7 +37521,7 @@
       </c>
       <c r="C1003" s="4" t="inlineStr">
         <is>
-          <t>LOPX-705</t>
+          <t>LOPX 705</t>
         </is>
       </c>
       <c r="D1003" s="4" t="inlineStr"/>
@@ -37556,7 +37556,7 @@
       </c>
       <c r="C1004" s="2" t="inlineStr">
         <is>
-          <t>LOPX-705</t>
+          <t>LOPX 705</t>
         </is>
       </c>
       <c r="D1004" s="2" t="inlineStr"/>
@@ -37591,7 +37591,7 @@
       </c>
       <c r="C1005" s="4" t="inlineStr">
         <is>
-          <t>LOPX-705</t>
+          <t>LOPX 705</t>
         </is>
       </c>
       <c r="D1005" s="4" t="inlineStr"/>
@@ -37626,7 +37626,7 @@
       </c>
       <c r="C1006" s="2" t="inlineStr">
         <is>
-          <t>LOPX-707</t>
+          <t>LOPX 707</t>
         </is>
       </c>
       <c r="D1006" s="2" t="inlineStr"/>
@@ -37661,7 +37661,7 @@
       </c>
       <c r="C1007" s="4" t="inlineStr">
         <is>
-          <t>LOPX-707</t>
+          <t>LOPX 707</t>
         </is>
       </c>
       <c r="D1007" s="4" t="inlineStr"/>
@@ -37696,7 +37696,7 @@
       </c>
       <c r="C1008" s="2" t="inlineStr">
         <is>
-          <t>LOPX-707</t>
+          <t>LOPX 707</t>
         </is>
       </c>
       <c r="D1008" s="2" t="inlineStr"/>
@@ -37731,7 +37731,7 @@
       </c>
       <c r="C1009" s="4" t="inlineStr">
         <is>
-          <t>LOPX-707</t>
+          <t>LOPX 707</t>
         </is>
       </c>
       <c r="D1009" s="4" t="inlineStr"/>
@@ -37766,7 +37766,7 @@
       </c>
       <c r="C1010" s="2" t="inlineStr">
         <is>
-          <t>LOPX-707</t>
+          <t>LOPX 707</t>
         </is>
       </c>
       <c r="D1010" s="2" t="inlineStr"/>
@@ -37801,7 +37801,7 @@
       </c>
       <c r="C1011" s="4" t="inlineStr">
         <is>
-          <t>LOPX-709</t>
+          <t>LOPX 709</t>
         </is>
       </c>
       <c r="D1011" s="4" t="inlineStr"/>
@@ -37836,7 +37836,7 @@
       </c>
       <c r="C1012" s="2" t="inlineStr">
         <is>
-          <t>LOPX-709</t>
+          <t>LOPX 709</t>
         </is>
       </c>
       <c r="D1012" s="2" t="inlineStr"/>
@@ -37871,7 +37871,7 @@
       </c>
       <c r="C1013" s="4" t="inlineStr">
         <is>
-          <t>LOPX-709</t>
+          <t>LOPX 709</t>
         </is>
       </c>
       <c r="D1013" s="4" t="inlineStr"/>
@@ -37906,7 +37906,7 @@
       </c>
       <c r="C1014" s="2" t="inlineStr">
         <is>
-          <t>LOPX-709</t>
+          <t>LOPX 709</t>
         </is>
       </c>
       <c r="D1014" s="2" t="inlineStr"/>
@@ -37941,7 +37941,7 @@
       </c>
       <c r="C1015" s="4" t="inlineStr">
         <is>
-          <t>LOPX-709</t>
+          <t>LOPX 709</t>
         </is>
       </c>
       <c r="D1015" s="4" t="inlineStr"/>
@@ -37976,7 +37976,7 @@
       </c>
       <c r="C1016" s="2" t="inlineStr">
         <is>
-          <t>LOPX-710</t>
+          <t>LOPX 710</t>
         </is>
       </c>
       <c r="D1016" s="2" t="inlineStr"/>
@@ -38011,7 +38011,7 @@
       </c>
       <c r="C1017" s="4" t="inlineStr">
         <is>
-          <t>LOPX-710</t>
+          <t>LOPX 710</t>
         </is>
       </c>
       <c r="D1017" s="4" t="inlineStr"/>
@@ -38046,7 +38046,7 @@
       </c>
       <c r="C1018" s="2" t="inlineStr">
         <is>
-          <t>LOPX-710</t>
+          <t>LOPX 710</t>
         </is>
       </c>
       <c r="D1018" s="2" t="inlineStr"/>
@@ -38081,7 +38081,7 @@
       </c>
       <c r="C1019" s="4" t="inlineStr">
         <is>
-          <t>LOPX-710</t>
+          <t>LOPX 710</t>
         </is>
       </c>
       <c r="D1019" s="4" t="inlineStr"/>
@@ -38116,7 +38116,7 @@
       </c>
       <c r="C1020" s="2" t="inlineStr">
         <is>
-          <t>LOPX-710</t>
+          <t>LOPX 710</t>
         </is>
       </c>
       <c r="D1020" s="2" t="inlineStr"/>
@@ -38151,7 +38151,7 @@
       </c>
       <c r="C1021" s="4" t="inlineStr">
         <is>
-          <t>LOPX-711</t>
+          <t>LOPX 711</t>
         </is>
       </c>
       <c r="D1021" s="4" t="inlineStr"/>
@@ -38186,7 +38186,7 @@
       </c>
       <c r="C1022" s="2" t="inlineStr">
         <is>
-          <t>LOPX-711</t>
+          <t>LOPX 711</t>
         </is>
       </c>
       <c r="D1022" s="2" t="inlineStr"/>
@@ -38221,7 +38221,7 @@
       </c>
       <c r="C1023" s="4" t="inlineStr">
         <is>
-          <t>LOPX-711</t>
+          <t>LOPX 711</t>
         </is>
       </c>
       <c r="D1023" s="4" t="inlineStr"/>
@@ -38256,7 +38256,7 @@
       </c>
       <c r="C1024" s="2" t="inlineStr">
         <is>
-          <t>LOPX-711</t>
+          <t>LOPX 711</t>
         </is>
       </c>
       <c r="D1024" s="2" t="inlineStr"/>
@@ -38291,7 +38291,7 @@
       </c>
       <c r="C1025" s="4" t="inlineStr">
         <is>
-          <t>LOPX-711</t>
+          <t>LOPX 711</t>
         </is>
       </c>
       <c r="D1025" s="4" t="inlineStr"/>
@@ -38326,7 +38326,7 @@
       </c>
       <c r="C1026" s="2" t="inlineStr">
         <is>
-          <t>LOPX-713</t>
+          <t>LOPX 713</t>
         </is>
       </c>
       <c r="D1026" s="2" t="inlineStr"/>
@@ -38361,7 +38361,7 @@
       </c>
       <c r="C1027" s="4" t="inlineStr">
         <is>
-          <t>LOPX-713</t>
+          <t>LOPX 713</t>
         </is>
       </c>
       <c r="D1027" s="4" t="inlineStr"/>
@@ -38396,7 +38396,7 @@
       </c>
       <c r="C1028" s="2" t="inlineStr">
         <is>
-          <t>LOPX-713</t>
+          <t>LOPX 713</t>
         </is>
       </c>
       <c r="D1028" s="2" t="inlineStr"/>
@@ -38431,7 +38431,7 @@
       </c>
       <c r="C1029" s="4" t="inlineStr">
         <is>
-          <t>LOPX-713</t>
+          <t>LOPX 713</t>
         </is>
       </c>
       <c r="D1029" s="4" t="inlineStr"/>
@@ -38466,7 +38466,7 @@
       </c>
       <c r="C1030" s="2" t="inlineStr">
         <is>
-          <t>LOPX-713</t>
+          <t>LOPX 713</t>
         </is>
       </c>
       <c r="D1030" s="2" t="inlineStr"/>
@@ -38501,7 +38501,7 @@
       </c>
       <c r="C1031" s="4" t="inlineStr">
         <is>
-          <t>LOPX-714</t>
+          <t>LOPX 714</t>
         </is>
       </c>
       <c r="D1031" s="4" t="inlineStr"/>
@@ -38536,7 +38536,7 @@
       </c>
       <c r="C1032" s="2" t="inlineStr">
         <is>
-          <t>LOPX-714</t>
+          <t>LOPX 714</t>
         </is>
       </c>
       <c r="D1032" s="2" t="inlineStr"/>
@@ -38571,7 +38571,7 @@
       </c>
       <c r="C1033" s="4" t="inlineStr">
         <is>
-          <t>LOPX-714</t>
+          <t>LOPX 714</t>
         </is>
       </c>
       <c r="D1033" s="4" t="inlineStr"/>
@@ -38606,7 +38606,7 @@
       </c>
       <c r="C1034" s="2" t="inlineStr">
         <is>
-          <t>LOPX-714</t>
+          <t>LOPX 714</t>
         </is>
       </c>
       <c r="D1034" s="2" t="inlineStr"/>
@@ -38641,7 +38641,7 @@
       </c>
       <c r="C1035" s="4" t="inlineStr">
         <is>
-          <t>LOPX-714</t>
+          <t>LOPX 714</t>
         </is>
       </c>
       <c r="D1035" s="4" t="inlineStr"/>
@@ -38676,7 +38676,7 @@
       </c>
       <c r="C1036" s="2" t="inlineStr">
         <is>
-          <t>MAB-102</t>
+          <t>MAB 102</t>
         </is>
       </c>
       <c r="D1036" s="2" t="inlineStr"/>
@@ -38711,7 +38711,7 @@
       </c>
       <c r="C1037" s="4" t="inlineStr">
         <is>
-          <t>MAB-102</t>
+          <t>MAB 102</t>
         </is>
       </c>
       <c r="D1037" s="4" t="inlineStr"/>
@@ -38746,7 +38746,7 @@
       </c>
       <c r="C1038" s="2" t="inlineStr">
         <is>
-          <t>MAB-102</t>
+          <t>MAB 102</t>
         </is>
       </c>
       <c r="D1038" s="2" t="inlineStr"/>
@@ -38781,7 +38781,7 @@
       </c>
       <c r="C1039" s="4" t="inlineStr">
         <is>
-          <t>MAB-102</t>
+          <t>MAB 102</t>
         </is>
       </c>
       <c r="D1039" s="4" t="inlineStr"/>
@@ -38816,7 +38816,7 @@
       </c>
       <c r="C1040" s="2" t="inlineStr">
         <is>
-          <t>MAB-102</t>
+          <t>MAB 102</t>
         </is>
       </c>
       <c r="D1040" s="2" t="inlineStr"/>
@@ -38851,7 +38851,7 @@
       </c>
       <c r="C1041" s="4" t="inlineStr">
         <is>
-          <t>MAB-103</t>
+          <t>MAB 103</t>
         </is>
       </c>
       <c r="D1041" s="4" t="inlineStr"/>
@@ -38886,7 +38886,7 @@
       </c>
       <c r="C1042" s="2" t="inlineStr">
         <is>
-          <t>MAB-103</t>
+          <t>MAB 103</t>
         </is>
       </c>
       <c r="D1042" s="2" t="inlineStr"/>
@@ -38921,7 +38921,7 @@
       </c>
       <c r="C1043" s="4" t="inlineStr">
         <is>
-          <t>MAB-103</t>
+          <t>MAB 103</t>
         </is>
       </c>
       <c r="D1043" s="4" t="inlineStr"/>
@@ -38956,7 +38956,7 @@
       </c>
       <c r="C1044" s="2" t="inlineStr">
         <is>
-          <t>MAB-103</t>
+          <t>MAB 103</t>
         </is>
       </c>
       <c r="D1044" s="2" t="inlineStr"/>
@@ -38991,7 +38991,7 @@
       </c>
       <c r="C1045" s="4" t="inlineStr">
         <is>
-          <t>MAB-103</t>
+          <t>MAB 103</t>
         </is>
       </c>
       <c r="D1045" s="4" t="inlineStr"/>
@@ -39026,7 +39026,7 @@
       </c>
       <c r="C1046" s="2" t="inlineStr">
         <is>
-          <t>MAB-104</t>
+          <t>MAB 104</t>
         </is>
       </c>
       <c r="D1046" s="2" t="inlineStr"/>
@@ -39061,7 +39061,7 @@
       </c>
       <c r="C1047" s="4" t="inlineStr">
         <is>
-          <t>MAB-104</t>
+          <t>MAB 104</t>
         </is>
       </c>
       <c r="D1047" s="4" t="inlineStr"/>
@@ -39096,7 +39096,7 @@
       </c>
       <c r="C1048" s="2" t="inlineStr">
         <is>
-          <t>MAB-104</t>
+          <t>MAB 104</t>
         </is>
       </c>
       <c r="D1048" s="2" t="inlineStr"/>
@@ -39131,7 +39131,7 @@
       </c>
       <c r="C1049" s="4" t="inlineStr">
         <is>
-          <t>MAB-104</t>
+          <t>MAB 104</t>
         </is>
       </c>
       <c r="D1049" s="4" t="inlineStr"/>
@@ -39166,7 +39166,7 @@
       </c>
       <c r="C1050" s="2" t="inlineStr">
         <is>
-          <t>MAB-104</t>
+          <t>MAB 104</t>
         </is>
       </c>
       <c r="D1050" s="2" t="inlineStr"/>
@@ -39201,7 +39201,7 @@
       </c>
       <c r="C1051" s="4" t="inlineStr">
         <is>
-          <t>MAB-204</t>
+          <t>MAB 204</t>
         </is>
       </c>
       <c r="D1051" s="4" t="inlineStr"/>
@@ -39236,7 +39236,7 @@
       </c>
       <c r="C1052" s="2" t="inlineStr">
         <is>
-          <t>MAB-204</t>
+          <t>MAB 204</t>
         </is>
       </c>
       <c r="D1052" s="2" t="inlineStr"/>
@@ -39271,7 +39271,7 @@
       </c>
       <c r="C1053" s="4" t="inlineStr">
         <is>
-          <t>MAB-204</t>
+          <t>MAB 204</t>
         </is>
       </c>
       <c r="D1053" s="4" t="inlineStr"/>
@@ -39306,7 +39306,7 @@
       </c>
       <c r="C1054" s="2" t="inlineStr">
         <is>
-          <t>MAB-204</t>
+          <t>MAB 204</t>
         </is>
       </c>
       <c r="D1054" s="2" t="inlineStr"/>
@@ -39341,7 +39341,7 @@
       </c>
       <c r="C1055" s="4" t="inlineStr">
         <is>
-          <t>MAB-204</t>
+          <t>MAB 204</t>
         </is>
       </c>
       <c r="D1055" s="4" t="inlineStr"/>
@@ -39376,7 +39376,7 @@
       </c>
       <c r="C1056" s="2" t="inlineStr">
         <is>
-          <t>MAB-205</t>
+          <t>MAB 205</t>
         </is>
       </c>
       <c r="D1056" s="2" t="inlineStr"/>
@@ -39411,7 +39411,7 @@
       </c>
       <c r="C1057" s="4" t="inlineStr">
         <is>
-          <t>MAB-205</t>
+          <t>MAB 205</t>
         </is>
       </c>
       <c r="D1057" s="4" t="inlineStr"/>
@@ -39446,7 +39446,7 @@
       </c>
       <c r="C1058" s="2" t="inlineStr">
         <is>
-          <t>MAB-205</t>
+          <t>MAB 205</t>
         </is>
       </c>
       <c r="D1058" s="2" t="inlineStr"/>
@@ -39481,7 +39481,7 @@
       </c>
       <c r="C1059" s="4" t="inlineStr">
         <is>
-          <t>MAB-205</t>
+          <t>MAB 205</t>
         </is>
       </c>
       <c r="D1059" s="4" t="inlineStr"/>
@@ -39516,7 +39516,7 @@
       </c>
       <c r="C1060" s="2" t="inlineStr">
         <is>
-          <t>MAB-205</t>
+          <t>MAB 205</t>
         </is>
       </c>
       <c r="D1060" s="2" t="inlineStr"/>
@@ -39551,7 +39551,7 @@
       </c>
       <c r="C1061" s="4" t="inlineStr">
         <is>
-          <t>MAB-206</t>
+          <t>MAB 206</t>
         </is>
       </c>
       <c r="D1061" s="4" t="inlineStr"/>
@@ -39586,7 +39586,7 @@
       </c>
       <c r="C1062" s="2" t="inlineStr">
         <is>
-          <t>MAB-206</t>
+          <t>MAB 206</t>
         </is>
       </c>
       <c r="D1062" s="2" t="inlineStr"/>
@@ -39621,7 +39621,7 @@
       </c>
       <c r="C1063" s="4" t="inlineStr">
         <is>
-          <t>MAB-206</t>
+          <t>MAB 206</t>
         </is>
       </c>
       <c r="D1063" s="4" t="inlineStr"/>
@@ -39656,7 +39656,7 @@
       </c>
       <c r="C1064" s="2" t="inlineStr">
         <is>
-          <t>MAB-206</t>
+          <t>MAB 206</t>
         </is>
       </c>
       <c r="D1064" s="2" t="inlineStr"/>
@@ -39691,7 +39691,7 @@
       </c>
       <c r="C1065" s="4" t="inlineStr">
         <is>
-          <t>MAB-206</t>
+          <t>MAB 206</t>
         </is>
       </c>
       <c r="D1065" s="4" t="inlineStr"/>
@@ -39726,7 +39726,7 @@
       </c>
       <c r="C1066" s="2" t="inlineStr">
         <is>
-          <t>MAB-207</t>
+          <t>MAB 207</t>
         </is>
       </c>
       <c r="D1066" s="2" t="inlineStr"/>
@@ -39761,7 +39761,7 @@
       </c>
       <c r="C1067" s="4" t="inlineStr">
         <is>
-          <t>MAB-207</t>
+          <t>MAB 207</t>
         </is>
       </c>
       <c r="D1067" s="4" t="inlineStr"/>
@@ -39796,7 +39796,7 @@
       </c>
       <c r="C1068" s="2" t="inlineStr">
         <is>
-          <t>MAB-207</t>
+          <t>MAB 207</t>
         </is>
       </c>
       <c r="D1068" s="2" t="inlineStr"/>
@@ -39831,7 +39831,7 @@
       </c>
       <c r="C1069" s="4" t="inlineStr">
         <is>
-          <t>MAB-207</t>
+          <t>MAB 207</t>
         </is>
       </c>
       <c r="D1069" s="4" t="inlineStr"/>
@@ -39866,7 +39866,7 @@
       </c>
       <c r="C1070" s="2" t="inlineStr">
         <is>
-          <t>MAB-207</t>
+          <t>MAB 207</t>
         </is>
       </c>
       <c r="D1070" s="2" t="inlineStr"/>
@@ -39901,7 +39901,7 @@
       </c>
       <c r="C1071" s="4" t="inlineStr">
         <is>
-          <t>MAB-209</t>
+          <t>MAB 209</t>
         </is>
       </c>
       <c r="D1071" s="4" t="inlineStr"/>
@@ -39936,7 +39936,7 @@
       </c>
       <c r="C1072" s="2" t="inlineStr">
         <is>
-          <t>MAB-209</t>
+          <t>MAB 209</t>
         </is>
       </c>
       <c r="D1072" s="2" t="inlineStr"/>
@@ -39971,7 +39971,7 @@
       </c>
       <c r="C1073" s="4" t="inlineStr">
         <is>
-          <t>MAB-209</t>
+          <t>MAB 209</t>
         </is>
       </c>
       <c r="D1073" s="4" t="inlineStr"/>
@@ -40006,7 +40006,7 @@
       </c>
       <c r="C1074" s="2" t="inlineStr">
         <is>
-          <t>MAB-209</t>
+          <t>MAB 209</t>
         </is>
       </c>
       <c r="D1074" s="2" t="inlineStr"/>
@@ -40041,7 +40041,7 @@
       </c>
       <c r="C1075" s="4" t="inlineStr">
         <is>
-          <t>MAB-209</t>
+          <t>MAB 209</t>
         </is>
       </c>
       <c r="D1075" s="4" t="inlineStr"/>
@@ -40076,7 +40076,7 @@
       </c>
       <c r="C1076" s="2" t="inlineStr">
         <is>
-          <t>MAPX-204</t>
+          <t>MAPX 204</t>
         </is>
       </c>
       <c r="D1076" s="2" t="inlineStr"/>
@@ -40111,7 +40111,7 @@
       </c>
       <c r="C1077" s="4" t="inlineStr">
         <is>
-          <t>MAPX-204</t>
+          <t>MAPX 204</t>
         </is>
       </c>
       <c r="D1077" s="4" t="inlineStr"/>
@@ -40146,7 +40146,7 @@
       </c>
       <c r="C1078" s="2" t="inlineStr">
         <is>
-          <t>MAPX-204</t>
+          <t>MAPX 204</t>
         </is>
       </c>
       <c r="D1078" s="2" t="inlineStr"/>
@@ -40181,7 +40181,7 @@
       </c>
       <c r="C1079" s="4" t="inlineStr">
         <is>
-          <t>MAPX-204</t>
+          <t>MAPX 204</t>
         </is>
       </c>
       <c r="D1079" s="4" t="inlineStr"/>
@@ -40216,7 +40216,7 @@
       </c>
       <c r="C1080" s="2" t="inlineStr">
         <is>
-          <t>MAPX-204</t>
+          <t>MAPX 204</t>
         </is>
       </c>
       <c r="D1080" s="2" t="inlineStr"/>
@@ -40251,7 +40251,7 @@
       </c>
       <c r="C1081" s="4" t="inlineStr">
         <is>
-          <t>MAPX-205</t>
+          <t>MAPX 205</t>
         </is>
       </c>
       <c r="D1081" s="4" t="inlineStr"/>
@@ -40286,7 +40286,7 @@
       </c>
       <c r="C1082" s="2" t="inlineStr">
         <is>
-          <t>MAPX-205</t>
+          <t>MAPX 205</t>
         </is>
       </c>
       <c r="D1082" s="2" t="inlineStr"/>
@@ -40321,7 +40321,7 @@
       </c>
       <c r="C1083" s="4" t="inlineStr">
         <is>
-          <t>MAPX-205</t>
+          <t>MAPX 205</t>
         </is>
       </c>
       <c r="D1083" s="4" t="inlineStr"/>
@@ -40356,7 +40356,7 @@
       </c>
       <c r="C1084" s="2" t="inlineStr">
         <is>
-          <t>MAPX-205</t>
+          <t>MAPX 205</t>
         </is>
       </c>
       <c r="D1084" s="2" t="inlineStr"/>
@@ -40391,7 +40391,7 @@
       </c>
       <c r="C1085" s="4" t="inlineStr">
         <is>
-          <t>MAPX-205</t>
+          <t>MAPX 205</t>
         </is>
       </c>
       <c r="D1085" s="4" t="inlineStr"/>
@@ -40426,7 +40426,7 @@
       </c>
       <c r="C1086" s="2" t="inlineStr">
         <is>
-          <t>MAPX-207</t>
+          <t>MAPX 207</t>
         </is>
       </c>
       <c r="D1086" s="2" t="inlineStr"/>
@@ -40461,7 +40461,7 @@
       </c>
       <c r="C1087" s="4" t="inlineStr">
         <is>
-          <t>MAPX-207</t>
+          <t>MAPX 207</t>
         </is>
       </c>
       <c r="D1087" s="4" t="inlineStr"/>
@@ -40496,7 +40496,7 @@
       </c>
       <c r="C1088" s="2" t="inlineStr">
         <is>
-          <t>MAPX-207</t>
+          <t>MAPX 207</t>
         </is>
       </c>
       <c r="D1088" s="2" t="inlineStr"/>
@@ -40531,7 +40531,7 @@
       </c>
       <c r="C1089" s="4" t="inlineStr">
         <is>
-          <t>MAPX-210</t>
+          <t>MAPX 210</t>
         </is>
       </c>
       <c r="D1089" s="4" t="inlineStr"/>
@@ -40566,7 +40566,7 @@
       </c>
       <c r="C1090" s="2" t="inlineStr">
         <is>
-          <t>MAPX-210</t>
+          <t>MAPX 210</t>
         </is>
       </c>
       <c r="D1090" s="2" t="inlineStr"/>
@@ -40601,7 +40601,7 @@
       </c>
       <c r="C1091" s="4" t="inlineStr">
         <is>
-          <t>MAPX-210</t>
+          <t>MAPX 210</t>
         </is>
       </c>
       <c r="D1091" s="4" t="inlineStr"/>
@@ -40636,7 +40636,7 @@
       </c>
       <c r="C1092" s="2" t="inlineStr">
         <is>
-          <t>MAPX-210</t>
+          <t>MAPX 210</t>
         </is>
       </c>
       <c r="D1092" s="2" t="inlineStr"/>
@@ -40671,7 +40671,7 @@
       </c>
       <c r="C1093" s="4" t="inlineStr">
         <is>
-          <t>MAPX-210</t>
+          <t>MAPX 210</t>
         </is>
       </c>
       <c r="D1093" s="4" t="inlineStr"/>
@@ -40706,7 +40706,7 @@
       </c>
       <c r="C1094" s="2" t="inlineStr">
         <is>
-          <t>MAPX-309</t>
+          <t>MAPX 309</t>
         </is>
       </c>
       <c r="D1094" s="2" t="inlineStr"/>
@@ -40741,7 +40741,7 @@
       </c>
       <c r="C1095" s="4" t="inlineStr">
         <is>
-          <t>MAPX-309</t>
+          <t>MAPX 309</t>
         </is>
       </c>
       <c r="D1095" s="4" t="inlineStr"/>
@@ -40776,7 +40776,7 @@
       </c>
       <c r="C1096" s="2" t="inlineStr">
         <is>
-          <t>MAPX-309</t>
+          <t>MAPX 309</t>
         </is>
       </c>
       <c r="D1096" s="2" t="inlineStr"/>
@@ -40811,7 +40811,7 @@
       </c>
       <c r="C1097" s="4" t="inlineStr">
         <is>
-          <t>MAPX-309</t>
+          <t>MAPX 309</t>
         </is>
       </c>
       <c r="D1097" s="4" t="inlineStr"/>
@@ -40846,7 +40846,7 @@
       </c>
       <c r="C1098" s="2" t="inlineStr">
         <is>
-          <t>MAPX-309</t>
+          <t>MAPX 309</t>
         </is>
       </c>
       <c r="D1098" s="2" t="inlineStr"/>
@@ -40881,7 +40881,7 @@
       </c>
       <c r="C1099" s="4" t="inlineStr">
         <is>
-          <t>MAPX-313</t>
+          <t>MAPX 313</t>
         </is>
       </c>
       <c r="D1099" s="4" t="inlineStr"/>
@@ -40916,7 +40916,7 @@
       </c>
       <c r="C1100" s="2" t="inlineStr">
         <is>
-          <t>MAPX-313</t>
+          <t>MAPX 313</t>
         </is>
       </c>
       <c r="D1100" s="2" t="inlineStr"/>
@@ -40951,7 +40951,7 @@
       </c>
       <c r="C1101" s="4" t="inlineStr">
         <is>
-          <t>MAPX-313</t>
+          <t>MAPX 313</t>
         </is>
       </c>
       <c r="D1101" s="4" t="inlineStr"/>
@@ -40986,7 +40986,7 @@
       </c>
       <c r="C1102" s="2" t="inlineStr">
         <is>
-          <t>MAPX-313</t>
+          <t>MAPX 313</t>
         </is>
       </c>
       <c r="D1102" s="2" t="inlineStr"/>
@@ -41021,7 +41021,7 @@
       </c>
       <c r="C1103" s="4" t="inlineStr">
         <is>
-          <t>MAPX-313</t>
+          <t>MAPX 313</t>
         </is>
       </c>
       <c r="D1103" s="4" t="inlineStr"/>
@@ -41056,7 +41056,7 @@
       </c>
       <c r="C1104" s="2" t="inlineStr">
         <is>
-          <t>MFPX-307</t>
+          <t>MFPX 307</t>
         </is>
       </c>
       <c r="D1104" s="2" t="inlineStr"/>
@@ -41091,7 +41091,7 @@
       </c>
       <c r="C1105" s="4" t="inlineStr">
         <is>
-          <t>MFPX-307</t>
+          <t>MFPX 307</t>
         </is>
       </c>
       <c r="D1105" s="4" t="inlineStr"/>
@@ -41126,7 +41126,7 @@
       </c>
       <c r="C1106" s="2" t="inlineStr">
         <is>
-          <t>MFPX-307</t>
+          <t>MFPX 307</t>
         </is>
       </c>
       <c r="D1106" s="2" t="inlineStr"/>
@@ -41161,7 +41161,7 @@
       </c>
       <c r="C1107" s="4" t="inlineStr">
         <is>
-          <t>MFPX-307</t>
+          <t>MFPX 307</t>
         </is>
       </c>
       <c r="D1107" s="4" t="inlineStr"/>
@@ -41196,7 +41196,7 @@
       </c>
       <c r="C1108" s="2" t="inlineStr">
         <is>
-          <t>MMB-304</t>
+          <t>MMB 304</t>
         </is>
       </c>
       <c r="D1108" s="2" t="inlineStr"/>
@@ -41231,7 +41231,7 @@
       </c>
       <c r="C1109" s="4" t="inlineStr">
         <is>
-          <t>MMB-304</t>
+          <t>MMB 304</t>
         </is>
       </c>
       <c r="D1109" s="4" t="inlineStr"/>
@@ -41266,7 +41266,7 @@
       </c>
       <c r="C1110" s="2" t="inlineStr">
         <is>
-          <t>MMB-304</t>
+          <t>MMB 304</t>
         </is>
       </c>
       <c r="D1110" s="2" t="inlineStr"/>
@@ -41301,7 +41301,7 @@
       </c>
       <c r="C1111" s="4" t="inlineStr">
         <is>
-          <t>MMB-304</t>
+          <t>MMB 304</t>
         </is>
       </c>
       <c r="D1111" s="4" t="inlineStr"/>
@@ -41336,7 +41336,7 @@
       </c>
       <c r="C1112" s="2" t="inlineStr">
         <is>
-          <t>MMB-305</t>
+          <t>MMB 305</t>
         </is>
       </c>
       <c r="D1112" s="2" t="inlineStr"/>
@@ -41371,7 +41371,7 @@
       </c>
       <c r="C1113" s="4" t="inlineStr">
         <is>
-          <t>MMB-305</t>
+          <t>MMB 305</t>
         </is>
       </c>
       <c r="D1113" s="4" t="inlineStr"/>
@@ -41406,7 +41406,7 @@
       </c>
       <c r="C1114" s="2" t="inlineStr">
         <is>
-          <t>MMB-305</t>
+          <t>MMB 305</t>
         </is>
       </c>
       <c r="D1114" s="2" t="inlineStr"/>
@@ -41441,7 +41441,7 @@
       </c>
       <c r="C1115" s="4" t="inlineStr">
         <is>
-          <t>MMB-305</t>
+          <t>MMB 305</t>
         </is>
       </c>
       <c r="D1115" s="4" t="inlineStr"/>
@@ -41476,7 +41476,7 @@
       </c>
       <c r="C1116" s="2" t="inlineStr">
         <is>
-          <t>MMPX-303</t>
+          <t>MMPX 303</t>
         </is>
       </c>
       <c r="D1116" s="2" t="inlineStr"/>
@@ -41511,7 +41511,7 @@
       </c>
       <c r="C1117" s="4" t="inlineStr">
         <is>
-          <t>MMPX-303</t>
+          <t>MMPX 303</t>
         </is>
       </c>
       <c r="D1117" s="4" t="inlineStr"/>
@@ -41546,7 +41546,7 @@
       </c>
       <c r="C1118" s="2" t="inlineStr">
         <is>
-          <t>MMPX-303</t>
+          <t>MMPX 303</t>
         </is>
       </c>
       <c r="D1118" s="2" t="inlineStr"/>
@@ -41581,7 +41581,7 @@
       </c>
       <c r="C1119" s="4" t="inlineStr">
         <is>
-          <t>MMPX-303</t>
+          <t>MMPX 303</t>
         </is>
       </c>
       <c r="D1119" s="4" t="inlineStr"/>
@@ -41616,7 +41616,7 @@
       </c>
       <c r="C1120" s="2" t="inlineStr">
         <is>
-          <t>MMPX-304</t>
+          <t>MMPX 304</t>
         </is>
       </c>
       <c r="D1120" s="2" t="inlineStr"/>
@@ -41651,7 +41651,7 @@
       </c>
       <c r="C1121" s="4" t="inlineStr">
         <is>
-          <t>MMPX-304</t>
+          <t>MMPX 304</t>
         </is>
       </c>
       <c r="D1121" s="4" t="inlineStr"/>
@@ -41686,7 +41686,7 @@
       </c>
       <c r="C1122" s="2" t="inlineStr">
         <is>
-          <t>MMPX-304</t>
+          <t>MMPX 304</t>
         </is>
       </c>
       <c r="D1122" s="2" t="inlineStr"/>
@@ -41721,7 +41721,7 @@
       </c>
       <c r="C1123" s="4" t="inlineStr">
         <is>
-          <t>MMPX-304</t>
+          <t>MMPX 304</t>
         </is>
       </c>
       <c r="D1123" s="4" t="inlineStr"/>
@@ -41756,7 +41756,7 @@
       </c>
       <c r="C1124" s="2" t="inlineStr">
         <is>
-          <t>MMPX-403</t>
+          <t>MMPX 403</t>
         </is>
       </c>
       <c r="D1124" s="2" t="inlineStr"/>
@@ -41791,7 +41791,7 @@
       </c>
       <c r="C1125" s="4" t="inlineStr">
         <is>
-          <t>MMPX-403</t>
+          <t>MMPX 403</t>
         </is>
       </c>
       <c r="D1125" s="4" t="inlineStr"/>
@@ -41826,7 +41826,7 @@
       </c>
       <c r="C1126" s="2" t="inlineStr">
         <is>
-          <t>MMPX-403</t>
+          <t>MMPX 403</t>
         </is>
       </c>
       <c r="D1126" s="2" t="inlineStr"/>
@@ -41861,7 +41861,7 @@
       </c>
       <c r="C1127" s="4" t="inlineStr">
         <is>
-          <t>MMPX-403</t>
+          <t>MMPX 403</t>
         </is>
       </c>
       <c r="D1127" s="4" t="inlineStr"/>
@@ -41896,7 +41896,7 @@
       </c>
       <c r="C1128" s="2" t="inlineStr">
         <is>
-          <t>MMPX-404</t>
+          <t>MMPX 404</t>
         </is>
       </c>
       <c r="D1128" s="2" t="inlineStr"/>
@@ -41931,7 +41931,7 @@
       </c>
       <c r="C1129" s="4" t="inlineStr">
         <is>
-          <t>MMPX-404</t>
+          <t>MMPX 404</t>
         </is>
       </c>
       <c r="D1129" s="4" t="inlineStr"/>
@@ -41966,7 +41966,7 @@
       </c>
       <c r="C1130" s="2" t="inlineStr">
         <is>
-          <t>MMPX-404</t>
+          <t>MMPX 404</t>
         </is>
       </c>
       <c r="D1130" s="2" t="inlineStr"/>
@@ -42001,7 +42001,7 @@
       </c>
       <c r="C1131" s="4" t="inlineStr">
         <is>
-          <t>MMPX-404</t>
+          <t>MMPX 404</t>
         </is>
       </c>
       <c r="D1131" s="4" t="inlineStr"/>
@@ -42036,7 +42036,7 @@
       </c>
       <c r="C1132" s="2" t="inlineStr">
         <is>
-          <t>MOPX-204</t>
+          <t>MOPX 204</t>
         </is>
       </c>
       <c r="D1132" s="2" t="inlineStr"/>
@@ -42071,7 +42071,7 @@
       </c>
       <c r="C1133" s="4" t="inlineStr">
         <is>
-          <t>MOPX-204</t>
+          <t>MOPX 204</t>
         </is>
       </c>
       <c r="D1133" s="4" t="inlineStr"/>
@@ -42106,7 +42106,7 @@
       </c>
       <c r="C1134" s="2" t="inlineStr">
         <is>
-          <t>MOPX-204</t>
+          <t>MOPX 204</t>
         </is>
       </c>
       <c r="D1134" s="2" t="inlineStr"/>
@@ -42141,7 +42141,7 @@
       </c>
       <c r="C1135" s="4" t="inlineStr">
         <is>
-          <t>MOPX-204</t>
+          <t>MOPX 204</t>
         </is>
       </c>
       <c r="D1135" s="4" t="inlineStr"/>
@@ -42176,7 +42176,7 @@
       </c>
       <c r="C1136" s="2" t="inlineStr">
         <is>
-          <t>MOPX-204</t>
+          <t>MOPX 204</t>
         </is>
       </c>
       <c r="D1136" s="2" t="inlineStr"/>
@@ -42211,7 +42211,7 @@
       </c>
       <c r="C1137" s="4" t="inlineStr">
         <is>
-          <t>MOPX-205</t>
+          <t>MOPX 205</t>
         </is>
       </c>
       <c r="D1137" s="4" t="inlineStr"/>
@@ -42246,7 +42246,7 @@
       </c>
       <c r="C1138" s="2" t="inlineStr">
         <is>
-          <t>MOPX-205</t>
+          <t>MOPX 205</t>
         </is>
       </c>
       <c r="D1138" s="2" t="inlineStr"/>
@@ -42281,7 +42281,7 @@
       </c>
       <c r="C1139" s="4" t="inlineStr">
         <is>
-          <t>MOPX-205</t>
+          <t>MOPX 205</t>
         </is>
       </c>
       <c r="D1139" s="4" t="inlineStr"/>
@@ -42316,7 +42316,7 @@
       </c>
       <c r="C1140" s="2" t="inlineStr">
         <is>
-          <t>MOPX-205</t>
+          <t>MOPX 205</t>
         </is>
       </c>
       <c r="D1140" s="2" t="inlineStr"/>
@@ -42351,7 +42351,7 @@
       </c>
       <c r="C1141" s="4" t="inlineStr">
         <is>
-          <t>MOPX-205</t>
+          <t>MOPX 205</t>
         </is>
       </c>
       <c r="D1141" s="4" t="inlineStr"/>
@@ -42386,7 +42386,7 @@
       </c>
       <c r="C1142" s="2" t="inlineStr">
         <is>
-          <t>MOPX-207</t>
+          <t>MOPX 207</t>
         </is>
       </c>
       <c r="D1142" s="2" t="inlineStr"/>
@@ -42421,7 +42421,7 @@
       </c>
       <c r="C1143" s="4" t="inlineStr">
         <is>
-          <t>MOPX-207</t>
+          <t>MOPX 207</t>
         </is>
       </c>
       <c r="D1143" s="4" t="inlineStr"/>
@@ -42456,7 +42456,7 @@
       </c>
       <c r="C1144" s="2" t="inlineStr">
         <is>
-          <t>MOPX-207</t>
+          <t>MOPX 207</t>
         </is>
       </c>
       <c r="D1144" s="2" t="inlineStr"/>
@@ -42491,7 +42491,7 @@
       </c>
       <c r="C1145" s="4" t="inlineStr">
         <is>
-          <t>MOPX-209</t>
+          <t>MOPX 209</t>
         </is>
       </c>
       <c r="D1145" s="4" t="inlineStr"/>
@@ -42526,7 +42526,7 @@
       </c>
       <c r="C1146" s="2" t="inlineStr">
         <is>
-          <t>MOPX-209</t>
+          <t>MOPX 209</t>
         </is>
       </c>
       <c r="D1146" s="2" t="inlineStr"/>
@@ -42561,7 +42561,7 @@
       </c>
       <c r="C1147" s="4" t="inlineStr">
         <is>
-          <t>MOPX-209</t>
+          <t>MOPX 209</t>
         </is>
       </c>
       <c r="D1147" s="4" t="inlineStr"/>
@@ -42596,7 +42596,7 @@
       </c>
       <c r="C1148" s="2" t="inlineStr">
         <is>
-          <t>MOPX-209</t>
+          <t>MOPX 209</t>
         </is>
       </c>
       <c r="D1148" s="2" t="inlineStr"/>
@@ -42631,7 +42631,7 @@
       </c>
       <c r="C1149" s="4" t="inlineStr">
         <is>
-          <t>MOPX-209</t>
+          <t>MOPX 209</t>
         </is>
       </c>
       <c r="D1149" s="4" t="inlineStr"/>
@@ -42666,7 +42666,7 @@
       </c>
       <c r="C1150" s="2" t="inlineStr">
         <is>
-          <t>MOPX-210</t>
+          <t>MOPX 210</t>
         </is>
       </c>
       <c r="D1150" s="2" t="inlineStr"/>
@@ -42701,7 +42701,7 @@
       </c>
       <c r="C1151" s="4" t="inlineStr">
         <is>
-          <t>MOPX-210</t>
+          <t>MOPX 210</t>
         </is>
       </c>
       <c r="D1151" s="4" t="inlineStr"/>
@@ -42736,7 +42736,7 @@
       </c>
       <c r="C1152" s="2" t="inlineStr">
         <is>
-          <t>MOPX-210</t>
+          <t>MOPX 210</t>
         </is>
       </c>
       <c r="D1152" s="2" t="inlineStr"/>
@@ -42771,7 +42771,7 @@
       </c>
       <c r="C1153" s="4" t="inlineStr">
         <is>
-          <t>MOPX-210</t>
+          <t>MOPX 210</t>
         </is>
       </c>
       <c r="D1153" s="4" t="inlineStr"/>
@@ -42806,7 +42806,7 @@
       </c>
       <c r="C1154" s="2" t="inlineStr">
         <is>
-          <t>MOPX-210</t>
+          <t>MOPX 210</t>
         </is>
       </c>
       <c r="D1154" s="2" t="inlineStr"/>
@@ -42841,7 +42841,7 @@
       </c>
       <c r="C1155" s="4" t="inlineStr">
         <is>
-          <t>MOPX-213</t>
+          <t>MOPX 213</t>
         </is>
       </c>
       <c r="D1155" s="4" t="inlineStr"/>
@@ -42876,7 +42876,7 @@
       </c>
       <c r="C1156" s="2" t="inlineStr">
         <is>
-          <t>MOPX-213</t>
+          <t>MOPX 213</t>
         </is>
       </c>
       <c r="D1156" s="2" t="inlineStr"/>
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C1157" s="4" t="inlineStr">
         <is>
-          <t>MOPX-213</t>
+          <t>MOPX 213</t>
         </is>
       </c>
       <c r="D1157" s="4" t="inlineStr"/>
@@ -42946,7 +42946,7 @@
       </c>
       <c r="C1158" s="2" t="inlineStr">
         <is>
-          <t>MOPX-213</t>
+          <t>MOPX 213</t>
         </is>
       </c>
       <c r="D1158" s="2" t="inlineStr"/>
@@ -42981,7 +42981,7 @@
       </c>
       <c r="C1159" s="4" t="inlineStr">
         <is>
-          <t>MOPX-213</t>
+          <t>MOPX 213</t>
         </is>
       </c>
       <c r="D1159" s="4" t="inlineStr"/>
@@ -43016,7 +43016,7 @@
       </c>
       <c r="C1160" s="2" t="inlineStr">
         <is>
-          <t>MOPX-309</t>
+          <t>MOPX 309</t>
         </is>
       </c>
       <c r="D1160" s="2" t="inlineStr"/>
@@ -43051,7 +43051,7 @@
       </c>
       <c r="C1161" s="4" t="inlineStr">
         <is>
-          <t>MOPX-309</t>
+          <t>MOPX 309</t>
         </is>
       </c>
       <c r="D1161" s="4" t="inlineStr"/>
@@ -43086,7 +43086,7 @@
       </c>
       <c r="C1162" s="2" t="inlineStr">
         <is>
-          <t>MOPX-309</t>
+          <t>MOPX 309</t>
         </is>
       </c>
       <c r="D1162" s="2" t="inlineStr"/>
@@ -43121,7 +43121,7 @@
       </c>
       <c r="C1163" s="4" t="inlineStr">
         <is>
-          <t>MOPX-309</t>
+          <t>MOPX 309</t>
         </is>
       </c>
       <c r="D1163" s="4" t="inlineStr"/>
@@ -43156,7 +43156,7 @@
       </c>
       <c r="C1164" s="2" t="inlineStr">
         <is>
-          <t>MOPX-309</t>
+          <t>MOPX 309</t>
         </is>
       </c>
       <c r="D1164" s="2" t="inlineStr"/>
@@ -43191,7 +43191,7 @@
       </c>
       <c r="C1165" s="4" t="inlineStr">
         <is>
-          <t>MOPX-310</t>
+          <t>MOPX 310</t>
         </is>
       </c>
       <c r="D1165" s="4" t="inlineStr"/>
@@ -43226,7 +43226,7 @@
       </c>
       <c r="C1166" s="2" t="inlineStr">
         <is>
-          <t>MOPX-310</t>
+          <t>MOPX 310</t>
         </is>
       </c>
       <c r="D1166" s="2" t="inlineStr"/>
@@ -43261,7 +43261,7 @@
       </c>
       <c r="C1167" s="4" t="inlineStr">
         <is>
-          <t>MOPX-310</t>
+          <t>MOPX 310</t>
         </is>
       </c>
       <c r="D1167" s="4" t="inlineStr"/>
@@ -43296,7 +43296,7 @@
       </c>
       <c r="C1168" s="2" t="inlineStr">
         <is>
-          <t>MOPX-310</t>
+          <t>MOPX 310</t>
         </is>
       </c>
       <c r="D1168" s="2" t="inlineStr"/>
@@ -43331,7 +43331,7 @@
       </c>
       <c r="C1169" s="4" t="inlineStr">
         <is>
-          <t>MOPX-310</t>
+          <t>MOPX 310</t>
         </is>
       </c>
       <c r="D1169" s="4" t="inlineStr"/>
@@ -43366,7 +43366,7 @@
       </c>
       <c r="C1170" s="2" t="inlineStr">
         <is>
-          <t>MOPX-313</t>
+          <t>MOPX 313</t>
         </is>
       </c>
       <c r="D1170" s="2" t="inlineStr"/>
@@ -43401,7 +43401,7 @@
       </c>
       <c r="C1171" s="4" t="inlineStr">
         <is>
-          <t>MOPX-313</t>
+          <t>MOPX 313</t>
         </is>
       </c>
       <c r="D1171" s="4" t="inlineStr"/>
@@ -43436,7 +43436,7 @@
       </c>
       <c r="C1172" s="2" t="inlineStr">
         <is>
-          <t>MOPX-313</t>
+          <t>MOPX 313</t>
         </is>
       </c>
       <c r="D1172" s="2" t="inlineStr"/>
@@ -43471,7 +43471,7 @@
       </c>
       <c r="C1173" s="4" t="inlineStr">
         <is>
-          <t>MOPX-313</t>
+          <t>MOPX 313</t>
         </is>
       </c>
       <c r="D1173" s="4" t="inlineStr"/>
@@ -43506,7 +43506,7 @@
       </c>
       <c r="C1174" s="2" t="inlineStr">
         <is>
-          <t>MOPX-313</t>
+          <t>MOPX 313</t>
         </is>
       </c>
       <c r="D1174" s="2" t="inlineStr"/>
@@ -43541,7 +43541,7 @@
       </c>
       <c r="C1175" s="4" t="inlineStr">
         <is>
-          <t>MSPX-303</t>
+          <t>MSPX 303</t>
         </is>
       </c>
       <c r="D1175" s="4" t="inlineStr"/>
@@ -43576,7 +43576,7 @@
       </c>
       <c r="C1176" s="2" t="inlineStr">
         <is>
-          <t>MSPX-303</t>
+          <t>MSPX 303</t>
         </is>
       </c>
       <c r="D1176" s="2" t="inlineStr"/>
@@ -43611,7 +43611,7 @@
       </c>
       <c r="C1177" s="4" t="inlineStr">
         <is>
-          <t>MSPX-303</t>
+          <t>MSPX 303</t>
         </is>
       </c>
       <c r="D1177" s="4" t="inlineStr"/>
@@ -43646,7 +43646,7 @@
       </c>
       <c r="C1178" s="2" t="inlineStr">
         <is>
-          <t>MSPX-303</t>
+          <t>MSPX 303</t>
         </is>
       </c>
       <c r="D1178" s="2" t="inlineStr"/>
@@ -43681,7 +43681,7 @@
       </c>
       <c r="C1179" s="4" t="inlineStr">
         <is>
-          <t>MSPX-403</t>
+          <t>MSPX 403</t>
         </is>
       </c>
       <c r="D1179" s="4" t="inlineStr"/>
@@ -43716,7 +43716,7 @@
       </c>
       <c r="C1180" s="2" t="inlineStr">
         <is>
-          <t>MSPX-403</t>
+          <t>MSPX 403</t>
         </is>
       </c>
       <c r="D1180" s="2" t="inlineStr"/>
@@ -43751,7 +43751,7 @@
       </c>
       <c r="C1181" s="4" t="inlineStr">
         <is>
-          <t>MSPX-403</t>
+          <t>MSPX 403</t>
         </is>
       </c>
       <c r="D1181" s="4" t="inlineStr"/>
@@ -43786,7 +43786,7 @@
       </c>
       <c r="C1182" s="2" t="inlineStr">
         <is>
-          <t>MSPX-403</t>
+          <t>MSPX 403</t>
         </is>
       </c>
       <c r="D1182" s="2" t="inlineStr"/>
@@ -43821,7 +43821,7 @@
       </c>
       <c r="C1183" s="4" t="inlineStr">
         <is>
-          <t>PA-600</t>
+          <t>PA 600</t>
         </is>
       </c>
       <c r="D1183" s="4" t="inlineStr"/>
@@ -43856,7 +43856,7 @@
       </c>
       <c r="C1184" s="2" t="inlineStr">
         <is>
-          <t>PA-600</t>
+          <t>PA 600</t>
         </is>
       </c>
       <c r="D1184" s="2" t="inlineStr"/>
@@ -43891,7 +43891,7 @@
       </c>
       <c r="C1185" s="4" t="inlineStr">
         <is>
-          <t>PA-600</t>
+          <t>PA 600</t>
         </is>
       </c>
       <c r="D1185" s="4" t="inlineStr"/>
@@ -43926,7 +43926,7 @@
       </c>
       <c r="C1186" s="2" t="inlineStr">
         <is>
-          <t>PA-600</t>
+          <t>PA 600</t>
         </is>
       </c>
       <c r="D1186" s="2" t="inlineStr"/>
@@ -43961,7 +43961,7 @@
       </c>
       <c r="C1187" s="4" t="inlineStr">
         <is>
-          <t>PA-605</t>
+          <t>PA 605</t>
         </is>
       </c>
       <c r="D1187" s="4" t="inlineStr"/>
@@ -43996,7 +43996,7 @@
       </c>
       <c r="C1188" s="2" t="inlineStr">
         <is>
-          <t>PA-605</t>
+          <t>PA 605</t>
         </is>
       </c>
       <c r="D1188" s="2" t="inlineStr"/>
@@ -44031,7 +44031,7 @@
       </c>
       <c r="C1189" s="4" t="inlineStr">
         <is>
-          <t>PA-605</t>
+          <t>PA 605</t>
         </is>
       </c>
       <c r="D1189" s="4" t="inlineStr"/>
@@ -44066,7 +44066,7 @@
       </c>
       <c r="C1190" s="2" t="inlineStr">
         <is>
-          <t>PA-605</t>
+          <t>PA 605</t>
         </is>
       </c>
       <c r="D1190" s="2" t="inlineStr"/>
@@ -44101,7 +44101,7 @@
       </c>
       <c r="C1191" s="4" t="inlineStr">
         <is>
-          <t>PA-610</t>
+          <t>PA 610</t>
         </is>
       </c>
       <c r="D1191" s="4" t="inlineStr"/>
@@ -44136,7 +44136,7 @@
       </c>
       <c r="C1192" s="2" t="inlineStr">
         <is>
-          <t>PA-610</t>
+          <t>PA 610</t>
         </is>
       </c>
       <c r="D1192" s="2" t="inlineStr"/>
@@ -44171,7 +44171,7 @@
       </c>
       <c r="C1193" s="4" t="inlineStr">
         <is>
-          <t>PA-610</t>
+          <t>PA 610</t>
         </is>
       </c>
       <c r="D1193" s="4" t="inlineStr"/>
@@ -44206,7 +44206,7 @@
       </c>
       <c r="C1194" s="2" t="inlineStr">
         <is>
-          <t>PA-610</t>
+          <t>PA 610</t>
         </is>
       </c>
       <c r="D1194" s="2" t="inlineStr"/>
@@ -44241,7 +44241,7 @@
       </c>
       <c r="C1195" s="4" t="inlineStr">
         <is>
-          <t>PA-615</t>
+          <t>PA 615</t>
         </is>
       </c>
       <c r="D1195" s="4" t="inlineStr"/>
@@ -44276,7 +44276,7 @@
       </c>
       <c r="C1196" s="2" t="inlineStr">
         <is>
-          <t>PA-615</t>
+          <t>PA 615</t>
         </is>
       </c>
       <c r="D1196" s="2" t="inlineStr"/>
@@ -44311,7 +44311,7 @@
       </c>
       <c r="C1197" s="4" t="inlineStr">
         <is>
-          <t>PA-615</t>
+          <t>PA 615</t>
         </is>
       </c>
       <c r="D1197" s="4" t="inlineStr"/>
@@ -44346,7 +44346,7 @@
       </c>
       <c r="C1198" s="2" t="inlineStr">
         <is>
-          <t>PA-615</t>
+          <t>PA 615</t>
         </is>
       </c>
       <c r="D1198" s="2" t="inlineStr"/>
@@ -44381,7 +44381,7 @@
       </c>
       <c r="C1199" s="4" t="inlineStr">
         <is>
-          <t>PA-625</t>
+          <t>PA 625</t>
         </is>
       </c>
       <c r="D1199" s="4" t="inlineStr">
@@ -44420,7 +44420,7 @@
       </c>
       <c r="C1200" s="2" t="inlineStr">
         <is>
-          <t>PA-625</t>
+          <t>PA 625</t>
         </is>
       </c>
       <c r="D1200" s="2" t="inlineStr">
@@ -44459,7 +44459,7 @@
       </c>
       <c r="C1201" s="4" t="inlineStr">
         <is>
-          <t>PA-635</t>
+          <t>PA 635</t>
         </is>
       </c>
       <c r="D1201" s="4" t="inlineStr">
@@ -44498,7 +44498,7 @@
       </c>
       <c r="C1202" s="2" t="inlineStr">
         <is>
-          <t>PA-635</t>
+          <t>PA 635</t>
         </is>
       </c>
       <c r="D1202" s="2" t="inlineStr">
@@ -44537,7 +44537,7 @@
       </c>
       <c r="C1203" s="4" t="inlineStr">
         <is>
-          <t>PU-100</t>
+          <t>PU 100</t>
         </is>
       </c>
       <c r="D1203" s="4" t="inlineStr"/>
@@ -44572,7 +44572,7 @@
       </c>
       <c r="C1204" s="2" t="inlineStr">
         <is>
-          <t>PU-100</t>
+          <t>PU 100</t>
         </is>
       </c>
       <c r="D1204" s="2" t="inlineStr"/>
@@ -44607,7 +44607,7 @@
       </c>
       <c r="C1205" s="4" t="inlineStr">
         <is>
-          <t>PU-100</t>
+          <t>PU 100</t>
         </is>
       </c>
       <c r="D1205" s="4" t="inlineStr"/>
@@ -44642,7 +44642,7 @@
       </c>
       <c r="C1206" s="2" t="inlineStr">
         <is>
-          <t>PU-100</t>
+          <t>PU 100</t>
         </is>
       </c>
       <c r="D1206" s="2" t="inlineStr"/>
@@ -44677,7 +44677,7 @@
       </c>
       <c r="C1207" s="4" t="inlineStr">
         <is>
-          <t>PU-150</t>
+          <t>PU 150</t>
         </is>
       </c>
       <c r="D1207" s="4" t="inlineStr"/>
@@ -44712,7 +44712,7 @@
       </c>
       <c r="C1208" s="2" t="inlineStr">
         <is>
-          <t>PU-150</t>
+          <t>PU 150</t>
         </is>
       </c>
       <c r="D1208" s="2" t="inlineStr"/>
@@ -44747,7 +44747,7 @@
       </c>
       <c r="C1209" s="4" t="inlineStr">
         <is>
-          <t>PU-150</t>
+          <t>PU 150</t>
         </is>
       </c>
       <c r="D1209" s="4" t="inlineStr"/>
@@ -44782,7 +44782,7 @@
       </c>
       <c r="C1210" s="2" t="inlineStr">
         <is>
-          <t>PU-150</t>
+          <t>PU 150</t>
         </is>
       </c>
       <c r="D1210" s="2" t="inlineStr"/>
@@ -44817,7 +44817,7 @@
       </c>
       <c r="C1211" s="4" t="inlineStr">
         <is>
-          <t>S-300</t>
+          <t>S 300</t>
         </is>
       </c>
       <c r="D1211" s="4" t="inlineStr">
@@ -44856,7 +44856,7 @@
       </c>
       <c r="C1212" s="2" t="inlineStr">
         <is>
-          <t>S-300</t>
+          <t>S 300</t>
         </is>
       </c>
       <c r="D1212" s="2" t="inlineStr">
@@ -44895,7 +44895,7 @@
       </c>
       <c r="C1213" s="4" t="inlineStr">
         <is>
-          <t>S-300</t>
+          <t>S 300</t>
         </is>
       </c>
       <c r="D1213" s="4" t="inlineStr">
@@ -44934,7 +44934,7 @@
       </c>
       <c r="C1214" s="2" t="inlineStr">
         <is>
-          <t>S-500</t>
+          <t>S 500</t>
         </is>
       </c>
       <c r="D1214" s="2" t="inlineStr">
@@ -44973,7 +44973,7 @@
       </c>
       <c r="C1215" s="4" t="inlineStr">
         <is>
-          <t>S-500</t>
+          <t>S 500</t>
         </is>
       </c>
       <c r="D1215" s="4" t="inlineStr">
@@ -45012,7 +45012,7 @@
       </c>
       <c r="C1216" s="2" t="inlineStr">
         <is>
-          <t>S-500</t>
+          <t>S 500</t>
         </is>
       </c>
       <c r="D1216" s="2" t="inlineStr">
@@ -45051,7 +45051,7 @@
       </c>
       <c r="C1217" s="4" t="inlineStr">
         <is>
-          <t>S-811</t>
+          <t>S 811</t>
         </is>
       </c>
       <c r="D1217" s="4" t="inlineStr">
@@ -45090,7 +45090,7 @@
       </c>
       <c r="C1218" s="2" t="inlineStr">
         <is>
-          <t>S-811</t>
+          <t>S 811</t>
         </is>
       </c>
       <c r="D1218" s="2" t="inlineStr">
@@ -45129,7 +45129,7 @@
       </c>
       <c r="C1219" s="4" t="inlineStr">
         <is>
-          <t>S-816</t>
+          <t>S 816</t>
         </is>
       </c>
       <c r="D1219" s="4" t="inlineStr">
@@ -45168,7 +45168,7 @@
       </c>
       <c r="C1220" s="2" t="inlineStr">
         <is>
-          <t>S-816</t>
+          <t>S 816</t>
         </is>
       </c>
       <c r="D1220" s="2" t="inlineStr">
@@ -45207,7 +45207,7 @@
       </c>
       <c r="C1221" s="4" t="inlineStr">
         <is>
-          <t>S-820</t>
+          <t>S 820</t>
         </is>
       </c>
       <c r="D1221" s="4" t="inlineStr">
@@ -45246,7 +45246,7 @@
       </c>
       <c r="C1222" s="2" t="inlineStr">
         <is>
-          <t>S-820</t>
+          <t>S 820</t>
         </is>
       </c>
       <c r="D1222" s="2" t="inlineStr">
@@ -45285,7 +45285,7 @@
       </c>
       <c r="C1223" s="4" t="inlineStr">
         <is>
-          <t>S-821</t>
+          <t>S 821</t>
         </is>
       </c>
       <c r="D1223" s="4" t="inlineStr">
@@ -45324,7 +45324,7 @@
       </c>
       <c r="C1224" s="2" t="inlineStr">
         <is>
-          <t>S-821</t>
+          <t>S 821</t>
         </is>
       </c>
       <c r="D1224" s="2" t="inlineStr">
@@ -45363,7 +45363,7 @@
       </c>
       <c r="C1225" s="4" t="inlineStr">
         <is>
-          <t>S-825</t>
+          <t>S 825</t>
         </is>
       </c>
       <c r="D1225" s="4" t="inlineStr">
@@ -45402,7 +45402,7 @@
       </c>
       <c r="C1226" s="2" t="inlineStr">
         <is>
-          <t>S-825</t>
+          <t>S 825</t>
         </is>
       </c>
       <c r="D1226" s="2" t="inlineStr">
@@ -45441,7 +45441,7 @@
       </c>
       <c r="C1227" s="4" t="inlineStr">
         <is>
-          <t>S-826</t>
+          <t>S 826</t>
         </is>
       </c>
       <c r="D1227" s="4" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="C1228" s="2" t="inlineStr">
         <is>
-          <t>S-826</t>
+          <t>S 826</t>
         </is>
       </c>
       <c r="D1228" s="2" t="inlineStr">
@@ -45519,7 +45519,7 @@
       </c>
       <c r="C1229" s="4" t="inlineStr">
         <is>
-          <t>S-830</t>
+          <t>S 830</t>
         </is>
       </c>
       <c r="D1229" s="4" t="inlineStr">
@@ -45558,7 +45558,7 @@
       </c>
       <c r="C1230" s="2" t="inlineStr">
         <is>
-          <t>S-830</t>
+          <t>S 830</t>
         </is>
       </c>
       <c r="D1230" s="2" t="inlineStr">
@@ -45597,7 +45597,7 @@
       </c>
       <c r="C1231" s="4" t="inlineStr">
         <is>
-          <t>S-831</t>
+          <t>S 831</t>
         </is>
       </c>
       <c r="D1231" s="4" t="inlineStr">
@@ -45636,7 +45636,7 @@
       </c>
       <c r="C1232" s="2" t="inlineStr">
         <is>
-          <t>S-831</t>
+          <t>S 831</t>
         </is>
       </c>
       <c r="D1232" s="2" t="inlineStr">
@@ -45675,7 +45675,7 @@
       </c>
       <c r="C1233" s="4" t="inlineStr">
         <is>
-          <t>S-835</t>
+          <t>S 835</t>
         </is>
       </c>
       <c r="D1233" s="4" t="inlineStr">
@@ -45714,7 +45714,7 @@
       </c>
       <c r="C1234" s="2" t="inlineStr">
         <is>
-          <t>S-835</t>
+          <t>S 835</t>
         </is>
       </c>
       <c r="D1234" s="2" t="inlineStr">
@@ -45753,7 +45753,7 @@
       </c>
       <c r="C1235" s="4" t="inlineStr">
         <is>
-          <t>S-836</t>
+          <t>S 836</t>
         </is>
       </c>
       <c r="D1235" s="4" t="inlineStr">
@@ -45792,7 +45792,7 @@
       </c>
       <c r="C1236" s="2" t="inlineStr">
         <is>
-          <t>S-836</t>
+          <t>S 836</t>
         </is>
       </c>
       <c r="D1236" s="2" t="inlineStr">
@@ -45831,7 +45831,7 @@
       </c>
       <c r="C1237" s="4" t="inlineStr">
         <is>
-          <t>S-840</t>
+          <t>S 840</t>
         </is>
       </c>
       <c r="D1237" s="4" t="inlineStr">
@@ -45870,7 +45870,7 @@
       </c>
       <c r="C1238" s="2" t="inlineStr">
         <is>
-          <t>S-840</t>
+          <t>S 840</t>
         </is>
       </c>
       <c r="D1238" s="2" t="inlineStr">
@@ -45909,7 +45909,7 @@
       </c>
       <c r="C1239" s="4" t="inlineStr">
         <is>
-          <t>S-841</t>
+          <t>S 841</t>
         </is>
       </c>
       <c r="D1239" s="4" t="inlineStr">
@@ -45948,7 +45948,7 @@
       </c>
       <c r="C1240" s="2" t="inlineStr">
         <is>
-          <t>S-841</t>
+          <t>S 841</t>
         </is>
       </c>
       <c r="D1240" s="2" t="inlineStr">
@@ -45987,7 +45987,7 @@
       </c>
       <c r="C1241" s="4" t="inlineStr">
         <is>
-          <t>S-845</t>
+          <t>S 845</t>
         </is>
       </c>
       <c r="D1241" s="4" t="inlineStr">
@@ -46026,7 +46026,7 @@
       </c>
       <c r="C1242" s="2" t="inlineStr">
         <is>
-          <t>S-845</t>
+          <t>S 845</t>
         </is>
       </c>
       <c r="D1242" s="2" t="inlineStr">
@@ -46065,7 +46065,7 @@
       </c>
       <c r="C1243" s="4" t="inlineStr">
         <is>
-          <t>S-846</t>
+          <t>S 846</t>
         </is>
       </c>
       <c r="D1243" s="4" t="inlineStr">
@@ -46104,7 +46104,7 @@
       </c>
       <c r="C1244" s="2" t="inlineStr">
         <is>
-          <t>S-846</t>
+          <t>S 846</t>
         </is>
       </c>
       <c r="D1244" s="2" t="inlineStr">
@@ -46143,7 +46143,7 @@
       </c>
       <c r="C1245" s="4" t="inlineStr">
         <is>
-          <t>S-850</t>
+          <t>S 850</t>
         </is>
       </c>
       <c r="D1245" s="4" t="inlineStr">
@@ -46182,7 +46182,7 @@
       </c>
       <c r="C1246" s="2" t="inlineStr">
         <is>
-          <t>S-850</t>
+          <t>S 850</t>
         </is>
       </c>
       <c r="D1246" s="2" t="inlineStr">
@@ -46221,7 +46221,7 @@
       </c>
       <c r="C1247" s="4" t="inlineStr">
         <is>
-          <t>S-851</t>
+          <t>S 851</t>
         </is>
       </c>
       <c r="D1247" s="4" t="inlineStr">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C1248" s="2" t="inlineStr">
         <is>
-          <t>S-851</t>
+          <t>S 851</t>
         </is>
       </c>
       <c r="D1248" s="2" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="C1249" s="4" t="inlineStr">
         <is>
-          <t>S-855</t>
+          <t>S 855</t>
         </is>
       </c>
       <c r="D1249" s="4" t="inlineStr">
@@ -46338,7 +46338,7 @@
       </c>
       <c r="C1250" s="2" t="inlineStr">
         <is>
-          <t>S-855</t>
+          <t>S 855</t>
         </is>
       </c>
       <c r="D1250" s="2" t="inlineStr">
@@ -46377,7 +46377,7 @@
       </c>
       <c r="C1251" s="4" t="inlineStr">
         <is>
-          <t>S-856</t>
+          <t>S 856</t>
         </is>
       </c>
       <c r="D1251" s="4" t="inlineStr">
@@ -46416,7 +46416,7 @@
       </c>
       <c r="C1252" s="2" t="inlineStr">
         <is>
-          <t>S-856</t>
+          <t>S 856</t>
         </is>
       </c>
       <c r="D1252" s="2" t="inlineStr">
@@ -46455,7 +46455,7 @@
       </c>
       <c r="C1253" s="4" t="inlineStr">
         <is>
-          <t>S-860</t>
+          <t>S 860</t>
         </is>
       </c>
       <c r="D1253" s="4" t="inlineStr">
@@ -46494,7 +46494,7 @@
       </c>
       <c r="C1254" s="2" t="inlineStr">
         <is>
-          <t>S-860</t>
+          <t>S 860</t>
         </is>
       </c>
       <c r="D1254" s="2" t="inlineStr">
@@ -46533,7 +46533,7 @@
       </c>
       <c r="C1255" s="4" t="inlineStr">
         <is>
-          <t>S-861</t>
+          <t>S 861</t>
         </is>
       </c>
       <c r="D1255" s="4" t="inlineStr">
@@ -46572,7 +46572,7 @@
       </c>
       <c r="C1256" s="2" t="inlineStr">
         <is>
-          <t>S-861</t>
+          <t>S 861</t>
         </is>
       </c>
       <c r="D1256" s="2" t="inlineStr">
@@ -46611,7 +46611,7 @@
       </c>
       <c r="C1257" s="4" t="inlineStr">
         <is>
-          <t>S-865</t>
+          <t>S 865</t>
         </is>
       </c>
       <c r="D1257" s="4" t="inlineStr">
@@ -46650,7 +46650,7 @@
       </c>
       <c r="C1258" s="2" t="inlineStr">
         <is>
-          <t>S-865</t>
+          <t>S 865</t>
         </is>
       </c>
       <c r="D1258" s="2" t="inlineStr">
@@ -46689,7 +46689,7 @@
       </c>
       <c r="C1259" s="4" t="inlineStr">
         <is>
-          <t>S-866</t>
+          <t>S 866</t>
         </is>
       </c>
       <c r="D1259" s="4" t="inlineStr">
@@ -46728,7 +46728,7 @@
       </c>
       <c r="C1260" s="2" t="inlineStr">
         <is>
-          <t>S-866</t>
+          <t>S 866</t>
         </is>
       </c>
       <c r="D1260" s="2" t="inlineStr">
@@ -46767,7 +46767,7 @@
       </c>
       <c r="C1261" s="4" t="inlineStr">
         <is>
-          <t>S-870</t>
+          <t>S 870</t>
         </is>
       </c>
       <c r="D1261" s="4" t="inlineStr">
@@ -46806,7 +46806,7 @@
       </c>
       <c r="C1262" s="2" t="inlineStr">
         <is>
-          <t>S-870</t>
+          <t>S 870</t>
         </is>
       </c>
       <c r="D1262" s="2" t="inlineStr">
@@ -46845,7 +46845,7 @@
       </c>
       <c r="C1263" s="4" t="inlineStr">
         <is>
-          <t>S-871</t>
+          <t>S 871</t>
         </is>
       </c>
       <c r="D1263" s="4" t="inlineStr">
@@ -46884,7 +46884,7 @@
       </c>
       <c r="C1264" s="2" t="inlineStr">
         <is>
-          <t>S-871</t>
+          <t>S 871</t>
         </is>
       </c>
       <c r="D1264" s="2" t="inlineStr">
@@ -46923,7 +46923,7 @@
       </c>
       <c r="C1265" s="4" t="inlineStr">
         <is>
-          <t>S-875</t>
+          <t>S 875</t>
         </is>
       </c>
       <c r="D1265" s="4" t="inlineStr">
@@ -46962,7 +46962,7 @@
       </c>
       <c r="C1266" s="2" t="inlineStr">
         <is>
-          <t>S-875</t>
+          <t>S 875</t>
         </is>
       </c>
       <c r="D1266" s="2" t="inlineStr">
@@ -47001,7 +47001,7 @@
       </c>
       <c r="C1267" s="4" t="inlineStr">
         <is>
-          <t>S-876</t>
+          <t>S 876</t>
         </is>
       </c>
       <c r="D1267" s="4" t="inlineStr">
@@ -47040,7 +47040,7 @@
       </c>
       <c r="C1268" s="2" t="inlineStr">
         <is>
-          <t>S-876</t>
+          <t>S 876</t>
         </is>
       </c>
       <c r="D1268" s="2" t="inlineStr">
@@ -47079,7 +47079,7 @@
       </c>
       <c r="C1269" s="4" t="inlineStr">
         <is>
-          <t>S-880</t>
+          <t>S 880</t>
         </is>
       </c>
       <c r="D1269" s="4" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="C1270" s="2" t="inlineStr">
         <is>
-          <t>S-880</t>
+          <t>S 880</t>
         </is>
       </c>
       <c r="D1270" s="2" t="inlineStr">
@@ -47157,7 +47157,7 @@
       </c>
       <c r="C1271" s="4" t="inlineStr">
         <is>
-          <t>S-881</t>
+          <t>S 881</t>
         </is>
       </c>
       <c r="D1271" s="4" t="inlineStr">
@@ -47196,7 +47196,7 @@
       </c>
       <c r="C1272" s="2" t="inlineStr">
         <is>
-          <t>S-881</t>
+          <t>S 881</t>
         </is>
       </c>
       <c r="D1272" s="2" t="inlineStr">
@@ -47235,7 +47235,7 @@
       </c>
       <c r="C1273" s="4" t="inlineStr">
         <is>
-          <t>S-885</t>
+          <t>S 885</t>
         </is>
       </c>
       <c r="D1273" s="4" t="inlineStr">
@@ -47274,7 +47274,7 @@
       </c>
       <c r="C1274" s="2" t="inlineStr">
         <is>
-          <t>S-885</t>
+          <t>S 885</t>
         </is>
       </c>
       <c r="D1274" s="2" t="inlineStr">
@@ -47313,7 +47313,7 @@
       </c>
       <c r="C1275" s="4" t="inlineStr">
         <is>
-          <t>S-886</t>
+          <t>S 886</t>
         </is>
       </c>
       <c r="D1275" s="4" t="inlineStr">
@@ -47352,7 +47352,7 @@
       </c>
       <c r="C1276" s="2" t="inlineStr">
         <is>
-          <t>S-886</t>
+          <t>S 886</t>
         </is>
       </c>
       <c r="D1276" s="2" t="inlineStr">
@@ -47391,7 +47391,7 @@
       </c>
       <c r="C1277" s="4" t="inlineStr">
         <is>
-          <t>WHPX-405</t>
+          <t>WHPX 405</t>
         </is>
       </c>
       <c r="D1277" s="4" t="inlineStr"/>
@@ -47426,7 +47426,7 @@
       </c>
       <c r="C1278" s="2" t="inlineStr">
         <is>
-          <t>WHPX-405</t>
+          <t>WHPX 405</t>
         </is>
       </c>
       <c r="D1278" s="2" t="inlineStr"/>
@@ -47461,7 +47461,7 @@
       </c>
       <c r="C1279" s="4" t="inlineStr">
         <is>
-          <t>WHPX-405</t>
+          <t>WHPX 405</t>
         </is>
       </c>
       <c r="D1279" s="4" t="inlineStr"/>
@@ -47496,7 +47496,7 @@
       </c>
       <c r="C1280" s="2" t="inlineStr">
         <is>
-          <t>WHPX-405</t>
+          <t>WHPX 405</t>
         </is>
       </c>
       <c r="D1280" s="2" t="inlineStr"/>
@@ -47531,7 +47531,7 @@
       </c>
       <c r="C1281" s="4" t="inlineStr">
         <is>
-          <t>WHPX-405</t>
+          <t>WHPX 405</t>
         </is>
       </c>
       <c r="D1281" s="4" t="inlineStr"/>
@@ -47566,7 +47566,7 @@
       </c>
       <c r="C1282" s="2" t="inlineStr">
         <is>
-          <t>WHPX-505</t>
+          <t>WHPX 505</t>
         </is>
       </c>
       <c r="D1282" s="2" t="inlineStr"/>
@@ -47601,7 +47601,7 @@
       </c>
       <c r="C1283" s="4" t="inlineStr">
         <is>
-          <t>WHPX-505</t>
+          <t>WHPX 505</t>
         </is>
       </c>
       <c r="D1283" s="4" t="inlineStr"/>
@@ -47636,7 +47636,7 @@
       </c>
       <c r="C1284" s="2" t="inlineStr">
         <is>
-          <t>WHPX-505</t>
+          <t>WHPX 505</t>
         </is>
       </c>
       <c r="D1284" s="2" t="inlineStr"/>
@@ -47671,7 +47671,7 @@
       </c>
       <c r="C1285" s="4" t="inlineStr">
         <is>
-          <t>WHPX-505</t>
+          <t>WHPX 505</t>
         </is>
       </c>
       <c r="D1285" s="4" t="inlineStr"/>
@@ -47706,7 +47706,7 @@
       </c>
       <c r="C1286" s="2" t="inlineStr">
         <is>
-          <t>WHPX-505</t>
+          <t>WHPX 505</t>
         </is>
       </c>
       <c r="D1286" s="2" t="inlineStr"/>
@@ -47741,7 +47741,7 @@
       </c>
       <c r="C1287" s="4" t="inlineStr">
         <is>
-          <t>WHPX-407</t>
+          <t>WHPX 407</t>
         </is>
       </c>
       <c r="D1287" s="4" t="inlineStr"/>
@@ -47776,7 +47776,7 @@
       </c>
       <c r="C1288" s="2" t="inlineStr">
         <is>
-          <t>WHPX-407</t>
+          <t>WHPX 407</t>
         </is>
       </c>
       <c r="D1288" s="2" t="inlineStr"/>
@@ -47811,7 +47811,7 @@
       </c>
       <c r="C1289" s="4" t="inlineStr">
         <is>
-          <t>WHPX-407</t>
+          <t>WHPX 407</t>
         </is>
       </c>
       <c r="D1289" s="4" t="inlineStr"/>
@@ -47846,7 +47846,7 @@
       </c>
       <c r="C1290" s="2" t="inlineStr">
         <is>
-          <t>WHPX-407</t>
+          <t>WHPX 407</t>
         </is>
       </c>
       <c r="D1290" s="2" t="inlineStr"/>
@@ -47881,7 +47881,7 @@
       </c>
       <c r="C1291" s="4" t="inlineStr">
         <is>
-          <t>WHPX-407</t>
+          <t>WHPX 407</t>
         </is>
       </c>
       <c r="D1291" s="4" t="inlineStr"/>
@@ -47916,7 +47916,7 @@
       </c>
       <c r="C1292" s="2" t="inlineStr">
         <is>
-          <t>WHPX-409</t>
+          <t>WHPX 409</t>
         </is>
       </c>
       <c r="D1292" s="2" t="inlineStr"/>
@@ -47951,7 +47951,7 @@
       </c>
       <c r="C1293" s="4" t="inlineStr">
         <is>
-          <t>WHPX-409</t>
+          <t>WHPX 409</t>
         </is>
       </c>
       <c r="D1293" s="4" t="inlineStr"/>
@@ -47986,7 +47986,7 @@
       </c>
       <c r="C1294" s="2" t="inlineStr">
         <is>
-          <t>WHPX-409</t>
+          <t>WHPX 409</t>
         </is>
       </c>
       <c r="D1294" s="2" t="inlineStr"/>
@@ -48021,7 +48021,7 @@
       </c>
       <c r="C1295" s="4" t="inlineStr">
         <is>
-          <t>WHPX-409</t>
+          <t>WHPX 409</t>
         </is>
       </c>
       <c r="D1295" s="4" t="inlineStr"/>
@@ -48056,7 +48056,7 @@
       </c>
       <c r="C1296" s="2" t="inlineStr">
         <is>
-          <t>WHPX-409</t>
+          <t>WHPX 409</t>
         </is>
       </c>
       <c r="D1296" s="2" t="inlineStr"/>
@@ -48091,7 +48091,7 @@
       </c>
       <c r="C1297" s="4" t="inlineStr">
         <is>
-          <t>WHPX-410</t>
+          <t>WHPX 410</t>
         </is>
       </c>
       <c r="D1297" s="4" t="inlineStr"/>
@@ -48126,7 +48126,7 @@
       </c>
       <c r="C1298" s="2" t="inlineStr">
         <is>
-          <t>WHPX-410</t>
+          <t>WHPX 410</t>
         </is>
       </c>
       <c r="D1298" s="2" t="inlineStr"/>
@@ -48161,7 +48161,7 @@
       </c>
       <c r="C1299" s="4" t="inlineStr">
         <is>
-          <t>WHPX-410</t>
+          <t>WHPX 410</t>
         </is>
       </c>
       <c r="D1299" s="4" t="inlineStr"/>
@@ -48196,7 +48196,7 @@
       </c>
       <c r="C1300" s="2" t="inlineStr">
         <is>
-          <t>WHPX-410</t>
+          <t>WHPX 410</t>
         </is>
       </c>
       <c r="D1300" s="2" t="inlineStr"/>
@@ -48231,7 +48231,7 @@
       </c>
       <c r="C1301" s="4" t="inlineStr">
         <is>
-          <t>WHPX-410</t>
+          <t>WHPX 410</t>
         </is>
       </c>
       <c r="D1301" s="4" t="inlineStr"/>
@@ -48266,7 +48266,7 @@
       </c>
       <c r="C1302" s="2" t="inlineStr">
         <is>
-          <t>WHPX-413</t>
+          <t>WHPX 413</t>
         </is>
       </c>
       <c r="D1302" s="2" t="inlineStr"/>
@@ -48301,7 +48301,7 @@
       </c>
       <c r="C1303" s="4" t="inlineStr">
         <is>
-          <t>WHPX-413</t>
+          <t>WHPX 413</t>
         </is>
       </c>
       <c r="D1303" s="4" t="inlineStr"/>
@@ -48336,7 +48336,7 @@
       </c>
       <c r="C1304" s="2" t="inlineStr">
         <is>
-          <t>WHPX-413</t>
+          <t>WHPX 413</t>
         </is>
       </c>
       <c r="D1304" s="2" t="inlineStr"/>
@@ -48371,7 +48371,7 @@
       </c>
       <c r="C1305" s="4" t="inlineStr">
         <is>
-          <t>WHPX-413</t>
+          <t>WHPX 413</t>
         </is>
       </c>
       <c r="D1305" s="4" t="inlineStr"/>
@@ -48406,7 +48406,7 @@
       </c>
       <c r="C1306" s="2" t="inlineStr">
         <is>
-          <t>WHPX-413</t>
+          <t>WHPX 413</t>
         </is>
       </c>
       <c r="D1306" s="2" t="inlineStr"/>
@@ -48441,7 +48441,7 @@
       </c>
       <c r="C1307" s="4" t="inlineStr">
         <is>
-          <t>WHPX-507</t>
+          <t>WHPX 507</t>
         </is>
       </c>
       <c r="D1307" s="4" t="inlineStr"/>
@@ -48476,7 +48476,7 @@
       </c>
       <c r="C1308" s="2" t="inlineStr">
         <is>
-          <t>WHPX-507</t>
+          <t>WHPX 507</t>
         </is>
       </c>
       <c r="D1308" s="2" t="inlineStr"/>
@@ -48511,7 +48511,7 @@
       </c>
       <c r="C1309" s="4" t="inlineStr">
         <is>
-          <t>WHPX-507</t>
+          <t>WHPX 507</t>
         </is>
       </c>
       <c r="D1309" s="4" t="inlineStr"/>
@@ -48546,7 +48546,7 @@
       </c>
       <c r="C1310" s="2" t="inlineStr">
         <is>
-          <t>WHPX-507</t>
+          <t>WHPX 507</t>
         </is>
       </c>
       <c r="D1310" s="2" t="inlineStr"/>
@@ -48581,7 +48581,7 @@
       </c>
       <c r="C1311" s="4" t="inlineStr">
         <is>
-          <t>WHPX-507</t>
+          <t>WHPX 507</t>
         </is>
       </c>
       <c r="D1311" s="4" t="inlineStr"/>
@@ -48616,7 +48616,7 @@
       </c>
       <c r="C1312" s="2" t="inlineStr">
         <is>
-          <t>WHPX-508</t>
+          <t>WHPX 508</t>
         </is>
       </c>
       <c r="D1312" s="2" t="inlineStr"/>
@@ -48651,7 +48651,7 @@
       </c>
       <c r="C1313" s="4" t="inlineStr">
         <is>
-          <t>WHPX-508</t>
+          <t>WHPX 508</t>
         </is>
       </c>
       <c r="D1313" s="4" t="inlineStr"/>
@@ -48686,7 +48686,7 @@
       </c>
       <c r="C1314" s="2" t="inlineStr">
         <is>
-          <t>WHPX-508</t>
+          <t>WHPX 508</t>
         </is>
       </c>
       <c r="D1314" s="2" t="inlineStr"/>
@@ -48721,7 +48721,7 @@
       </c>
       <c r="C1315" s="4" t="inlineStr">
         <is>
-          <t>WHPX-508</t>
+          <t>WHPX 508</t>
         </is>
       </c>
       <c r="D1315" s="4" t="inlineStr"/>
@@ -48756,7 +48756,7 @@
       </c>
       <c r="C1316" s="2" t="inlineStr">
         <is>
-          <t>WHPX-508</t>
+          <t>WHPX 508</t>
         </is>
       </c>
       <c r="D1316" s="2" t="inlineStr"/>
@@ -48791,7 +48791,7 @@
       </c>
       <c r="C1317" s="4" t="inlineStr">
         <is>
-          <t>WHPX-513</t>
+          <t>WHPX 513</t>
         </is>
       </c>
       <c r="D1317" s="4" t="inlineStr"/>
@@ -48826,7 +48826,7 @@
       </c>
       <c r="C1318" s="2" t="inlineStr">
         <is>
-          <t>WHPX-513</t>
+          <t>WHPX 513</t>
         </is>
       </c>
       <c r="D1318" s="2" t="inlineStr"/>
@@ -48861,7 +48861,7 @@
       </c>
       <c r="C1319" s="4" t="inlineStr">
         <is>
-          <t>WHPX-513</t>
+          <t>WHPX 513</t>
         </is>
       </c>
       <c r="D1319" s="4" t="inlineStr"/>
@@ -48896,7 +48896,7 @@
       </c>
       <c r="C1320" s="2" t="inlineStr">
         <is>
-          <t>WHPX-513</t>
+          <t>WHPX 513</t>
         </is>
       </c>
       <c r="D1320" s="2" t="inlineStr"/>
@@ -48931,7 +48931,7 @@
       </c>
       <c r="C1321" s="4" t="inlineStr">
         <is>
-          <t>WHPX-513</t>
+          <t>WHPX 513</t>
         </is>
       </c>
       <c r="D1321" s="4" t="inlineStr"/>
@@ -48966,7 +48966,7 @@
       </c>
       <c r="C1322" s="2" t="inlineStr">
         <is>
-          <t>SJ-E-all types</t>
+          <t>SJ-E all types</t>
         </is>
       </c>
       <c r="D1322" s="2" t="inlineStr"/>
@@ -49001,7 +49001,7 @@
       </c>
       <c r="C1323" s="4" t="inlineStr">
         <is>
-          <t>SJ-G-all types</t>
+          <t>SJ-G all types</t>
         </is>
       </c>
       <c r="D1323" s="4" t="inlineStr"/>
@@ -49071,7 +49071,7 @@
       </c>
       <c r="C1325" s="4" t="inlineStr">
         <is>
-          <t>OSA-7</t>
+          <t>OSA 7</t>
         </is>
       </c>
       <c r="D1325" s="4" t="inlineStr"/>
@@ -49106,7 +49106,7 @@
       </c>
       <c r="C1326" s="2" t="inlineStr">
         <is>
-          <t>OSA-7</t>
+          <t>OSA 7</t>
         </is>
       </c>
       <c r="D1326" s="2" t="inlineStr"/>
@@ -49141,7 +49141,7 @@
       </c>
       <c r="C1327" s="4" t="inlineStr">
         <is>
-          <t>OSA-20</t>
+          <t>OSA 20</t>
         </is>
       </c>
       <c r="D1327" s="4" t="inlineStr"/>
@@ -49176,7 +49176,7 @@
       </c>
       <c r="C1328" s="2" t="inlineStr">
         <is>
-          <t>OSA-35</t>
+          <t>OSA 35</t>
         </is>
       </c>
       <c r="D1328" s="2" t="inlineStr"/>
@@ -49211,7 +49211,7 @@
       </c>
       <c r="C1329" s="4" t="inlineStr">
         <is>
-          <t>OSB-20</t>
+          <t>OSB 20</t>
         </is>
       </c>
       <c r="D1329" s="4" t="inlineStr"/>
@@ -49246,7 +49246,7 @@
       </c>
       <c r="C1330" s="2" t="inlineStr">
         <is>
-          <t>OSB-30</t>
+          <t>OSB 30</t>
         </is>
       </c>
       <c r="D1330" s="2" t="inlineStr"/>
@@ -49281,7 +49281,7 @@
       </c>
       <c r="C1331" s="4" t="inlineStr">
         <is>
-          <t>OSB-35</t>
+          <t>OSB 35</t>
         </is>
       </c>
       <c r="D1331" s="4" t="inlineStr"/>
@@ -49316,7 +49316,7 @@
       </c>
       <c r="C1332" s="2" t="inlineStr">
         <is>
-          <t>OSC-4</t>
+          <t>OSC 4</t>
         </is>
       </c>
       <c r="D1332" s="2" t="inlineStr"/>
@@ -49351,7 +49351,7 @@
       </c>
       <c r="C1333" s="4" t="inlineStr">
         <is>
-          <t>OSC-4</t>
+          <t>OSC 4</t>
         </is>
       </c>
       <c r="D1333" s="4" t="inlineStr"/>
@@ -49386,7 +49386,7 @@
       </c>
       <c r="C1334" s="2" t="inlineStr">
         <is>
-          <t>OSC-5</t>
+          <t>OSC 5</t>
         </is>
       </c>
       <c r="D1334" s="2" t="inlineStr"/>
@@ -49421,7 +49421,7 @@
       </c>
       <c r="C1335" s="4" t="inlineStr">
         <is>
-          <t>OSC-5</t>
+          <t>OSC 5</t>
         </is>
       </c>
       <c r="D1335" s="4" t="inlineStr"/>
@@ -49456,7 +49456,7 @@
       </c>
       <c r="C1336" s="2" t="inlineStr">
         <is>
-          <t>OSC-15</t>
+          <t>OSC 15</t>
         </is>
       </c>
       <c r="D1336" s="2" t="inlineStr"/>
@@ -49491,7 +49491,7 @@
       </c>
       <c r="C1337" s="4" t="inlineStr">
         <is>
-          <t>OSC-18</t>
+          <t>OSC 18</t>
         </is>
       </c>
       <c r="D1337" s="4" t="inlineStr"/>
@@ -49526,7 +49526,7 @@
       </c>
       <c r="C1338" s="2" t="inlineStr">
         <is>
-          <t>OSC-25</t>
+          <t>OSC 25</t>
         </is>
       </c>
       <c r="D1338" s="2" t="inlineStr"/>
@@ -49561,7 +49561,7 @@
       </c>
       <c r="C1339" s="4" t="inlineStr">
         <is>
-          <t>OSC-30</t>
+          <t>OSC 30</t>
         </is>
       </c>
       <c r="D1339" s="4" t="inlineStr"/>
@@ -49596,7 +49596,7 @@
       </c>
       <c r="C1340" s="2" t="inlineStr">
         <is>
-          <t>OSC-40</t>
+          <t>OSC 40</t>
         </is>
       </c>
       <c r="D1340" s="2" t="inlineStr"/>
@@ -49631,7 +49631,7 @@
       </c>
       <c r="C1341" s="4" t="inlineStr">
         <is>
-          <t>OSC-50</t>
+          <t>OSC 50</t>
         </is>
       </c>
       <c r="D1341" s="4" t="inlineStr"/>
@@ -49666,7 +49666,7 @@
       </c>
       <c r="C1342" s="2" t="inlineStr">
         <is>
-          <t>OSD-all types</t>
+          <t>OSD all types</t>
         </is>
       </c>
       <c r="D1342" s="2" t="inlineStr"/>
@@ -49701,7 +49701,7 @@
       </c>
       <c r="C1343" s="4" t="inlineStr">
         <is>
-          <t>OSD-all types</t>
+          <t>OSD all types</t>
         </is>
       </c>
       <c r="D1343" s="4" t="inlineStr"/>
@@ -49736,7 +49736,7 @@
       </c>
       <c r="C1344" s="2" t="inlineStr">
         <is>
-          <t>OSE-all types</t>
+          <t>OSE all types</t>
         </is>
       </c>
       <c r="D1344" s="2" t="inlineStr"/>
@@ -49771,7 +49771,7 @@
       </c>
       <c r="C1345" s="4" t="inlineStr">
         <is>
-          <t>OSE-all types</t>
+          <t>OSE all types</t>
         </is>
       </c>
       <c r="D1345" s="4" t="inlineStr"/>
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C1346" s="2" t="inlineStr">
         <is>
-          <t>OTA-2</t>
+          <t>OTA 2</t>
         </is>
       </c>
       <c r="D1346" s="2" t="inlineStr"/>
@@ -49841,7 +49841,7 @@
       </c>
       <c r="C1347" s="4" t="inlineStr">
         <is>
-          <t>OTA-7</t>
+          <t>OTA 7</t>
         </is>
       </c>
       <c r="D1347" s="4" t="inlineStr"/>
@@ -49876,7 +49876,7 @@
       </c>
       <c r="C1348" s="2" t="inlineStr">
         <is>
-          <t>OTA-14</t>
+          <t>OTA 14</t>
         </is>
       </c>
       <c r="D1348" s="2" t="inlineStr"/>
@@ -49911,7 +49911,7 @@
       </c>
       <c r="C1349" s="4" t="inlineStr">
         <is>
-          <t>OTA-14</t>
+          <t>OTA 14</t>
         </is>
       </c>
       <c r="D1349" s="4" t="inlineStr"/>
@@ -49946,7 +49946,7 @@
       </c>
       <c r="C1350" s="2" t="inlineStr">
         <is>
-          <t>OTA-14</t>
+          <t>OTA 14</t>
         </is>
       </c>
       <c r="D1350" s="2" t="inlineStr"/>
@@ -49981,7 +49981,7 @@
       </c>
       <c r="C1351" s="4" t="inlineStr">
         <is>
-          <t>OTA-18</t>
+          <t>OTA 18</t>
         </is>
       </c>
       <c r="D1351" s="4" t="inlineStr"/>
@@ -50016,7 +50016,7 @@
       </c>
       <c r="C1352" s="2" t="inlineStr">
         <is>
-          <t>OTA-30</t>
+          <t>OTA 30</t>
         </is>
       </c>
       <c r="D1352" s="2" t="inlineStr"/>
@@ -50051,7 +50051,7 @@
       </c>
       <c r="C1353" s="4" t="inlineStr">
         <is>
-          <t>OTB-1</t>
+          <t>OTB 1</t>
         </is>
       </c>
       <c r="D1353" s="4" t="inlineStr"/>
@@ -50086,7 +50086,7 @@
       </c>
       <c r="C1354" s="2" t="inlineStr">
         <is>
-          <t>OTB-1</t>
+          <t>OTB 1</t>
         </is>
       </c>
       <c r="D1354" s="2" t="inlineStr"/>
@@ -50121,7 +50121,7 @@
       </c>
       <c r="C1355" s="4" t="inlineStr">
         <is>
-          <t>OTB-3</t>
+          <t>OTB 3</t>
         </is>
       </c>
       <c r="D1355" s="4" t="inlineStr"/>
@@ -50156,7 +50156,7 @@
       </c>
       <c r="C1356" s="2" t="inlineStr">
         <is>
-          <t>OTB-3</t>
+          <t>OTB 3</t>
         </is>
       </c>
       <c r="D1356" s="2" t="inlineStr"/>
@@ -50191,7 +50191,7 @@
       </c>
       <c r="C1357" s="4" t="inlineStr">
         <is>
-          <t>OTB-9</t>
+          <t>OTB 9</t>
         </is>
       </c>
       <c r="D1357" s="4" t="inlineStr"/>
@@ -50226,7 +50226,7 @@
       </c>
       <c r="C1358" s="2" t="inlineStr">
         <is>
-          <t>OTB-9</t>
+          <t>OTB 9</t>
         </is>
       </c>
       <c r="D1358" s="2" t="inlineStr"/>
@@ -50261,7 +50261,7 @@
       </c>
       <c r="C1359" s="4" t="inlineStr">
         <is>
-          <t>OTB-18</t>
+          <t>OTB 18</t>
         </is>
       </c>
       <c r="D1359" s="4" t="inlineStr"/>
@@ -50296,7 +50296,7 @@
       </c>
       <c r="C1360" s="2" t="inlineStr">
         <is>
-          <t>OTB-35</t>
+          <t>OTB 35</t>
         </is>
       </c>
       <c r="D1360" s="2" t="inlineStr"/>
@@ -50331,7 +50331,7 @@
       </c>
       <c r="C1361" s="4" t="inlineStr">
         <is>
-          <t>OTC-all types</t>
+          <t>OTC all types</t>
         </is>
       </c>
       <c r="D1361" s="4" t="inlineStr"/>
@@ -50366,7 +50366,7 @@
       </c>
       <c r="C1362" s="2" t="inlineStr">
         <is>
-          <t>OTC-all types</t>
+          <t>OTC all types</t>
         </is>
       </c>
       <c r="D1362" s="2" t="inlineStr"/>
